--- a/resources/combat/spell.xlsx
+++ b/resources/combat/spell.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="752" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="common_spell" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="spell_data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="passive_data" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="buff_data" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="anim_montage_override_data" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="effect_actor_override_data" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="common_spell" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spell_data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="passive_data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="buff_data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="anim_montage_override_data" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="effect_actor_override_data" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="2" hidden="1">spell_data!#REF!</definedName>
@@ -456,7 +456,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -752,6 +752,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3897,7 +3900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E587"/>
+  <dimension ref="A1:E589"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" style="42" min="1" max="1"/>
@@ -5328,7 +5331,7 @@
       <c r="A60" s="6" t="n">
         <v>610</v>
       </c>
-      <c r="B60" s="76" t="inlineStr">
+      <c r="B60" s="64" t="inlineStr">
         <is>
           <t>火球</t>
         </is>
@@ -13556,42 +13559,46 @@
       </c>
     </row>
     <row r="425" ht="16.5" customHeight="1" s="57">
-      <c r="A425" s="6" t="n">
-        <v>900023</v>
-      </c>
-      <c r="B425" s="43" t="inlineStr">
-        <is>
-          <t>水清决</t>
-        </is>
-      </c>
-      <c r="D425" s="43" t="inlineStr">
-        <is>
-          <t>icon_spell_009</t>
-        </is>
-      </c>
+      <c r="A425" s="42" t="n">
+        <v>900015</v>
+      </c>
+      <c r="B425" s="3" t="inlineStr">
+        <is>
+          <t>朱雀流火</t>
+        </is>
+      </c>
+      <c r="C425" s="30" t="inlineStr">
+        <is>
+          <t>对 3 个目标各 160% 伤害</t>
+        </is>
+      </c>
+      <c r="D425" s="43" t="n"/>
+      <c r="E425" s="30" t="n"/>
     </row>
     <row r="426" ht="16.5" customHeight="1" s="57">
-      <c r="A426" s="6" t="n">
-        <v>900024</v>
-      </c>
-      <c r="B426" s="43" t="inlineStr">
-        <is>
-          <t>冰清决</t>
-        </is>
-      </c>
-      <c r="D426" s="43" t="inlineStr">
-        <is>
-          <t>icon_spell_009</t>
-        </is>
-      </c>
+      <c r="A426" s="42" t="n">
+        <v>900016</v>
+      </c>
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>朱雀焚天</t>
+        </is>
+      </c>
+      <c r="C426" s="30" t="inlineStr">
+        <is>
+          <t>「焚天朱雀」（原句：新增传说灵兽「焚天朱雀」，model_id 1075，品质 3、元素 fire，）</t>
+        </is>
+      </c>
+      <c r="D426" s="43" t="n"/>
+      <c r="E426" s="30" t="n"/>
     </row>
     <row r="427" ht="16.5" customHeight="1" s="57">
       <c r="A427" s="6" t="n">
-        <v>900025</v>
+        <v>900023</v>
       </c>
       <c r="B427" s="43" t="inlineStr">
         <is>
-          <t>玉清诀</t>
+          <t>水清决</t>
         </is>
       </c>
       <c r="D427" s="43" t="inlineStr">
@@ -13602,11 +13609,11 @@
     </row>
     <row r="428" ht="16.5" customHeight="1" s="57">
       <c r="A428" s="6" t="n">
-        <v>900026</v>
+        <v>900024</v>
       </c>
       <c r="B428" s="43" t="inlineStr">
         <is>
-          <t>晶清决</t>
+          <t>冰清决</t>
         </is>
       </c>
       <c r="D428" s="43" t="inlineStr">
@@ -13617,176 +13624,176 @@
     </row>
     <row r="429" ht="16.5" customHeight="1" s="57">
       <c r="A429" s="6" t="n">
-        <v>900027</v>
+        <v>900025</v>
       </c>
       <c r="B429" s="43" t="inlineStr">
         <is>
-          <t>笑里藏刀</t>
+          <t>玉清诀</t>
         </is>
       </c>
       <c r="D429" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_012</t>
+          <t>icon_spell_009</t>
         </is>
       </c>
     </row>
     <row r="430" ht="16.5" customHeight="1" s="57">
       <c r="A430" s="6" t="n">
-        <v>900028</v>
+        <v>900026</v>
       </c>
       <c r="B430" s="43" t="inlineStr">
         <is>
-          <t>野兽之力</t>
+          <t>晶清决</t>
         </is>
       </c>
       <c r="D430" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_016</t>
+          <t>icon_spell_009</t>
         </is>
       </c>
     </row>
     <row r="431" ht="16.5" customHeight="1" s="57">
       <c r="A431" s="6" t="n">
-        <v>900029</v>
+        <v>900027</v>
       </c>
       <c r="B431" s="43" t="inlineStr">
         <is>
-          <t>魔兽之印</t>
+          <t>笑里藏刀</t>
         </is>
       </c>
       <c r="D431" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_015</t>
+          <t>icon_spell_012</t>
         </is>
       </c>
     </row>
     <row r="432" ht="16.5" customHeight="1" s="57">
       <c r="A432" s="6" t="n">
-        <v>900030</v>
+        <v>900028</v>
       </c>
       <c r="B432" s="43" t="inlineStr">
         <is>
-          <t>圣甲之灵</t>
+          <t>野兽之力</t>
         </is>
       </c>
       <c r="D432" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_019</t>
+          <t>icon_spell_016</t>
         </is>
       </c>
     </row>
     <row r="433" ht="16.5" customHeight="1" s="57">
       <c r="A433" s="6" t="n">
-        <v>900031</v>
+        <v>900029</v>
       </c>
       <c r="B433" s="43" t="inlineStr">
         <is>
-          <t>罗汉金钟</t>
+          <t>魔兽之印</t>
         </is>
       </c>
       <c r="D433" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_004</t>
+          <t>icon_spell_015</t>
         </is>
       </c>
     </row>
     <row r="434" ht="16.5" customHeight="1" s="57">
       <c r="A434" s="6" t="n">
-        <v>900032</v>
+        <v>900030</v>
       </c>
       <c r="B434" s="43" t="inlineStr">
         <is>
-          <t>放下屠刀</t>
+          <t>圣甲之灵</t>
         </is>
       </c>
       <c r="D434" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_025</t>
+          <t>icon_spell_019</t>
         </is>
       </c>
     </row>
     <row r="435" ht="16.5" customHeight="1" s="57">
       <c r="A435" s="6" t="n">
-        <v>900033</v>
+        <v>900031</v>
       </c>
       <c r="B435" s="43" t="inlineStr">
         <is>
-          <t>破血狂攻</t>
+          <t>罗汉金钟</t>
         </is>
       </c>
       <c r="D435" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_038</t>
+          <t>icon_spell_004</t>
         </is>
       </c>
     </row>
     <row r="436" ht="16.5" customHeight="1" s="57">
       <c r="A436" s="6" t="n">
-        <v>900034</v>
+        <v>900032</v>
       </c>
       <c r="B436" s="43" t="inlineStr">
         <is>
-          <t>弱点击破</t>
+          <t>放下屠刀</t>
         </is>
       </c>
       <c r="D436" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_008</t>
+          <t>icon_spell_025</t>
         </is>
       </c>
     </row>
     <row r="437" ht="16.5" customHeight="1" s="57">
       <c r="A437" s="6" t="n">
-        <v>900035</v>
+        <v>900033</v>
       </c>
       <c r="B437" s="43" t="inlineStr">
         <is>
-          <t>破碎无双</t>
+          <t>破血狂攻</t>
         </is>
       </c>
       <c r="D437" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_030</t>
+          <t>icon_spell_038</t>
         </is>
       </c>
     </row>
     <row r="438" ht="16.5" customHeight="1" s="57">
       <c r="A438" s="6" t="n">
-        <v>900036</v>
+        <v>900034</v>
       </c>
       <c r="B438" s="43" t="inlineStr">
         <is>
-          <t>气疗术</t>
+          <t>弱点击破</t>
         </is>
       </c>
       <c r="D438" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_017</t>
+          <t>icon_spell_008</t>
         </is>
       </c>
     </row>
     <row r="439" ht="16.5" customHeight="1" s="57">
       <c r="A439" s="6" t="n">
-        <v>900037</v>
+        <v>900035</v>
       </c>
       <c r="B439" s="43" t="inlineStr">
         <is>
-          <t>心疗术</t>
+          <t>破碎无双</t>
         </is>
       </c>
       <c r="D439" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_017</t>
+          <t>icon_spell_030</t>
         </is>
       </c>
     </row>
     <row r="440" ht="16.5" customHeight="1" s="57">
       <c r="A440" s="6" t="n">
-        <v>900038</v>
+        <v>900036</v>
       </c>
       <c r="B440" s="43" t="inlineStr">
         <is>
-          <t>命疗术</t>
+          <t>气疗术</t>
         </is>
       </c>
       <c r="D440" s="43" t="inlineStr">
@@ -13797,697 +13804,731 @@
     </row>
     <row r="441" ht="16.5" customHeight="1" s="57">
       <c r="A441" s="6" t="n">
-        <v>900039</v>
+        <v>900037</v>
       </c>
       <c r="B441" s="43" t="inlineStr">
         <is>
-          <t>起死回生</t>
+          <t>心疗术</t>
         </is>
       </c>
       <c r="D441" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_024</t>
+          <t>icon_spell_017</t>
         </is>
       </c>
     </row>
     <row r="442" ht="16.5" customHeight="1" s="57">
       <c r="A442" s="6" t="n">
-        <v>900040</v>
+        <v>900038</v>
       </c>
       <c r="B442" s="43" t="inlineStr">
         <is>
-          <t>回魂咒</t>
+          <t>命疗术</t>
         </is>
       </c>
       <c r="D442" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_024</t>
+          <t>icon_spell_017</t>
         </is>
       </c>
     </row>
     <row r="443" ht="16.5" customHeight="1" s="57">
       <c r="A443" s="6" t="n">
-        <v>900041</v>
+        <v>900039</v>
       </c>
       <c r="B443" s="43" t="inlineStr">
         <is>
-          <t>测试技能</t>
-        </is>
-      </c>
-      <c r="C443" s="30" t="inlineStr">
-        <is>
-          <t>对单个目标造成{damage}点伤害</t>
-        </is>
-      </c>
-      <c r="D443" s="43" t="n">
-        <v>1001</v>
-      </c>
-      <c r="E443" s="30" t="inlineStr">
-        <is>
-          <t>对单个目标造成{damage}点伤害</t>
-        </is>
-      </c>
+          <t>起死回生</t>
+        </is>
+      </c>
+      <c r="C443" s="30" t="n"/>
+      <c r="D443" s="43" t="inlineStr">
+        <is>
+          <t>icon_spell_024</t>
+        </is>
+      </c>
+      <c r="E443" s="30" t="n"/>
     </row>
     <row r="444" ht="16.5" customHeight="1" s="57">
       <c r="A444" s="6" t="n">
-        <v>1010001</v>
-      </c>
-      <c r="B444" s="3" t="inlineStr">
-        <is>
-          <t>御剑·养剑</t>
-        </is>
-      </c>
-      <c r="C444" s="81" t="inlineStr">
-        <is>
-          <t>开局即获得额外飞剑，加速进入战斗节奏。</t>
-        </is>
-      </c>
-      <c r="D444" s="0" t="n"/>
-      <c r="E444" s="30" t="inlineStr">
-        <is>
-          <t>首回合立即获得2把飞剑</t>
-        </is>
-      </c>
+        <v>900040</v>
+      </c>
+      <c r="B444" s="43" t="inlineStr">
+        <is>
+          <t>回魂咒</t>
+        </is>
+      </c>
+      <c r="C444" s="30" t="n"/>
+      <c r="D444" s="43" t="inlineStr">
+        <is>
+          <t>icon_spell_024</t>
+        </is>
+      </c>
+      <c r="E444" s="30" t="n"/>
     </row>
     <row r="445" ht="16.5" customHeight="1" s="57">
       <c r="A445" s="6" t="n">
+        <v>900041</v>
+      </c>
+      <c r="B445" s="43" t="inlineStr">
+        <is>
+          <t>测试技能</t>
+        </is>
+      </c>
+      <c r="C445" s="30" t="inlineStr">
+        <is>
+          <t>对单个目标造成{damage}点伤害</t>
+        </is>
+      </c>
+      <c r="D445" s="43" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E445" s="30" t="inlineStr">
+        <is>
+          <t>对单个目标造成{damage}点伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="6" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="B446" s="3" t="inlineStr">
+        <is>
+          <t>御剑·养剑</t>
+        </is>
+      </c>
+      <c r="C446" s="100" t="inlineStr">
+        <is>
+          <t>开局即获得额外飞剑，加速进入战斗节奏。</t>
+        </is>
+      </c>
+      <c r="D446" s="0" t="n"/>
+      <c r="E446" s="30" t="inlineStr">
+        <is>
+          <t>首回合立即获得2把飞剑</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="6" t="n">
         <v>1010002</v>
       </c>
-      <c r="B445" s="3" t="inlineStr">
+      <c r="B447" s="3" t="inlineStr">
         <is>
           <t>御剑·嗜杀</t>
         </is>
       </c>
-      <c r="C445" s="81" t="inlineStr">
+      <c r="C447" s="100" t="inlineStr">
         <is>
           <t>击败敌方时额外获得飞剑，杀敌越多剑越多。</t>
         </is>
       </c>
-      <c r="D445" s="0" t="n"/>
-      <c r="E445" s="30" t="inlineStr">
+      <c r="D447" s="0" t="n"/>
+      <c r="E447" s="30" t="inlineStr">
         <is>
           <t>造成击败时获得1把飞剑</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" s="42" t="n">
-        <v>1020001</v>
-      </c>
-      <c r="B446" s="3" t="inlineStr">
-        <is>
-          <t>诛仙·不息</t>
-        </is>
-      </c>
-      <c r="C446" s="30" t="inlineStr">
-        <is>
-          <t>诛仙释放后有概率不进入休息，保持战斗节奏。</t>
-        </is>
-      </c>
-      <c r="E446" s="30" t="inlineStr">
-        <is>
-          <t>诛仙释放后20%概率不进入休息状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" s="42" t="n">
-        <v>1020002</v>
-      </c>
-      <c r="B447" s="3" t="inlineStr">
-        <is>
-          <t>诛仙·三绝</t>
-        </is>
-      </c>
-      <c r="C447" s="30" t="inlineStr">
-        <is>
-          <t>三段剑击的暴击概率逐段递增，越到后段越容易暴击。</t>
-        </is>
-      </c>
-      <c r="E447" s="30" t="inlineStr">
-        <is>
-          <t>三诛仙次斩击顺次额外增加10%/20%/30%暴击概率</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="42" t="n">
-        <v>1030001</v>
+        <v>1020001</v>
       </c>
       <c r="B448" s="3" t="inlineStr">
         <is>
-          <t>万剑·漫天</t>
+          <t>诛仙·不息</t>
         </is>
       </c>
       <c r="C448" s="30" t="inlineStr">
         <is>
-          <t>飞剑覆盖范围扩大，可攻击更多目标。</t>
+          <t>诛仙释放后有概率不进入休息，保持战斗节奏。</t>
         </is>
       </c>
       <c r="E448" s="30" t="inlineStr">
         <is>
-          <t>增加1个攻击目标（共4个）</t>
+          <t>诛仙释放后20%概率不进入休息状态</t>
         </is>
       </c>
     </row>
     <row r="449" ht="27" customHeight="1" s="57">
       <c r="A449" s="42" t="n">
-        <v>1030002</v>
+        <v>1020002</v>
       </c>
       <c r="B449" s="3" t="inlineStr">
         <is>
-          <t>万剑·化劲</t>
+          <t>诛仙·三绝</t>
         </is>
       </c>
       <c r="C449" s="30" t="inlineStr">
         <is>
-          <t>放弃暴击，将暴击率转化为稳定的伤害增幅。</t>
+          <t>三段剑击的暴击概率逐段递增，越到后段越容易暴击。</t>
         </is>
       </c>
       <c r="E449" s="30" t="inlineStr">
         <is>
-          <t>该技能不触发物理暴击，基于物理暴击率X%增幅玩家的基础伤害伤害X%×2</t>
+          <t>三诛仙次斩击顺次额外增加10%/20%/30%暴击概率</t>
         </is>
       </c>
     </row>
     <row r="450" ht="40.5" customHeight="1" s="57">
       <c r="A450" s="42" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="B450" s="3" t="inlineStr">
+        <is>
+          <t>万剑·漫天</t>
+        </is>
+      </c>
+      <c r="C450" s="30" t="inlineStr">
+        <is>
+          <t>飞剑覆盖范围扩大，可攻击更多目标。</t>
+        </is>
+      </c>
+      <c r="E450" s="30" t="inlineStr">
+        <is>
+          <t>增加1个攻击目标（共4个）</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" ht="27" customHeight="1" s="57">
+      <c r="A451" s="42" t="n">
+        <v>1030002</v>
+      </c>
+      <c r="B451" s="3" t="inlineStr">
+        <is>
+          <t>万剑·化劲</t>
+        </is>
+      </c>
+      <c r="C451" s="30" t="inlineStr">
+        <is>
+          <t>放弃暴击，将暴击率转化为稳定的伤害增幅。</t>
+        </is>
+      </c>
+      <c r="E451" s="30" t="inlineStr">
+        <is>
+          <t>该技能不触发物理暴击，基于物理暴击率X%增幅玩家的基础伤害伤害X%×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="42" t="n">
         <v>1040001</v>
       </c>
-      <c r="B450" s="3" t="inlineStr">
+      <c r="B452" s="3" t="inlineStr">
         <is>
           <t>杀意·连破</t>
         </is>
       </c>
-      <c r="C450" s="30" t="inlineStr">
+      <c r="C452" s="30" t="inlineStr">
         <is>
           <t>击败敌方后杀意持续延长，连杀不止。</t>
         </is>
       </c>
-      <c r="E450" s="30" t="inlineStr">
+      <c r="E452" s="30" t="inlineStr">
         <is>
           <t>【杀意】状态下，主动单体攻击造成任意击败延长杀意效果1-2回合
 70%概率1回合，30%概率2回合</t>
         </is>
       </c>
     </row>
-    <row r="451" ht="27" customHeight="1" s="57">
-      <c r="A451" s="42" t="n">
-        <v>1040002</v>
-      </c>
-      <c r="B451" s="3" t="inlineStr">
-        <is>
-          <t>杀意·觉醒</t>
-        </is>
-      </c>
-      <c r="C451" s="30" t="inlineStr">
-        <is>
-          <t>诛仙击败时有概率触发杀意，连锁爆发。</t>
-        </is>
-      </c>
-      <c r="E451" s="30" t="inlineStr">
-        <is>
-          <t>诛仙击败非人物单位时，10%附加【杀意】并立刻触发1次【杀意】效果</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" s="42" t="n">
-        <v>1050001</v>
-      </c>
-      <c r="B452" s="3" t="inlineStr">
-        <is>
-          <t>剑魄·锋芒</t>
-        </is>
-      </c>
-      <c r="C452" s="30" t="inlineStr">
-        <is>
-          <t>飞剑追击的伤害上限提升。</t>
-        </is>
-      </c>
-      <c r="E452" s="30" t="inlineStr">
-        <is>
-          <t>飞剑伤害提升至最大气血8%</t>
-        </is>
-      </c>
-    </row>
     <row r="453">
       <c r="A453" s="42" t="n">
-        <v>1050002</v>
+        <v>1040002</v>
       </c>
       <c r="B453" s="3" t="inlineStr">
         <is>
-          <t>剑魄·聚剑</t>
+          <t>杀意·觉醒</t>
         </is>
       </c>
       <c r="C453" s="30" t="inlineStr">
         <is>
-          <t>飞剑容量扩大，宠物击败敌方时也可为主人获得飞剑。</t>
+          <t>诛仙击败时有概率触发杀意，连锁爆发。</t>
         </is>
       </c>
       <c r="E453" s="30" t="inlineStr">
         <is>
-          <t>飞剑上限+2(至5)，宠物击败30%概率获得飞剑</t>
+          <t>诛仙击败非人物单位时，10%附加【杀意】并立刻触发1次【杀意】效果</t>
         </is>
       </c>
     </row>
     <row r="454" ht="27" customHeight="1" s="57">
       <c r="A454" s="42" t="n">
-        <v>1060001</v>
+        <v>1050001</v>
       </c>
       <c r="B454" s="3" t="inlineStr">
         <is>
-          <t>天罡护体·先觉</t>
+          <t>剑魄·锋芒</t>
         </is>
       </c>
       <c r="C454" s="30" t="inlineStr">
         <is>
-          <t>面对高速敌方时格挡概率额外提升，以静制动。</t>
+          <t>飞剑追击的伤害上限提升。</t>
         </is>
       </c>
       <c r="E454" s="30" t="inlineStr">
         <is>
-          <t>对方速度速度高于自身时，【罡气】增加10%格挡概率</t>
+          <t>飞剑伤害提升至最大气血8%</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="42" t="n">
-        <v>1060002</v>
+        <v>1050002</v>
       </c>
       <c r="B455" s="3" t="inlineStr">
         <is>
-          <t>天罡护体·传罡</t>
+          <t>剑魄·聚剑</t>
         </is>
       </c>
       <c r="C455" s="30" t="inlineStr">
         <is>
-          <t>释放时将罡气同步传递给宠物，人宠共同受到护体。</t>
+          <t>飞剑容量扩大，宠物击败敌方时也可为主人获得飞剑。</t>
         </is>
       </c>
       <c r="E455" s="30" t="inlineStr">
         <is>
-          <t>主动释放时，己方物攻最高宠物获3回合【罡气】效果</t>
+          <t>飞剑上限+2(至5)，宠物击败30%概率获得飞剑</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="42" t="n">
-        <v>1070001</v>
+        <v>1060001</v>
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>追风·风驰</t>
+          <t>天罡护体·先觉</t>
         </is>
       </c>
       <c r="C456" s="30" t="inlineStr">
         <is>
-          <t>神速状态下击败低速目标可延长神速持续时间。</t>
+          <t>面对高速敌方时格挡概率额外提升，以静制动。</t>
         </is>
       </c>
       <c r="E456" s="30" t="inlineStr">
         <is>
-          <t>神速下击败速度低于自身单位时，延长1回合【神速】</t>
+          <t>对方速度速度高于自身时，【罡气】增加10%格挡概率</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="42" t="n">
-        <v>1070002</v>
+        <v>1060002</v>
       </c>
       <c r="B457" s="3" t="inlineStr">
         <is>
-          <t>追风·破速</t>
+          <t>天罡护体·传罡</t>
         </is>
       </c>
       <c r="C457" s="30" t="inlineStr">
         <is>
-          <t>神速状态下击败敌方可附加虚弱削弱效果。</t>
+          <t>释放时将罡气同步传递给宠物，人宠共同受到护体。</t>
         </is>
       </c>
       <c r="E457" s="30" t="inlineStr">
         <is>
-          <t>神速下击败对方时，附加1层【虚弱】</t>
+          <t>主动释放时，己方物攻最高宠物获3回合【罡气】效果</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="42" t="n">
-        <v>1080001</v>
+        <v>1070001</v>
       </c>
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>破军·趁危</t>
+          <t>追风·风驰</t>
         </is>
       </c>
       <c r="C458" s="30" t="inlineStr">
         <is>
-          <t>攻击重伤目标时暴击概率大幅提升，趁危追命。</t>
+          <t>神速状态下击败低速目标可延长神速持续时间。</t>
         </is>
       </c>
       <c r="E458" s="30" t="inlineStr">
         <is>
-          <t>对【重伤】单位，增加15%暴击率</t>
+          <t>神速下击败速度低于自身单位时，延长1回合【神速】</t>
         </is>
       </c>
     </row>
     <row r="459" ht="27" customHeight="1" s="57">
       <c r="A459" s="42" t="n">
-        <v>1080002</v>
+        <v>1070002</v>
       </c>
       <c r="B459" s="3" t="inlineStr">
         <is>
-          <t>破军·协攻</t>
+          <t>追风·破速</t>
         </is>
       </c>
       <c r="C459" s="30" t="inlineStr">
         <is>
-          <t>释放时宠物同步获得攻击力提升，人宠协攻。</t>
+          <t>神速状态下击败敌方可附加虚弱削弱效果。</t>
         </is>
       </c>
       <c r="E459" s="30" t="inlineStr">
         <is>
-          <t>释放后，我方物攻最高宠物单位本回合也增加20%物理攻击</t>
+          <t>神速下击败对方时，附加1层【虚弱】</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="42" t="n">
-        <v>1090001</v>
+        <v>1080001</v>
       </c>
       <c r="B460" s="3" t="inlineStr">
         <is>
-          <t>生死决·入骨</t>
+          <t>破军·趁危</t>
         </is>
       </c>
       <c r="C460" s="30" t="inlineStr">
         <is>
-          <t>获胜后为败方施加多层重伤，后续治疗难以恢复。</t>
+          <t>攻击重伤目标时暴击概率大幅提升，趁危追命。</t>
         </is>
       </c>
       <c r="E460" s="30" t="inlineStr">
         <is>
-          <t>获胜时，为倒地单位附加3层【重伤】</t>
+          <t>对【重伤】单位，增加15%暴击率</t>
         </is>
       </c>
     </row>
     <row r="461" ht="27" customHeight="1" s="57">
       <c r="A461" s="42" t="n">
+        <v>1080002</v>
+      </c>
+      <c r="B461" s="3" t="inlineStr">
+        <is>
+          <t>破军·协攻</t>
+        </is>
+      </c>
+      <c r="C461" s="30" t="inlineStr">
+        <is>
+          <t>释放时宠物同步获得攻击力提升，人宠协攻。</t>
+        </is>
+      </c>
+      <c r="E461" s="30" t="inlineStr">
+        <is>
+          <t>释放后，我方物攻最高宠物单位本回合也增加20%物理攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="42" t="n">
+        <v>1090001</v>
+      </c>
+      <c r="B462" s="3" t="inlineStr">
+        <is>
+          <t>生死决·入骨</t>
+        </is>
+      </c>
+      <c r="C462" s="30" t="inlineStr">
+        <is>
+          <t>获胜后为败方施加多层重伤，后续治疗难以恢复。</t>
+        </is>
+      </c>
+      <c r="E462" s="30" t="inlineStr">
+        <is>
+          <t>获胜时，为倒地单位附加3层【重伤】</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="27" customHeight="1" s="57">
+      <c r="A463" s="42" t="n">
         <v>1090002</v>
       </c>
-      <c r="B461" s="3" t="inlineStr">
+      <c r="B463" s="3" t="inlineStr">
         <is>
           <t>生死决·回生</t>
         </is>
       </c>
-      <c r="C461" s="30" t="inlineStr">
+      <c r="C463" s="30" t="inlineStr">
         <is>
           <t>获胜后回复全体友方气血，化险为夷。</t>
         </is>
       </c>
-      <c r="E461" s="30" t="inlineStr">
+      <c r="E463" s="30" t="inlineStr">
         <is>
           <t>获胜回复全体15%气血
 不超过自身最大气血的20%</t>
         </is>
       </c>
     </row>
-    <row r="462">
-      <c r="A462" s="42" t="n">
-        <v>2010001</v>
-      </c>
-      <c r="B462" s="3" t="inlineStr">
-        <is>
-          <t>驭风·乘胜</t>
-        </is>
-      </c>
-      <c r="C462" s="30" t="inlineStr">
-        <is>
-          <t>击败敌方时有概率额外积累风势。</t>
-        </is>
-      </c>
-      <c r="E462" s="30" t="inlineStr">
-        <is>
-          <t>造成击败时，20%概率增加1层【风势】</t>
-        </is>
-      </c>
-    </row>
-    <row r="463" ht="27" customHeight="1" s="57">
-      <c r="A463" s="42" t="n">
-        <v>2010002</v>
-      </c>
-      <c r="B463" s="3" t="inlineStr">
-        <is>
-          <t>驭风·化伤</t>
-        </is>
-      </c>
-      <c r="C463" s="30" t="inlineStr">
-        <is>
-          <t>每次进入狂风时法术伤害持续提升。</t>
-        </is>
-      </c>
-      <c r="E463" s="30" t="inlineStr">
-        <is>
-          <t>每次进入【狂风】时，附加【化伤】增益，增加2%的法术伤害结果，可叠加5次</t>
-        </is>
-      </c>
-    </row>
     <row r="464" ht="27" customHeight="1" s="57">
       <c r="A464" s="42" t="n">
-        <v>2020001</v>
+        <v>2010001</v>
       </c>
       <c r="B464" s="3" t="inlineStr">
         <is>
-          <t>扶摇·连追</t>
+          <t>驭风·乘胜</t>
         </is>
       </c>
       <c r="C464" s="30" t="inlineStr">
         <is>
-          <t>追击击败时再次追击，连杀不断。</t>
+          <t>击败敌方时有概率额外积累风势。</t>
         </is>
       </c>
       <c r="E464" s="30" t="inlineStr">
         <is>
-          <t>追击造成击败时，再以40%法伤结果追击1次气血最低目标</t>
+          <t>造成击败时，20%概率增加1层【风势】</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="42" t="n">
-        <v>2020002</v>
+        <v>2010002</v>
       </c>
       <c r="B465" s="3" t="inlineStr">
         <is>
-          <t>扶摇·蓄暴</t>
+          <t>驭风·化伤</t>
         </is>
       </c>
       <c r="C465" s="30" t="inlineStr">
         <is>
-          <t>低风势时法术暴击大幅提升，蓄势待发。</t>
+          <t>每次进入狂风时法术伤害持续提升。</t>
         </is>
       </c>
       <c r="E465" s="30" t="inlineStr">
         <is>
-          <t>风势小于等于3时，额外增加20%的法术暴击</t>
+          <t>每次进入【狂风】时，附加【化伤】增益，增加2%的法术伤害结果，可叠加5次</t>
         </is>
       </c>
     </row>
     <row r="466" ht="27" customHeight="1" s="57">
       <c r="A466" s="42" t="n">
-        <v>2030001</v>
+        <v>2020001</v>
       </c>
       <c r="B466" s="3" t="inlineStr">
         <is>
-          <t>罡风·凌速</t>
+          <t>扶摇·连追</t>
         </is>
       </c>
       <c r="C466" s="30" t="inlineStr">
         <is>
-          <t>攻击速度低于自身的目标时暴击率额外提升。</t>
+          <t>追击击败时再次追击，连杀不断。</t>
         </is>
       </c>
       <c r="E466" s="30" t="inlineStr">
         <is>
-          <t>自身速度高于攻击目标时，对攻击目标额外增加5%法术暴击率</t>
+          <t>追击造成击败时，再以40%法伤结果追击1次气血最低目标</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="42" t="n">
-        <v>2030002</v>
+        <v>2020002</v>
       </c>
       <c r="B467" s="3" t="inlineStr">
         <is>
-          <t>罡风·扩散</t>
+          <t>扶摇·蓄暴</t>
         </is>
       </c>
       <c r="C467" s="30" t="inlineStr">
         <is>
-          <t>风势充足时攻击范围扩大，覆盖更多目标。</t>
+          <t>低风势时法术暴击大幅提升，蓄势待发。</t>
         </is>
       </c>
       <c r="E467" s="30" t="inlineStr">
         <is>
-          <t>风势≥4层时，增加1个攻击目标</t>
+          <t>风势小于等于3时，额外增加20%的法术暴击</t>
         </is>
       </c>
     </row>
     <row r="468" ht="27" customHeight="1" s="57">
       <c r="A468" s="42" t="n">
+        <v>2030001</v>
+      </c>
+      <c r="B468" s="3" t="inlineStr">
+        <is>
+          <t>罡风·凌速</t>
+        </is>
+      </c>
+      <c r="C468" s="30" t="inlineStr">
+        <is>
+          <t>攻击速度低于自身的目标时暴击率额外提升。</t>
+        </is>
+      </c>
+      <c r="E468" s="30" t="inlineStr">
+        <is>
+          <t>自身速度高于攻击目标时，对攻击目标额外增加5%法术暴击率</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="42" t="n">
+        <v>2030002</v>
+      </c>
+      <c r="B469" s="3" t="inlineStr">
+        <is>
+          <t>罡风·扩散</t>
+        </is>
+      </c>
+      <c r="C469" s="30" t="inlineStr">
+        <is>
+          <t>风势充足时攻击范围扩大，覆盖更多目标。</t>
+        </is>
+      </c>
+      <c r="E469" s="30" t="inlineStr">
+        <is>
+          <t>风势≥4层时，增加1个攻击目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="42" t="n">
         <v>2040001</v>
       </c>
-      <c r="B468" s="3" t="inlineStr">
+      <c r="B470" s="3" t="inlineStr">
         <is>
           <t>乘风·连杀</t>
         </is>
       </c>
-      <c r="C468" s="30" t="inlineStr">
+      <c r="C470" s="30" t="inlineStr">
         <is>
           <t>单回合连续击败时有概率自动附加乘风效果。</t>
         </is>
       </c>
-      <c r="E468" s="30" t="inlineStr">
+      <c r="E470" s="30" t="inlineStr">
         <is>
           <t>自身单回合击败2个及以上的目标时
 50%概率为自身附加【乘风】效果</t>
         </is>
       </c>
     </row>
-    <row r="469">
-      <c r="A469" s="42" t="n">
-        <v>2040002</v>
-      </c>
-      <c r="B469" s="3" t="inlineStr">
-        <is>
-          <t>乘风·传功</t>
-        </is>
-      </c>
-      <c r="C469" s="30" t="inlineStr">
-        <is>
-          <t>释放时有概率同时为宠物附加相同效果。</t>
-        </is>
-      </c>
-      <c r="E469" s="30" t="inlineStr">
-        <is>
-          <t>50%同时给法攻最高宠物释放</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" s="42" t="n">
-        <v>2050001</v>
-      </c>
-      <c r="B470" s="3" t="inlineStr">
-        <is>
-          <t>裂空·续力</t>
-        </is>
-      </c>
-      <c r="C470" s="30" t="inlineStr">
-        <is>
-          <t>进入狂风时延长自身所有增益效果的持续时间。</t>
-        </is>
-      </c>
-      <c r="E470" s="30" t="inlineStr">
-        <is>
-          <t>进入【狂风】状态时，延长自身所有增益效果1回合</t>
-        </is>
-      </c>
-    </row>
     <row r="471">
       <c r="A471" s="42" t="n">
-        <v>2050002</v>
+        <v>2040002</v>
       </c>
       <c r="B471" s="3" t="inlineStr">
         <is>
-          <t>裂空·回气</t>
+          <t>乘风·传功</t>
         </is>
       </c>
       <c r="C471" s="30" t="inlineStr">
         <is>
-          <t>进入狂风时回复愤怒与法宝灵气。</t>
+          <t>释放时有概率同时为宠物附加相同效果。</t>
         </is>
       </c>
       <c r="E471" s="30" t="inlineStr">
         <is>
-          <t>进入狂风+10愤怒+1法宝灵气</t>
+          <t>50%同时给法攻最高宠物释放</t>
         </is>
       </c>
     </row>
     <row r="472" ht="27" customHeight="1" s="57">
       <c r="A472" s="42" t="n">
-        <v>2060001</v>
+        <v>2050001</v>
       </c>
       <c r="B472" s="3" t="inlineStr">
         <is>
-          <t>拂柳·灵动</t>
+          <t>裂空·续力</t>
         </is>
       </c>
       <c r="C472" s="30" t="inlineStr">
         <is>
-          <t>面对低速敌方时闪避能力额外提升。</t>
+          <t>进入狂风时延长自身所有增益效果的持续时间。</t>
         </is>
       </c>
       <c r="E472" s="30" t="inlineStr">
         <is>
-          <t>受到速度低于自身的单位攻击时，【拂柳】附加的物理闪避额外+10%</t>
+          <t>进入【狂风】状态时，延长自身所有增益效果1回合</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="42" t="n">
-        <v>2060002</v>
+        <v>2050002</v>
       </c>
       <c r="B473" s="3" t="inlineStr">
         <is>
-          <t>拂柳·存护</t>
+          <t>裂空·回气</t>
         </is>
       </c>
       <c r="C473" s="30" t="inlineStr">
         <is>
-          <t>被复活时有概率自动附加拂柳效果。</t>
+          <t>进入狂风时回复愤怒与法宝灵气。</t>
         </is>
       </c>
       <c r="E473" s="30" t="inlineStr">
         <is>
-          <t>被复活时30%概率附加【拂柳】</t>
+          <t>进入狂风+10愤怒+1法宝灵气</t>
         </is>
       </c>
     </row>
     <row r="474" ht="27" customHeight="1" s="57">
       <c r="A474" s="42" t="n">
-        <v>2070001</v>
+        <v>2060001</v>
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>祭风·竭力</t>
+          <t>拂柳·灵动</t>
         </is>
       </c>
       <c r="C474" s="30" t="inlineStr">
         <is>
-          <t>风势为零时额外消耗气血多获得一层风势。</t>
+          <t>面对低速敌方时闪避能力额外提升。</t>
         </is>
       </c>
       <c r="E474" s="30" t="inlineStr">
         <is>
-          <t>风势为0时，额外消耗10%最大气血获得1层风势（获得4层）</t>
+          <t>受到速度低于自身的单位攻击时，【拂柳】附加的物理闪避额外+10%</t>
         </is>
       </c>
     </row>
     <row r="475" ht="54" customHeight="1" s="57">
       <c r="A475" s="42" t="n">
+        <v>2060002</v>
+      </c>
+      <c r="B475" s="3" t="inlineStr">
+        <is>
+          <t>拂柳·存护</t>
+        </is>
+      </c>
+      <c r="C475" s="30" t="inlineStr">
+        <is>
+          <t>被复活时有概率自动附加拂柳效果。</t>
+        </is>
+      </c>
+      <c r="E475" s="30" t="inlineStr">
+        <is>
+          <t>被复活时30%概率附加【拂柳】</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="42" t="n">
+        <v>2070001</v>
+      </c>
+      <c r="B476" s="3" t="inlineStr">
+        <is>
+          <t>祭风·竭力</t>
+        </is>
+      </c>
+      <c r="C476" s="30" t="inlineStr">
+        <is>
+          <t>风势为零时额外消耗气血多获得一层风势。</t>
+        </is>
+      </c>
+      <c r="E476" s="30" t="inlineStr">
+        <is>
+          <t>风势为0时，额外消耗10%最大气血获得1层风势（获得4层）</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="27" customHeight="1" s="57">
+      <c r="A477" s="42" t="n">
         <v>2070002</v>
       </c>
-      <c r="B475" s="3" t="inlineStr">
+      <c r="B477" s="3" t="inlineStr">
         <is>
           <t>祭风·满溢</t>
         </is>
       </c>
-      <c r="C475" s="30" t="inlineStr">
+      <c r="C477" s="30" t="inlineStr">
         <is>
           <t>风势溢出时转化为法术伤害加成。</t>
         </is>
       </c>
-      <c r="E475" s="30" t="inlineStr">
+      <c r="E477" s="30" t="inlineStr">
         <is>
           <t>使用宁静时如果风势溢出(超过5层）
 附加【满溢】增益，持续2回合，
@@ -14496,852 +14537,852 @@
         </is>
       </c>
     </row>
-    <row r="476">
-      <c r="A476" s="42" t="n">
-        <v>2080001</v>
-      </c>
-      <c r="B476" s="3" t="inlineStr">
-        <is>
-          <t>碎空·穿透</t>
-        </is>
-      </c>
-      <c r="C476" s="30" t="inlineStr">
-        <is>
-          <t>攻击高速目标时削弱概率大幅提升。</t>
-        </is>
-      </c>
-      <c r="E476" s="30" t="inlineStr">
-        <is>
-          <t>对方速度高于自身时，【碎灵】附加概率增加15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="477" ht="27" customHeight="1" s="57">
-      <c r="A477" s="42" t="n">
-        <v>2080002</v>
-      </c>
-      <c r="B477" s="3" t="inlineStr">
-        <is>
-          <t>碎空·凝元</t>
-        </is>
-      </c>
-      <c r="C477" s="30" t="inlineStr">
-        <is>
-          <t>成功削弱时同步为宠物附加法伤增益。</t>
-        </is>
-      </c>
-      <c r="E477" s="30" t="inlineStr">
-        <is>
-          <t>该技能每次成功附加【碎灵】时，为我方宠物法伤最高单位附加1层【凝元】</t>
-        </is>
-      </c>
-    </row>
     <row r="478" ht="27" customHeight="1" s="57">
       <c r="A478" s="42" t="n">
+        <v>2080001</v>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>碎空·穿透</t>
+        </is>
+      </c>
+      <c r="C478" s="30" t="inlineStr">
+        <is>
+          <t>攻击高速目标时削弱概率大幅提升。</t>
+        </is>
+      </c>
+      <c r="E478" s="30" t="inlineStr">
+        <is>
+          <t>对方速度高于自身时，【碎灵】附加概率增加15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="42" t="n">
+        <v>2080002</v>
+      </c>
+      <c r="B479" s="3" t="inlineStr">
+        <is>
+          <t>碎空·凝元</t>
+        </is>
+      </c>
+      <c r="C479" s="30" t="inlineStr">
+        <is>
+          <t>成功削弱时同步为宠物附加法伤增益。</t>
+        </is>
+      </c>
+      <c r="E479" s="30" t="inlineStr">
+        <is>
+          <t>该技能每次成功附加【碎灵】时，为我方宠物法伤最高单位附加1层【凝元】</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="27" customHeight="1" s="57">
+      <c r="A480" s="42" t="n">
         <v>2090001</v>
       </c>
-      <c r="B478" s="3" t="inlineStr">
+      <c r="B480" s="3" t="inlineStr">
         <is>
           <t>大风起·先声</t>
         </is>
       </c>
-      <c r="C478" s="30" t="inlineStr">
+      <c r="C480" s="30" t="inlineStr">
         <is>
           <t>作为狂风首个指令时法术伤害大幅提升。</t>
         </is>
       </c>
-      <c r="E478" s="30" t="inlineStr">
+      <c r="E480" s="30" t="inlineStr">
         <is>
           <t>【狂风】下首个指令为该技能时
 增加30%的法术伤害结果</t>
         </is>
       </c>
     </row>
-    <row r="479">
-      <c r="A479" s="42" t="n">
+    <row r="481">
+      <c r="A481" s="42" t="n">
         <v>2090002</v>
       </c>
-      <c r="B479" s="3" t="inlineStr">
+      <c r="B481" s="3" t="inlineStr">
         <is>
           <t>大风起·余怒</t>
         </is>
       </c>
-      <c r="C479" s="30" t="inlineStr">
+      <c r="C481" s="30" t="inlineStr">
         <is>
           <t>作为狂风第二指令时回复大量愤怒。</t>
         </is>
       </c>
-      <c r="E479" s="30" t="inlineStr">
+      <c r="E481" s="30" t="inlineStr">
         <is>
           <t>【狂风】下第二个指令为该技能时，回复20点愤怒</t>
         </is>
       </c>
     </row>
-    <row r="480" ht="27" customHeight="1" s="57">
-      <c r="A480" s="42" t="n">
+    <row r="482">
+      <c r="A482" s="42" t="n">
         <v>3010001</v>
       </c>
-      <c r="B480" s="3" t="inlineStr">
+      <c r="B482" s="3" t="inlineStr">
         <is>
           <t>灵泉·凝灵</t>
         </is>
       </c>
-      <c r="C480" s="30" t="inlineStr">
+      <c r="C482" s="30" t="inlineStr">
         <is>
           <t>积蓄灵泉的同时持续提升治疗暴击能力。</t>
         </is>
       </c>
-      <c r="E480" s="30" t="inlineStr">
+      <c r="E482" s="30" t="inlineStr">
         <is>
           <t>战斗中每累计获得2滴灵泉，获得1层【洗心】增益，
 【洗心】：增加自身1%治疗暴击，至多叠加10层</t>
         </is>
       </c>
     </row>
-    <row r="481">
-      <c r="A481" s="42" t="n">
-        <v>3010002</v>
-      </c>
-      <c r="B481" s="3" t="inlineStr">
-        <is>
-          <t>灵泉·护佑</t>
-        </is>
-      </c>
-      <c r="C481" s="30" t="inlineStr">
-        <is>
-          <t>灵泉治疗时有概率为目标附加法术减免。</t>
-        </is>
-      </c>
-      <c r="E481" s="30" t="inlineStr">
-        <is>
-          <t>灵泉治疗时40%概率附加1层【灵护】</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" s="42" t="n">
-        <v>3020001</v>
-      </c>
-      <c r="B482" s="3" t="inlineStr">
-        <is>
-          <t>甘露·连弹</t>
-        </is>
-      </c>
-      <c r="C482" s="30" t="inlineStr">
-        <is>
-          <t>甘露弹射次数增加，覆盖更多队友。</t>
-        </is>
-      </c>
-      <c r="E482" s="30" t="inlineStr">
-        <is>
-          <t>弹射次数+1，对第四名目标回复50%治疗结果</t>
-        </is>
-      </c>
-    </row>
     <row r="483" ht="40.5" customHeight="1" s="57">
       <c r="A483" s="42" t="n">
+        <v>3010002</v>
+      </c>
+      <c r="B483" s="3" t="inlineStr">
+        <is>
+          <t>灵泉·护佑</t>
+        </is>
+      </c>
+      <c r="C483" s="30" t="inlineStr">
+        <is>
+          <t>灵泉治疗时有概率为目标附加法术减免。</t>
+        </is>
+      </c>
+      <c r="E483" s="30" t="inlineStr">
+        <is>
+          <t>灵泉治疗时40%概率附加1层【灵护】</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="42" t="n">
+        <v>3020001</v>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>甘露·连弹</t>
+        </is>
+      </c>
+      <c r="C484" s="30" t="inlineStr">
+        <is>
+          <t>甘露弹射次数增加，覆盖更多队友。</t>
+        </is>
+      </c>
+      <c r="E484" s="30" t="inlineStr">
+        <is>
+          <t>弹射次数+1，对第四名目标回复50%治疗结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="40.5" customHeight="1" s="57">
+      <c r="A485" s="42" t="n">
         <v>3020002</v>
       </c>
-      <c r="B483" s="3" t="inlineStr">
+      <c r="B485" s="3" t="inlineStr">
         <is>
           <t>甘露·滋养</t>
         </is>
       </c>
-      <c r="C483" s="30" t="inlineStr">
+      <c r="C485" s="30" t="inlineStr">
         <is>
           <t>每次弹射额外回复目标一定比例的最大生命。</t>
         </is>
       </c>
-      <c r="E483" s="30" t="inlineStr">
+      <c r="E485" s="30" t="inlineStr">
         <is>
           <t>该技能增加目标8%/6%/4%最大生命值的回复
 额外的治疗回复效果不超过目标单位的等级*境界倍率*10</t>
         </is>
       </c>
     </row>
-    <row r="484">
-      <c r="A484" s="42" t="n">
+    <row r="486" ht="40.5" customHeight="1" s="57">
+      <c r="A486" s="42" t="n">
         <v>3030001</v>
       </c>
-      <c r="B484" s="3" t="inlineStr">
+      <c r="B486" s="3" t="inlineStr">
         <is>
           <t>沧浪·夺泉</t>
         </is>
       </c>
-      <c r="C484" s="30" t="inlineStr">
+      <c r="C486" s="30" t="inlineStr">
         <is>
           <t>击败敌方时必定获得灵泉。</t>
         </is>
       </c>
-      <c r="E484" s="30" t="inlineStr">
+      <c r="E486" s="30" t="inlineStr">
         <is>
           <t>该技能造成击败时，额外获得1滴灵泉</t>
         </is>
       </c>
     </row>
-    <row r="485" ht="40.5" customHeight="1" s="57">
-      <c r="A485" s="42" t="n">
+    <row r="487">
+      <c r="A487" s="42" t="n">
         <v>3030002</v>
       </c>
-      <c r="B485" s="3" t="inlineStr">
+      <c r="B487" s="3" t="inlineStr">
         <is>
           <t>沧浪·暗涌</t>
         </is>
       </c>
-      <c r="C485" s="30" t="inlineStr">
+      <c r="C487" s="30" t="inlineStr">
         <is>
           <t>每回合未使用该技能时获得灵泉的概率持续增长。</t>
         </is>
       </c>
-      <c r="E485" s="30" t="inlineStr">
+      <c r="E487" s="30" t="inlineStr">
         <is>
           <t>未使用该技能时，每回合结束时增加沧浪20%获得灵泉的概率
 可叠加至多4层，释放后重置</t>
         </is>
       </c>
     </row>
-    <row r="486" ht="40.5" customHeight="1" s="57">
-      <c r="A486" s="42" t="n">
+    <row r="488">
+      <c r="A488" s="42" t="n">
         <v>3040001</v>
       </c>
-      <c r="B486" s="3" t="inlineStr">
+      <c r="B488" s="3" t="inlineStr">
         <is>
           <t>护灵诀·固本</t>
         </is>
       </c>
-      <c r="C486" s="30" t="inlineStr">
+      <c r="C488" s="30" t="inlineStr">
         <is>
           <t>首目标额外获得法术抗暴能力提升。</t>
         </is>
       </c>
-      <c r="E486" s="30" t="inlineStr">
+      <c r="E488" s="30" t="inlineStr">
         <is>
           <t>对首目标额外附加1层【固本】
 【固本】：提升5%法术抗暴并降低20%的法术被爆伤结果</t>
         </is>
       </c>
     </row>
-    <row r="487">
-      <c r="A487" s="42" t="n">
-        <v>3040002</v>
-      </c>
-      <c r="B487" s="3" t="inlineStr">
-        <is>
-          <t>护灵诀·迎新</t>
-        </is>
-      </c>
-      <c r="C487" s="30" t="inlineStr">
-        <is>
-          <t>召唤宠物出场时自动附加灵护。</t>
-        </is>
-      </c>
-      <c r="E487" s="30" t="inlineStr">
-        <is>
-          <t>我方召唤宠物时，为其附加1层【灵护】</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" s="42" t="n">
-        <v>3050001</v>
-      </c>
-      <c r="B488" s="3" t="inlineStr">
-        <is>
-          <t>潮汐·归泉</t>
-        </is>
-      </c>
-      <c r="C488" s="30" t="inlineStr">
-        <is>
-          <t>友方倒地或离场时有概率获得灵泉。</t>
-        </is>
-      </c>
-      <c r="E488" s="30" t="inlineStr">
-        <is>
-          <t>己方单位被击败或离场时，30%概率获得1滴灵泉。</t>
-        </is>
-      </c>
-    </row>
     <row r="489" ht="27" customHeight="1" s="57">
       <c r="A489" s="42" t="n">
-        <v>3050002</v>
+        <v>3040002</v>
       </c>
       <c r="B489" s="3" t="inlineStr">
         <is>
-          <t>潮汐·涌泉</t>
+          <t>护灵诀·迎新</t>
         </is>
       </c>
       <c r="C489" s="30" t="inlineStr">
         <is>
-          <t>灵泉容量扩大，且每次灵泉治疗量增加。</t>
+          <t>召唤宠物出场时自动附加灵护。</t>
         </is>
       </c>
       <c r="E489" s="30" t="inlineStr">
         <is>
-          <t>灵泉存储上限+1，增加目标最大生命5%的治疗量（合计8%）</t>
+          <t>我方召唤宠物时，为其附加1层【灵护】</t>
         </is>
       </c>
     </row>
     <row r="490" ht="27" customHeight="1" s="57">
       <c r="A490" s="42" t="n">
-        <v>3060001</v>
+        <v>3050001</v>
       </c>
       <c r="B490" s="3" t="inlineStr">
         <is>
-          <t>明镜止水·厚报</t>
+          <t>潮汐·归泉</t>
         </is>
       </c>
       <c r="C490" s="30" t="inlineStr">
         <is>
-          <t>友方气血极低时水镜回复量大幅提升。</t>
+          <t>友方倒地或离场时有概率获得灵泉。</t>
         </is>
       </c>
       <c r="E490" s="30" t="inlineStr">
         <is>
-          <t>受击后气血小于最大气血10%时，回复所受伤害70%的气血</t>
+          <t>己方单位被击败或离场时，30%概率获得1滴灵泉。</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="42" t="n">
-        <v>3060002</v>
+        <v>3050002</v>
       </c>
       <c r="B491" s="3" t="inlineStr">
         <is>
-          <t>明镜止水·延时</t>
+          <t>潮汐·涌泉</t>
         </is>
       </c>
       <c r="C491" s="30" t="inlineStr">
         <is>
-          <t>水镜持续时间延长。</t>
+          <t>灵泉容量扩大，且每次灵泉治疗量增加。</t>
         </is>
       </c>
       <c r="E491" s="30" t="inlineStr">
         <is>
-          <t>【水镜】持续时间增加1回合</t>
+          <t>灵泉存储上限+1，增加目标最大生命5%的治疗量（合计8%）</t>
         </is>
       </c>
     </row>
     <row r="492" ht="40.5" customHeight="1" s="57">
       <c r="A492" s="42" t="n">
+        <v>3060001</v>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>明镜止水·厚报</t>
+        </is>
+      </c>
+      <c r="C492" s="30" t="inlineStr">
+        <is>
+          <t>友方气血极低时水镜回复量大幅提升。</t>
+        </is>
+      </c>
+      <c r="E492" s="30" t="inlineStr">
+        <is>
+          <t>受击后气血小于最大气血10%时，回复所受伤害70%的气血</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="27" customHeight="1" s="57">
+      <c r="A493" s="42" t="n">
+        <v>3060002</v>
+      </c>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>明镜止水·延时</t>
+        </is>
+      </c>
+      <c r="C493" s="30" t="inlineStr">
+        <is>
+          <t>水镜持续时间延长。</t>
+        </is>
+      </c>
+      <c r="E493" s="30" t="inlineStr">
+        <is>
+          <t>【水镜】持续时间增加1回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="27" customHeight="1" s="57">
+      <c r="A494" s="42" t="n">
         <v>3070001</v>
       </c>
-      <c r="B492" s="3" t="inlineStr">
+      <c r="B494" s="3" t="inlineStr">
         <is>
           <t>渡生·泉愈</t>
         </is>
       </c>
-      <c r="C492" s="30" t="inlineStr">
+      <c r="C494" s="30" t="inlineStr">
         <is>
           <t>有灵泉时消耗一滴额外触发灵泉治疗。</t>
         </is>
       </c>
-      <c r="E492" s="30" t="inlineStr">
+      <c r="E494" s="30" t="inlineStr">
         <is>
           <t>存在灵泉时，消耗1点灵泉，复活时立刻触发1次灵泉回复
 同时额外回复相同气血的内伤</t>
         </is>
       </c>
     </row>
-    <row r="493" ht="27" customHeight="1" s="57">
-      <c r="A493" s="42" t="n">
-        <v>3070002</v>
-      </c>
-      <c r="B493" s="3" t="inlineStr">
-        <is>
-          <t>渡生·净化</t>
-        </is>
-      </c>
-      <c r="C493" s="30" t="inlineStr">
-        <is>
-          <t>复活后为目标转化一个减益为增益。</t>
-        </is>
-      </c>
-      <c r="E493" s="30" t="inlineStr">
-        <is>
-          <t>复活后，随机转化1个可净化的非封印减益变为1个随机门派增益</t>
-        </is>
-      </c>
-    </row>
-    <row r="494" ht="27" customHeight="1" s="57">
-      <c r="A494" s="42" t="n">
-        <v>3080001</v>
-      </c>
-      <c r="B494" s="3" t="inlineStr">
-        <is>
-          <t>断脉·借力</t>
-        </is>
-      </c>
-      <c r="C494" s="30" t="inlineStr">
-        <is>
-          <t>我方法术攻击被断脉的目标时伤害提升。</t>
-        </is>
-      </c>
-      <c r="E494" s="30" t="inlineStr">
-        <is>
-          <t>我方召唤灵法术攻击【断脉】单位时，法术伤害结果+10%</t>
-        </is>
-      </c>
-    </row>
     <row r="495" ht="27" customHeight="1" s="57">
       <c r="A495" s="42" t="n">
-        <v>3080002</v>
+        <v>3070002</v>
       </c>
       <c r="B495" s="3" t="inlineStr">
         <is>
-          <t>断脉·传脉</t>
+          <t>渡生·净化</t>
         </is>
       </c>
       <c r="C495" s="30" t="inlineStr">
         <is>
-          <t>敌方宠物满层断脉离场时会传染给法伤最高的敌方。</t>
+          <t>复活后为目标转化一个减益为增益。</t>
         </is>
       </c>
       <c r="E495" s="30" t="inlineStr">
         <is>
-          <t>对方宠物单位3层【断脉】离场时，给对方法伤最高单位附加1层【断脉】</t>
+          <t>复活后，随机转化1个可净化的非封印减益变为1个随机门派增益</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="42" t="n">
-        <v>3090001</v>
+        <v>3080001</v>
       </c>
       <c r="B496" s="3" t="inlineStr">
         <is>
-          <t>海纳百川·补泉</t>
+          <t>断脉·借力</t>
         </is>
       </c>
       <c r="C496" s="30" t="inlineStr">
         <is>
-          <t>释放后立即获得灵泉。</t>
+          <t>我方法术攻击被断脉的目标时伤害提升。</t>
         </is>
       </c>
       <c r="E496" s="30" t="inlineStr">
         <is>
-          <t>释放后，获得2滴灵泉</t>
+          <t>我方召唤灵法术攻击【断脉】单位时，法术伤害结果+10%</t>
         </is>
       </c>
     </row>
     <row r="497" ht="27" customHeight="1" s="57">
       <c r="A497" s="42" t="n">
-        <v>3090002</v>
+        <v>3080002</v>
       </c>
       <c r="B497" s="3" t="inlineStr">
         <is>
-          <t>海纳百川·分润</t>
+          <t>断脉·传脉</t>
         </is>
       </c>
       <c r="C497" s="30" t="inlineStr">
         <is>
-          <t>共患期间友方受治疗时将部分效果分配给全队。</t>
+          <t>敌方宠物满层断脉离场时会传染给法伤最高的敌方。</t>
         </is>
       </c>
       <c r="E497" s="30" t="inlineStr">
         <is>
-          <t>【共患】期间，任意友方受到治疗时，将治疗结果的 10% 额外分配给其他存活的【共患】单位</t>
+          <t>对方宠物单位3层【断脉】离场时，给对方法伤最高单位附加1层【断脉】</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="42" t="n">
-        <v>4010001</v>
+        <v>3090001</v>
       </c>
       <c r="B498" s="3" t="inlineStr">
         <is>
-          <t>画符·印痕</t>
+          <t>海纳百川·补泉</t>
         </is>
       </c>
       <c r="C498" s="30" t="inlineStr">
         <is>
-          <t>释放被强化的封印技能后封印命中提升。</t>
+          <t>释放后立即获得灵泉。</t>
         </is>
       </c>
       <c r="E498" s="30" t="inlineStr">
         <is>
-          <t>释放强化后的封印技能时，增加3%的封印命中</t>
+          <t>释放后，获得2滴灵泉</t>
         </is>
       </c>
     </row>
     <row r="499" ht="27" customHeight="1" s="57">
       <c r="A499" s="42" t="n">
-        <v>4010002</v>
+        <v>3090002</v>
       </c>
       <c r="B499" s="3" t="inlineStr">
         <is>
-          <t>画符·金甲</t>
+          <t>海纳百川·分润</t>
         </is>
       </c>
       <c r="C499" s="30" t="inlineStr">
         <is>
-          <t>释放被强化的非封印技能后获得物法减免提升。</t>
+          <t>共患期间友方受治疗时将部分效果分配给全队。</t>
         </is>
       </c>
       <c r="E499" s="30" t="inlineStr">
         <is>
-          <t>释放强化后的非封印技能时，本回合增加5%的物法减免</t>
+          <t>【共患】期间，任意友方受到治疗时，将治疗结果的 10% 额外分配给其他存活的【共患】单位</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="42" t="n">
-        <v>4020001</v>
+        <v>4010001</v>
       </c>
       <c r="B500" s="3" t="inlineStr">
         <is>
-          <t>失心·抢先</t>
+          <t>画符·印痕</t>
         </is>
       </c>
       <c r="C500" s="30" t="inlineStr">
         <is>
-          <t>速度高于目标时封印命中上限提升，先手制敌。</t>
+          <t>释放被强化的封印技能后封印命中提升。</t>
         </is>
       </c>
       <c r="E500" s="30" t="inlineStr">
         <is>
-          <t>自身速度高于目标时，封印命中上限额外增加5%</t>
+          <t>释放强化后的封印技能时，增加3%的封印命中</t>
         </is>
       </c>
     </row>
     <row r="501" ht="27" customHeight="1" s="57">
       <c r="A501" s="42" t="n">
-        <v>4020002</v>
+        <v>4010002</v>
       </c>
       <c r="B501" s="3" t="inlineStr">
         <is>
-          <t>失心·追击</t>
+          <t>画符·金甲</t>
         </is>
       </c>
       <c r="C501" s="30" t="inlineStr">
         <is>
-          <t>封印命中时有概率使宠物追击目标。</t>
+          <t>释放被强化的非封印技能后获得物法减免提升。</t>
         </is>
       </c>
       <c r="E501" s="30" t="inlineStr">
         <is>
-          <t>封印命中时，25%概率己方随机宠物对该目标追击 1 次，优先使用技能</t>
+          <t>释放强化后的非封印技能时，本回合增加5%的物法减免</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="42" t="n">
-        <v>4030001</v>
+        <v>4020001</v>
       </c>
       <c r="B502" s="3" t="inlineStr">
         <is>
-          <t>天雷·克兽</t>
+          <t>失心·抢先</t>
         </is>
       </c>
       <c r="C502" s="30" t="inlineStr">
         <is>
-          <t>攻击宠物时封禁概率额外提升。</t>
+          <t>速度高于目标时封印命中上限提升，先手制敌。</t>
         </is>
       </c>
       <c r="E502" s="30" t="inlineStr">
         <is>
-          <t>首目标为非人物单位时，封技概率额外增加 5%</t>
+          <t>自身速度高于目标时，封印命中上限额外增加5%</t>
         </is>
       </c>
     </row>
     <row r="503" ht="40.5" customHeight="1" s="57">
       <c r="A503" s="42" t="n">
+        <v>4020002</v>
+      </c>
+      <c r="B503" s="3" t="inlineStr">
+        <is>
+          <t>失心·追击</t>
+        </is>
+      </c>
+      <c r="C503" s="30" t="inlineStr">
+        <is>
+          <t>封印命中时有概率使宠物追击目标。</t>
+        </is>
+      </c>
+      <c r="E503" s="30" t="inlineStr">
+        <is>
+          <t>封印命中时，25%概率己方随机宠物对该目标追击 1 次，优先使用技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="40.5" customHeight="1" s="57">
+      <c r="A504" s="42" t="n">
+        <v>4030001</v>
+      </c>
+      <c r="B504" s="3" t="inlineStr">
+        <is>
+          <t>天雷·克兽</t>
+        </is>
+      </c>
+      <c r="C504" s="30" t="inlineStr">
+        <is>
+          <t>攻击宠物时封禁概率额外提升。</t>
+        </is>
+      </c>
+      <c r="E504" s="30" t="inlineStr">
+        <is>
+          <t>首目标为非人物单位时，封技概率额外增加 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="42" t="n">
         <v>4030002</v>
       </c>
-      <c r="B503" s="3" t="inlineStr">
+      <c r="B505" s="3" t="inlineStr">
         <is>
           <t>天雷·连击</t>
         </is>
       </c>
-      <c r="C503" s="30" t="inlineStr">
+      <c r="C505" s="30" t="inlineStr">
         <is>
           <t>首目标处于封印状态时自动追击另一个随机目标。</t>
         </is>
       </c>
-      <c r="E503" s="30" t="inlineStr">
+      <c r="E505" s="30" t="inlineStr">
         <is>
           <t>天雷对首目标造成伤害时，若目标当前处于任意封印状态，
 以 30% 伤害结果追击 1 次随机目标</t>
         </is>
       </c>
     </row>
-    <row r="504" ht="40.5" customHeight="1" s="57">
-      <c r="A504" s="42" t="n">
+    <row r="506">
+      <c r="A506" s="42" t="n">
         <v>4040001</v>
       </c>
-      <c r="B504" s="3" t="inlineStr">
+      <c r="B506" s="3" t="inlineStr">
         <is>
           <t>定身术·感染</t>
         </is>
       </c>
-      <c r="C504" s="30" t="inlineStr">
+      <c r="C506" s="30" t="inlineStr">
         <is>
           <t>击败被缴械/定身的宠物时有概率传染给其主人。</t>
         </is>
       </c>
-      <c r="E504" s="30" t="inlineStr">
+      <c r="E506" s="30" t="inlineStr">
         <is>
           <t>己方单体技能击败【缴械】或【定身】的宠物目标时，以30%概率传染到其主人上
 传染（继承效果与剩余回合数）</t>
         </is>
       </c>
     </row>
-    <row r="505">
-      <c r="A505" s="42" t="n">
-        <v>4040002</v>
-      </c>
-      <c r="B505" s="3" t="inlineStr">
-        <is>
-          <t>定身术·回怒</t>
-        </is>
-      </c>
-      <c r="C505" s="30" t="inlineStr">
-        <is>
-          <t>命中时回复愤怒。</t>
-        </is>
-      </c>
-      <c r="E505" s="30" t="inlineStr">
-        <is>
-          <t>该技能命中时，回复自身5点愤怒</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" s="42" t="n">
-        <v>4050001</v>
-      </c>
-      <c r="B506" s="3" t="inlineStr">
-        <is>
-          <t>律令·三符</t>
-        </is>
-      </c>
-      <c r="C506" s="30" t="inlineStr">
-        <is>
-          <t>有概率额外获得更多符箓。</t>
-        </is>
-      </c>
-      <c r="E506" s="30" t="inlineStr">
-        <is>
-          <t>30%概率获取符箓时额外增加1个随机符箓获取</t>
-        </is>
-      </c>
-    </row>
     <row r="507">
       <c r="A507" s="42" t="n">
-        <v>4050002</v>
+        <v>4040002</v>
       </c>
       <c r="B507" s="3" t="inlineStr">
         <is>
-          <t>律令·选符</t>
+          <t>定身术·回怒</t>
         </is>
       </c>
       <c r="C507" s="30" t="inlineStr">
         <is>
-          <t>符箓必定至少强化一个封印技能。</t>
+          <t>命中时回复愤怒。</t>
         </is>
       </c>
       <c r="E507" s="30" t="inlineStr">
         <is>
-          <t>符箓强化时，强化至少1个封印技能</t>
+          <t>该技能命中时，回复自身5点愤怒</t>
         </is>
       </c>
     </row>
     <row r="508" ht="27" customHeight="1" s="57">
       <c r="A508" s="42" t="n">
+        <v>4050001</v>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>律令·三符</t>
+        </is>
+      </c>
+      <c r="C508" s="30" t="inlineStr">
+        <is>
+          <t>有概率额外获得更多符箓。</t>
+        </is>
+      </c>
+      <c r="E508" s="30" t="inlineStr">
+        <is>
+          <t>30%概率获取符箓时额外增加1个随机符箓获取</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="40.5" customHeight="1" s="57">
+      <c r="A509" s="42" t="n">
+        <v>4050002</v>
+      </c>
+      <c r="B509" s="3" t="inlineStr">
+        <is>
+          <t>律令·选符</t>
+        </is>
+      </c>
+      <c r="C509" s="30" t="inlineStr">
+        <is>
+          <t>符箓必定至少强化一个封印技能。</t>
+        </is>
+      </c>
+      <c r="E509" s="30" t="inlineStr">
+        <is>
+          <t>符箓强化时，强化至少1个封印技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="42" t="n">
         <v>4060001</v>
       </c>
-      <c r="B508" s="3" t="inlineStr">
+      <c r="B510" s="3" t="inlineStr">
         <is>
           <t>斗转·增效</t>
         </is>
       </c>
-      <c r="C508" s="30" t="inlineStr">
+      <c r="C510" s="30" t="inlineStr">
         <is>
           <t>释放后自身封印命中持续提升。</t>
         </is>
       </c>
-      <c r="E508" s="30" t="inlineStr">
+      <c r="E510" s="30" t="inlineStr">
         <is>
           <t>释放后自身附加【斗转】增益
 【斗转】：获得4回合5%封印命中</t>
         </is>
       </c>
     </row>
-    <row r="509" ht="40.5" customHeight="1" s="57">
-      <c r="A509" s="42" t="n">
+    <row r="511" ht="27" customHeight="1" s="57">
+      <c r="A511" s="42" t="n">
         <v>4060002</v>
       </c>
-      <c r="B509" s="3" t="inlineStr">
+      <c r="B511" s="3" t="inlineStr">
         <is>
           <t>斗转·碎灵</t>
         </is>
       </c>
-      <c r="C509" s="30" t="inlineStr">
+      <c r="C511" s="30" t="inlineStr">
         <is>
           <t>斗转期间目标攻击自身后会被附加法防削弱。</t>
         </is>
       </c>
-      <c r="E509" s="30" t="inlineStr">
+      <c r="E511" s="30" t="inlineStr">
         <is>
           <t>斗转期间，目标每次攻击自身后，为其附加1层【碎灵】
 （1次出手算1次结算）</t>
         </is>
       </c>
     </row>
-    <row r="510">
-      <c r="A510" s="42" t="n">
-        <v>4070001</v>
-      </c>
-      <c r="B510" s="3" t="inlineStr">
-        <is>
-          <t>金光咒·再生</t>
-        </is>
-      </c>
-      <c r="C510" s="30" t="inlineStr">
-        <is>
-          <t>被复活时有概率自动获得金光咒效果。</t>
-        </is>
-      </c>
-      <c r="E510" s="30" t="inlineStr">
-        <is>
-          <t>被复活时，30%概率为自身附加【金光】技能</t>
-        </is>
-      </c>
-    </row>
-    <row r="511" ht="27" customHeight="1" s="57">
-      <c r="A511" s="42" t="n">
-        <v>4070002</v>
-      </c>
-      <c r="B511" s="3" t="inlineStr">
-        <is>
-          <t>金光咒·危照</t>
-        </is>
-      </c>
-      <c r="C511" s="30" t="inlineStr">
-        <is>
-          <t>内伤严重时金光咒获得强化的概率大幅提升，危难时金光护身。</t>
-        </is>
-      </c>
-      <c r="E511" s="30" t="inlineStr">
-        <is>
-          <t>自身内伤超过30%时，该技能获得符箓强化概率增加至50%</t>
-        </is>
-      </c>
-    </row>
     <row r="512" ht="27" customHeight="1" s="57">
       <c r="A512" s="42" t="n">
-        <v>4080001</v>
+        <v>4070001</v>
       </c>
       <c r="B512" s="3" t="inlineStr">
         <is>
-          <t>断念·制速</t>
+          <t>金光咒·再生</t>
         </is>
       </c>
       <c r="C512" s="30" t="inlineStr">
         <is>
-          <t>全场最快时命中率与上限大幅提升。</t>
+          <t>被复活时有概率自动获得金光咒效果。</t>
         </is>
       </c>
       <c r="E512" s="30" t="inlineStr">
         <is>
-          <t>自身速度为全场1速时，增加该技能的命中率与上限10%</t>
+          <t>被复活时，30%概率为自身附加【金光】技能</t>
         </is>
       </c>
     </row>
     <row r="513" ht="27" customHeight="1" s="57">
       <c r="A513" s="42" t="n">
-        <v>4080002</v>
+        <v>4070002</v>
       </c>
       <c r="B513" s="3" t="inlineStr">
         <is>
-          <t>断念·深化</t>
+          <t>金光咒·危照</t>
         </is>
       </c>
       <c r="C513" s="30" t="inlineStr">
         <is>
-          <t>成功延长多个减益时额外多延长一回合。</t>
+          <t>内伤严重时金光咒获得强化的概率大幅提升，危难时金光护身。</t>
         </is>
       </c>
       <c r="E513" s="30" t="inlineStr">
         <is>
-          <t>成功延长对方4个及以上的减益时，额外延长1回合减益效果</t>
+          <t>自身内伤超过30%时，该技能获得符箓强化概率增加至50%</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="42" t="n">
-        <v>4090001</v>
+        <v>4080001</v>
       </c>
       <c r="B514" s="3" t="inlineStr">
         <is>
-          <t>夺魄·不休</t>
+          <t>断念·制速</t>
         </is>
       </c>
       <c r="C514" s="30" t="inlineStr">
         <is>
-          <t>释放后不进入休息，但混乱命中率降低。</t>
+          <t>全场最快时命中率与上限大幅提升。</t>
         </is>
       </c>
       <c r="E514" s="30" t="inlineStr">
         <is>
-          <t>释放后自身不会休息，但混乱命中率为50%</t>
+          <t>自身速度为全场1速时，增加该技能的命中率与上限10%</t>
         </is>
       </c>
     </row>
     <row r="515" ht="54" customHeight="1" s="57">
       <c r="A515" s="42" t="n">
+        <v>4080002</v>
+      </c>
+      <c r="B515" s="3" t="inlineStr">
+        <is>
+          <t>断念·深化</t>
+        </is>
+      </c>
+      <c r="C515" s="30" t="inlineStr">
+        <is>
+          <t>成功延长多个减益时额外多延长一回合。</t>
+        </is>
+      </c>
+      <c r="E515" s="30" t="inlineStr">
+        <is>
+          <t>成功延长对方4个及以上的减益时，额外延长1回合减益效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="42" t="n">
+        <v>4090001</v>
+      </c>
+      <c r="B516" s="3" t="inlineStr">
+        <is>
+          <t>夺魄·不休</t>
+        </is>
+      </c>
+      <c r="C516" s="30" t="inlineStr">
+        <is>
+          <t>释放后不进入休息，但混乱命中率降低。</t>
+        </is>
+      </c>
+      <c r="E516" s="30" t="inlineStr">
+        <is>
+          <t>释放后自身不会休息，但混乱命中率为50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="81" customHeight="1" s="57">
+      <c r="A517" s="42" t="n">
         <v>4090002</v>
       </c>
-      <c r="B515" s="3" t="inlineStr">
+      <c r="B517" s="3" t="inlineStr">
         <is>
           <t>夺魄·反噬</t>
         </is>
       </c>
-      <c r="C515" s="30" t="inlineStr">
+      <c r="C517" s="30" t="inlineStr">
         <is>
           <t>混乱目标攻击我方时不造成伤害反而治疗受击者；攻击敌方时伤害增加。</t>
         </is>
       </c>
-      <c r="E515" s="30" t="inlineStr">
+      <c r="E517" s="30" t="inlineStr">
         <is>
           <t>混乱目标对我方单位造成伤害时，不会造成伤害并回复受击单位造成伤害30% 的气血
 混乱目标对敌方单位造成伤害时，增加30%伤害结果</t>
         </is>
       </c>
     </row>
-    <row r="516">
-      <c r="A516" s="42" t="n">
+    <row r="518">
+      <c r="A518" s="42" t="n">
         <v>5010001</v>
       </c>
-      <c r="B516" s="3" t="inlineStr">
+      <c r="B518" s="3" t="inlineStr">
         <is>
           <t>御兽·先发</t>
         </is>
       </c>
-      <c r="C516" s="30" t="inlineStr">
+      <c r="C518" s="30" t="inlineStr">
         <is>
           <t>战斗首回合结束时立即获得1个灵兽技能</t>
         </is>
       </c>
-      <c r="E516" s="30" t="inlineStr">
+      <c r="E518" s="30" t="inlineStr">
         <is>
           <t>首回合结束时，获得1个额外的宠物技能</t>
         </is>
       </c>
     </row>
-    <row r="517" ht="81" customHeight="1" s="57">
-      <c r="A517" s="42" t="n">
+    <row r="519">
+      <c r="A519" s="42" t="n">
         <v>5010002</v>
       </c>
-      <c r="B517" s="3" t="inlineStr">
+      <c r="B519" s="3" t="inlineStr">
         <is>
           <t>御兽·积威</t>
         </is>
       </c>
-      <c r="C517" s="30" t="inlineStr">
+      <c r="C519" s="30" t="inlineStr">
         <is>
           <t>获得灵兽技能时，自身物理伤害结果增加</t>
         </is>
       </c>
-      <c r="E517" s="30" t="inlineStr">
+      <c r="E519" s="30" t="inlineStr">
         <is>
           <t>每获得过1个宠物被动技能+1%物理伤害结果(至多10层)
 获得宠物技能石，增加1层BUFF【积威】（BUFFID 501），
@@ -15350,141 +15391,141 @@
         </is>
       </c>
     </row>
-    <row r="518">
-      <c r="A518" s="42" t="n">
-        <v>5020001</v>
-      </c>
-      <c r="B518" s="3" t="inlineStr">
-        <is>
-          <t>裂地枪·蓄力</t>
-        </is>
-      </c>
-      <c r="C518" s="30" t="inlineStr">
-        <is>
-          <t>持有的灵兽技能越多，裂地枪伤害越高。</t>
-        </is>
-      </c>
-      <c r="E518" s="30" t="inlineStr">
-        <is>
-          <t>每持有1个宠物被动技能，本技能+5%技能伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" s="42" t="n">
-        <v>5020002</v>
-      </c>
-      <c r="B519" s="3" t="inlineStr">
-        <is>
-          <t>裂地枪·广域</t>
-        </is>
-      </c>
-      <c r="C519" s="30" t="inlineStr">
-        <is>
-          <t>灵兽技能充足时攻击范围扩大，覆盖更多目标。</t>
-        </is>
-      </c>
-      <c r="E519" s="30" t="inlineStr">
-        <is>
-          <t>拥有宠物被动技能≥3时，该技能攻击目标+1</t>
-        </is>
-      </c>
-    </row>
     <row r="520" ht="40.5" customHeight="1" s="57">
       <c r="A520" s="42" t="n">
-        <v>5030001</v>
+        <v>5020001</v>
       </c>
       <c r="B520" s="3" t="inlineStr">
         <is>
-          <t>啸天·压制</t>
+          <t>裂地枪·蓄力</t>
         </is>
       </c>
       <c r="C520" s="30" t="inlineStr">
         <is>
-          <t>攻击速度高于自身的目标时伤害大幅提升。</t>
+          <t>持有的灵兽技能越多，裂地枪伤害越高。</t>
         </is>
       </c>
       <c r="E520" s="30" t="inlineStr">
         <is>
-          <t>目标速度高与自身时，该技能伤害结果增加30%</t>
+          <t>每持有1个宠物被动技能，本技能+5%技能伤害</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="42" t="n">
-        <v>5030002</v>
+        <v>5020002</v>
       </c>
       <c r="B521" s="3" t="inlineStr">
         <is>
-          <t>啸天·夺技</t>
+          <t>裂地枪·广域</t>
         </is>
       </c>
       <c r="C521" s="30" t="inlineStr">
         <is>
-          <t>击败宠物时获得灵兽技能的概率大幅提升。</t>
+          <t>灵兽技能充足时攻击范围扩大，覆盖更多目标。</t>
         </is>
       </c>
       <c r="E521" s="30" t="inlineStr">
         <is>
-          <t>击败宠物+50%获技能，优先该宠物技能</t>
+          <t>拥有宠物被动技能≥3时，该技能攻击目标+1</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="42" t="n">
-        <v>5040001</v>
+        <v>5030001</v>
       </c>
       <c r="B522" s="3" t="inlineStr">
         <is>
-          <t>共鸣·同化</t>
+          <t>啸天·压制</t>
         </is>
       </c>
       <c r="C522" s="30" t="inlineStr">
         <is>
-          <t>共鸣宠物击败敌方时，自身获得其一个宠物被动技能。</t>
+          <t>攻击速度高于自身的目标时伤害大幅提升。</t>
         </is>
       </c>
       <c r="E522" s="30" t="inlineStr">
         <is>
-          <t>共鸣宠物击败时，自身获得其一个可获得的宠物被动</t>
+          <t>目标速度高与自身时，该技能伤害结果增加30%</t>
         </is>
       </c>
     </row>
     <row r="523" ht="27" customHeight="1" s="57">
       <c r="A523" s="42" t="n">
-        <v>5040002</v>
+        <v>5030002</v>
       </c>
       <c r="B523" s="3" t="inlineStr">
         <is>
-          <t>共鸣·通感</t>
+          <t>啸天·夺技</t>
         </is>
       </c>
       <c r="C523" s="30" t="inlineStr">
         <is>
-          <t>建立共鸣时，自身获得共鸣宠物的一个技能。</t>
+          <t>击败宠物时获得灵兽技能的概率大幅提升。</t>
         </is>
       </c>
       <c r="E523" s="30" t="inlineStr">
         <is>
-          <t>赋予共鸣时，自身获得其一个可获得的宠物被动</t>
+          <t>击败宠物+50%获技能，优先该宠物技能</t>
         </is>
       </c>
     </row>
     <row r="524" ht="94.5" customHeight="1" s="57">
       <c r="A524" s="42" t="n">
+        <v>5040001</v>
+      </c>
+      <c r="B524" s="3" t="inlineStr">
+        <is>
+          <t>共鸣·同化</t>
+        </is>
+      </c>
+      <c r="C524" s="30" t="inlineStr">
+        <is>
+          <t>共鸣宠物击败敌方时，自身获得其一个宠物被动技能。</t>
+        </is>
+      </c>
+      <c r="E524" s="30" t="inlineStr">
+        <is>
+          <t>共鸣宠物击败时，自身获得其一个可获得的宠物被动</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="42" t="n">
+        <v>5040002</v>
+      </c>
+      <c r="B525" s="3" t="inlineStr">
+        <is>
+          <t>共鸣·通感</t>
+        </is>
+      </c>
+      <c r="C525" s="30" t="inlineStr">
+        <is>
+          <t>建立共鸣时，自身获得共鸣宠物的一个技能。</t>
+        </is>
+      </c>
+      <c r="E525" s="30" t="inlineStr">
+        <is>
+          <t>赋予共鸣时，自身获得其一个可获得的宠物被动</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="42" t="n">
         <v>5050001</v>
       </c>
-      <c r="B524" s="3" t="inlineStr">
+      <c r="B526" s="3" t="inlineStr">
         <is>
           <t>龙脉·精进</t>
         </is>
       </c>
-      <c r="C524" s="30" t="inlineStr">
+      <c r="C526" s="30" t="inlineStr">
         <is>
           <t>获得技能时更易获得已有技能，加速技能升级。</t>
         </is>
       </c>
-      <c r="E524" s="30" t="inlineStr">
+      <c r="E526" s="30" t="inlineStr">
         <is>
           <t>高概率获得已有的技能，获得已有的技能时，概率使其升级
 实现逻辑如下：
@@ -15493,1270 +15534,1270 @@
         </is>
       </c>
     </row>
-    <row r="525">
-      <c r="A525" s="42" t="n">
-        <v>5050002</v>
-      </c>
-      <c r="B525" s="3" t="inlineStr">
-        <is>
-          <t>龙脉·不灭</t>
-        </is>
-      </c>
-      <c r="C525" s="30" t="inlineStr">
-        <is>
-          <t>损失高级技能时有概率保留低级版本，降低损失。</t>
-        </is>
-      </c>
-      <c r="E525" s="30" t="inlineStr">
-        <is>
-          <t>高级技能损失时，50%概率返还获得1个低级技能</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" s="42" t="n">
-        <v>5060001</v>
-      </c>
-      <c r="B526" s="3" t="inlineStr">
-        <is>
-          <t>舍身·舍命</t>
-        </is>
-      </c>
-      <c r="C526" s="30" t="inlineStr">
-        <is>
-          <t>舍身状态下首次致死时牺牲一个灵兽技能保住性命。</t>
-        </is>
-      </c>
-      <c r="E526" s="30" t="inlineStr">
-        <is>
-          <t>每次【舍身】状态下，首次致死消耗1技能保1血</t>
-        </is>
-      </c>
-    </row>
     <row r="527">
       <c r="A527" s="42" t="n">
-        <v>5060002</v>
+        <v>5050002</v>
       </c>
       <c r="B527" s="3" t="inlineStr">
         <is>
-          <t>舍身·续战</t>
+          <t>龙脉·不灭</t>
         </is>
       </c>
       <c r="C527" s="30" t="inlineStr">
         <is>
-          <t>舍身状态下每回合持续回复损失的气血。</t>
+          <t>损失高级技能时有概率保留低级版本，降低损失。</t>
         </is>
       </c>
       <c r="E527" s="30" t="inlineStr">
         <is>
-          <t>【舍身】状态下，每回合回复15%损失气血</t>
+          <t>高级技能损失时，50%概率返还获得1个低级技能</t>
         </is>
       </c>
     </row>
     <row r="528" ht="40.5" customHeight="1" s="57">
       <c r="A528" s="42" t="n">
+        <v>5060001</v>
+      </c>
+      <c r="B528" s="3" t="inlineStr">
+        <is>
+          <t>舍身·舍命</t>
+        </is>
+      </c>
+      <c r="C528" s="30" t="inlineStr">
+        <is>
+          <t>舍身状态下首次致死时牺牲一个灵兽技能保住性命。</t>
+        </is>
+      </c>
+      <c r="E528" s="30" t="inlineStr">
+        <is>
+          <t>每次【舍身】状态下，首次致死消耗1技能保1血</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="42" t="n">
+        <v>5060002</v>
+      </c>
+      <c r="B529" s="3" t="inlineStr">
+        <is>
+          <t>舍身·续战</t>
+        </is>
+      </c>
+      <c r="C529" s="30" t="inlineStr">
+        <is>
+          <t>舍身状态下每回合持续回复损失的气血。</t>
+        </is>
+      </c>
+      <c r="E529" s="30" t="inlineStr">
+        <is>
+          <t>【舍身】状态下，每回合回复15%损失气血</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="42" t="n">
         <v>5070001</v>
       </c>
-      <c r="B528" s="3" t="inlineStr">
+      <c r="B530" s="3" t="inlineStr">
         <is>
           <t>骤雨·取舍</t>
         </is>
       </c>
-      <c r="C528" s="30" t="inlineStr">
+      <c r="C530" s="30" t="inlineStr">
         <is>
           <t>优先消耗非攻击类技能，保留核心战斗能力。</t>
         </is>
       </c>
-      <c r="E528" s="30" t="inlineStr">
+      <c r="E530" s="30" t="inlineStr">
         <is>
           <t>高概率消耗非攻击类
 基于【说明】中的技能页签，75%概率消耗非攻击类的技能</t>
         </is>
       </c>
     </row>
-    <row r="529">
-      <c r="A529" s="42" t="n">
-        <v>5070002</v>
-      </c>
-      <c r="B529" s="3" t="inlineStr">
-        <is>
-          <t>骤雨·回元</t>
-        </is>
-      </c>
-      <c r="C529" s="30" t="inlineStr">
-        <is>
-          <t>击败敌方时返还部分真元消耗。</t>
-        </is>
-      </c>
-      <c r="E529" s="30" t="inlineStr">
-        <is>
-          <t>该技能造成击败时，返还技能消耗的一半真元</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" s="42" t="n">
-        <v>5080001</v>
-      </c>
-      <c r="B530" s="3" t="inlineStr">
-        <is>
-          <t>天崩·精通</t>
-        </is>
-      </c>
-      <c r="C530" s="30" t="inlineStr">
-        <is>
-          <t>高级技能双倍计算，大幅提升伤害段数。</t>
-        </is>
-      </c>
-      <c r="E530" s="30" t="inlineStr">
-        <is>
-          <t>高级技能按照2个普通技能数结算</t>
-        </is>
-      </c>
-    </row>
     <row r="531" ht="27" customHeight="1" s="57">
       <c r="A531" s="42" t="n">
-        <v>5080002</v>
+        <v>5070002</v>
       </c>
       <c r="B531" s="3" t="inlineStr">
         <is>
-          <t>天崩·燃血</t>
+          <t>骤雨·回元</t>
         </is>
       </c>
       <c r="C531" s="30" t="inlineStr">
         <is>
-          <t>技能充足时额外消耗敌方真元，以力破巧。</t>
+          <t>击败敌方时返还部分真元消耗。</t>
         </is>
       </c>
       <c r="E531" s="30" t="inlineStr">
         <is>
-          <t>技能≥3时，真元扣除额外增加50%（算技能扣成100%）</t>
+          <t>该技能造成击败时，返还技能消耗的一半真元</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="42" t="n">
-        <v>5090001</v>
+        <v>5080001</v>
       </c>
       <c r="B532" s="3" t="inlineStr">
         <is>
-          <t>神龙摆尾·吞噬</t>
+          <t>天崩·精通</t>
         </is>
       </c>
       <c r="C532" s="30" t="inlineStr">
         <is>
-          <t>吸收时额外获得共鸣宠物的一个高级被动技能。</t>
+          <t>高级技能双倍计算，大幅提升伤害段数。</t>
         </is>
       </c>
       <c r="E532" s="30" t="inlineStr">
         <is>
-          <t>吸收时，获得共鸣宠物随机1个可获得的高级宠物技能</t>
+          <t>高级技能按照2个普通技能数结算</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="42" t="n">
-        <v>5090002</v>
+        <v>5080002</v>
       </c>
       <c r="B533" s="3" t="inlineStr">
         <is>
-          <t>神龙摆尾·治愈</t>
+          <t>天崩·燃血</t>
         </is>
       </c>
       <c r="C533" s="30" t="inlineStr">
         <is>
-          <t>吸收时回复宠物部分气血，减轻宠物损失。</t>
+          <t>技能充足时额外消耗敌方真元，以力破巧。</t>
         </is>
       </c>
       <c r="E533" s="30" t="inlineStr">
         <is>
-          <t>回复吸收宠物50%的当前气血</t>
+          <t>技能≥3时，真元扣除额外增加50%（算技能扣成100%）</t>
         </is>
       </c>
     </row>
     <row r="534" ht="40.5" customHeight="1" s="57">
       <c r="A534" s="42" t="n">
+        <v>5090001</v>
+      </c>
+      <c r="B534" s="3" t="inlineStr">
+        <is>
+          <t>神龙摆尾·吞噬</t>
+        </is>
+      </c>
+      <c r="C534" s="30" t="inlineStr">
+        <is>
+          <t>吸收时额外获得共鸣宠物的一个高级被动技能。</t>
+        </is>
+      </c>
+      <c r="E534" s="30" t="inlineStr">
+        <is>
+          <t>吸收时，获得共鸣宠物随机1个可获得的高级宠物技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="42" t="n">
+        <v>5090002</v>
+      </c>
+      <c r="B535" s="3" t="inlineStr">
+        <is>
+          <t>神龙摆尾·治愈</t>
+        </is>
+      </c>
+      <c r="C535" s="30" t="inlineStr">
+        <is>
+          <t>吸收时回复宠物部分气血，减轻宠物损失。</t>
+        </is>
+      </c>
+      <c r="E535" s="30" t="inlineStr">
+        <is>
+          <t>回复吸收宠物50%的当前气血</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="42" t="n">
         <v>6010001</v>
       </c>
-      <c r="B534" s="3" t="inlineStr">
+      <c r="B536" s="3" t="inlineStr">
         <is>
           <t>三昧真火·穿甲</t>
         </is>
       </c>
-      <c r="C534" s="30" t="inlineStr">
+      <c r="C536" s="30" t="inlineStr">
         <is>
           <t>消耗火球积累法术穿透，持续增强后续输出。</t>
         </is>
       </c>
-      <c r="E534" s="30" t="inlineStr">
+      <c r="E536" s="30" t="inlineStr">
         <is>
           <t>每消耗3个火球，增加自身1%的法术穿透，至多增加10%
 (溢出火球不计算为消耗）</t>
         </is>
       </c>
     </row>
-    <row r="535">
-      <c r="A535" s="42" t="n">
-        <v>6010002</v>
-      </c>
-      <c r="B535" s="3" t="inlineStr">
-        <is>
-          <t>三昧真火·感应</t>
-        </is>
-      </c>
-      <c r="C535" s="30" t="inlineStr">
-        <is>
-          <t>使用法宝特技时有概率额外积蓄火球。</t>
-        </is>
-      </c>
-      <c r="E535" s="30" t="inlineStr">
-        <is>
-          <t>自身使用法宝特技时，30%概率额外积累一个火球</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" s="42" t="n">
-        <v>6020001</v>
-      </c>
-      <c r="B536" s="3" t="inlineStr">
-        <is>
-          <t>红莲·灼身</t>
-        </is>
-      </c>
-      <c r="C536" s="30" t="inlineStr">
-        <is>
-          <t>攻击首目标时有概率附加灼烧持续伤害。</t>
-        </is>
-      </c>
-      <c r="E536" s="30" t="inlineStr">
-        <is>
-          <t>对首目标，20%概率附加【灼烧】</t>
-        </is>
-      </c>
-    </row>
     <row r="537">
       <c r="A537" s="42" t="n">
-        <v>6020002</v>
+        <v>6010002</v>
       </c>
       <c r="B537" s="3" t="inlineStr">
         <is>
-          <t>红莲·回火</t>
+          <t>三昧真火·感应</t>
         </is>
       </c>
       <c r="C537" s="30" t="inlineStr">
         <is>
-          <t>击败敌方时有概率回收火球。</t>
+          <t>使用法宝特技时有概率额外积蓄火球。</t>
         </is>
       </c>
       <c r="E537" s="30" t="inlineStr">
         <is>
-          <t>该技能造成击败时，50%概率回复1枚火球</t>
+          <t>自身使用法宝特技时，30%概率额外积累一个火球</t>
         </is>
       </c>
     </row>
     <row r="538" ht="27" customHeight="1" s="57">
       <c r="A538" s="42" t="n">
-        <v>6030001</v>
+        <v>6020001</v>
       </c>
       <c r="B538" s="3" t="inlineStr">
         <is>
-          <t>赤焰·蔓延</t>
+          <t>红莲·灼身</t>
         </is>
       </c>
       <c r="C538" s="30" t="inlineStr">
         <is>
-          <t>消耗火球时有概率对命中目标附加灼烧。</t>
+          <t>攻击首目标时有概率附加灼烧持续伤害。</t>
         </is>
       </c>
       <c r="E538" s="30" t="inlineStr">
         <is>
-          <t>消耗X个火球时，对每个目标10×X%概率附加【灼烧】</t>
+          <t>对首目标，20%概率附加【灼烧】</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="42" t="n">
-        <v>6030002</v>
+        <v>6020002</v>
       </c>
       <c r="B539" s="3" t="inlineStr">
         <is>
-          <t>赤焰·爆裂</t>
+          <t>红莲·回火</t>
         </is>
       </c>
       <c r="C539" s="30" t="inlineStr">
         <is>
-          <t>消耗多个火球时法术穿透大幅提升。</t>
+          <t>击败敌方时有概率回收火球。</t>
         </is>
       </c>
       <c r="E539" s="30" t="inlineStr">
         <is>
-          <t>消耗火球≥2时，增加15%的法术穿透</t>
+          <t>该技能造成击败时，50%概率回复1枚火球</t>
         </is>
       </c>
     </row>
     <row r="540" ht="27" customHeight="1" s="57">
       <c r="A540" s="42" t="n">
-        <v>6040001</v>
+        <v>6030001</v>
       </c>
       <c r="B540" s="3" t="inlineStr">
         <is>
-          <t>浴火·劫余</t>
+          <t>赤焰·蔓延</t>
         </is>
       </c>
       <c r="C540" s="30" t="inlineStr">
         <is>
-          <t>浴火期间击败敌方可回复气血与魔法，劫后余生。</t>
+          <t>消耗火球时有概率对命中目标附加灼烧。</t>
         </is>
       </c>
       <c r="E540" s="30" t="inlineStr">
         <is>
-          <t>【浴火】持续期间造成击败时，每个击败回复10%的最大魔法与10%的最大气血</t>
+          <t>消耗X个火球时，对每个目标10×X%概率附加【灼烧】</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="42" t="n">
-        <v>6040002</v>
+        <v>6030002</v>
       </c>
       <c r="B541" s="3" t="inlineStr">
         <is>
-          <t>浴火·怒焰</t>
+          <t>赤焰·爆裂</t>
         </is>
       </c>
       <c r="C541" s="30" t="inlineStr">
         <is>
-          <t>浴火状态下愤怒获取大幅提升。</t>
+          <t>消耗多个火球时法术穿透大幅提升。</t>
         </is>
       </c>
       <c r="E541" s="30" t="inlineStr">
         <is>
-          <t>焚身状态下，增加20%的愤怒获取</t>
+          <t>消耗火球≥2时，增加15%的法术穿透</t>
         </is>
       </c>
     </row>
     <row r="542" ht="27" customHeight="1" s="57">
       <c r="A542" s="42" t="n">
-        <v>6050001</v>
+        <v>6040001</v>
       </c>
       <c r="B542" s="3" t="inlineStr">
         <is>
-          <t>薪火·兽袭</t>
+          <t>浴火·劫余</t>
         </is>
       </c>
       <c r="C542" s="30" t="inlineStr">
         <is>
-          <t>薪火满层时宠物攻击后自动追击一次。</t>
+          <t>浴火期间击败敌方可回复气血与魔法，劫后余生。</t>
         </is>
       </c>
       <c r="E542" s="30" t="inlineStr">
         <is>
-          <t>【薪火】满层时，宠物攻击后以30%伤害使用相同技能追击1次</t>
+          <t>【浴火】持续期间造成击败时，每个击败回复10%的最大魔法与10%的最大气血</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="42" t="n">
-        <v>6050002</v>
+        <v>6040002</v>
       </c>
       <c r="B543" s="3" t="inlineStr">
         <is>
-          <t>薪火·反哺</t>
+          <t>浴火·怒焰</t>
         </is>
       </c>
       <c r="C543" s="30" t="inlineStr">
         <is>
-          <t>宠物击败敌方时有概率回收火球给主人。</t>
+          <t>浴火状态下愤怒获取大幅提升。</t>
         </is>
       </c>
       <c r="E543" s="30" t="inlineStr">
         <is>
-          <t>己方宠物造成击败时，40%概率回复自身1个火球</t>
+          <t>焚身状态下，增加20%的愤怒获取</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="42" t="n">
-        <v>6060001</v>
+        <v>6050001</v>
       </c>
       <c r="B544" s="3" t="inlineStr">
         <is>
-          <t>陨星坠·拾焰</t>
+          <t>薪火·兽袭</t>
         </is>
       </c>
       <c r="C544" s="30" t="inlineStr">
         <is>
-          <t>击败非人物单位时有概率回收火球。</t>
+          <t>薪火满层时宠物攻击后自动追击一次。</t>
         </is>
       </c>
       <c r="E544" s="30" t="inlineStr">
         <is>
-          <t>造成伤害时，25%概率附加1层【灼烧】</t>
+          <t>【薪火】满层时，宠物攻击后以30%伤害使用相同技能追击1次</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="42" t="n">
-        <v>6060002</v>
+        <v>6050002</v>
       </c>
       <c r="B545" s="3" t="inlineStr">
         <is>
-          <t>陨星坠·连破</t>
+          <t>薪火·反哺</t>
         </is>
       </c>
       <c r="C545" s="30" t="inlineStr">
         <is>
-          <t>每段命中均有概率附加灼烧。</t>
+          <t>宠物击败敌方时有概率回收火球给主人。</t>
         </is>
       </c>
       <c r="E545" s="30" t="inlineStr">
         <is>
-          <t>击败对方非人物单位时，50%概率回复1枚火球</t>
+          <t>己方宠物造成击败时，40%概率回复自身1个火球</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="42" t="n">
-        <v>6070001</v>
+        <v>6060001</v>
       </c>
       <c r="B546" s="3" t="inlineStr">
         <is>
-          <t>天赐·凝火</t>
+          <t>陨星坠·拾焰</t>
         </is>
       </c>
       <c r="C546" s="30" t="inlineStr">
         <is>
-          <t>附加时有概率直接凝出一个火球。</t>
+          <t>击败非人物单位时有概率回收火球。</t>
         </is>
       </c>
       <c r="E546" s="30" t="inlineStr">
         <is>
-          <t>附加该状态时，30%概率获得1个火球</t>
+          <t>造成伤害时，25%概率附加1层【灼烧】</t>
         </is>
       </c>
     </row>
     <row r="547" ht="27" customHeight="1" s="57">
       <c r="A547" s="42" t="n">
-        <v>6070002</v>
+        <v>6060002</v>
       </c>
       <c r="B547" s="3" t="inlineStr">
         <is>
-          <t>天赐·续焰</t>
+          <t>陨星坠·连破</t>
         </is>
       </c>
       <c r="C547" s="30" t="inlineStr">
         <is>
-          <t>天赐状态下每消耗火球有概率延长天赐持续时间。</t>
+          <t>每段命中均有概率附加灼烧。</t>
         </is>
       </c>
       <c r="E547" s="30" t="inlineStr">
         <is>
-          <t>天赐状态下每消耗1个火球，10%概率延长天赐状态1回合</t>
+          <t>击败对方非人物单位时，50%概率回复1枚火球</t>
         </is>
       </c>
     </row>
     <row r="548" ht="27" customHeight="1" s="57">
       <c r="A548" s="42" t="n">
+        <v>6070001</v>
+      </c>
+      <c r="B548" s="3" t="inlineStr">
+        <is>
+          <t>天赐·凝火</t>
+        </is>
+      </c>
+      <c r="C548" s="30" t="inlineStr">
+        <is>
+          <t>附加时有概率直接凝出一个火球。</t>
+        </is>
+      </c>
+      <c r="E548" s="30" t="inlineStr">
+        <is>
+          <t>附加该状态时，30%概率获得1个火球</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="42" t="n">
+        <v>6070002</v>
+      </c>
+      <c r="B549" s="3" t="inlineStr">
+        <is>
+          <t>天赐·续焰</t>
+        </is>
+      </c>
+      <c r="C549" s="30" t="inlineStr">
+        <is>
+          <t>天赐状态下每消耗火球有概率延长天赐持续时间。</t>
+        </is>
+      </c>
+      <c r="E549" s="30" t="inlineStr">
+        <is>
+          <t>天赐状态下每消耗1个火球，10%概率延长天赐状态1回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="550" ht="27" customHeight="1" s="57">
+      <c r="A550" s="42" t="n">
         <v>6080001</v>
       </c>
-      <c r="B548" s="3" t="inlineStr">
+      <c r="B550" s="3" t="inlineStr">
         <is>
           <t>炎盾·温养</t>
         </is>
       </c>
-      <c r="C548" s="30" t="inlineStr">
+      <c r="C550" s="30" t="inlineStr">
         <is>
           <t>炎盾存在时每有敌方处于灼烧状态可回复气血。</t>
         </is>
       </c>
-      <c r="E548" s="30" t="inlineStr">
+      <c r="E550" s="30" t="inlineStr">
         <is>
           <t>【炎盾】状态下，敌方回合每存在1个【灼烧】单位
 回合结束时，回复自身等级*境界倍率*3的气血</t>
         </is>
       </c>
     </row>
-    <row r="549">
-      <c r="A549" s="42" t="n">
+    <row r="551">
+      <c r="A551" s="42" t="n">
         <v>6080002</v>
       </c>
-      <c r="B549" s="3" t="inlineStr">
+      <c r="B551" s="3" t="inlineStr">
         <is>
           <t>炎盾·余烬</t>
         </is>
       </c>
-      <c r="C549" s="30" t="inlineStr">
+      <c r="C551" s="30" t="inlineStr">
         <is>
           <t>被复活时有概率自动附加炎盾。</t>
         </is>
       </c>
-      <c r="E549" s="30" t="inlineStr">
+      <c r="E551" s="30" t="inlineStr">
         <is>
           <t>被复活时，50%概率附加【炎盾】状态</t>
         </is>
       </c>
     </row>
-    <row r="550" ht="27" customHeight="1" s="57">
-      <c r="A550" s="42" t="n">
+    <row r="552">
+      <c r="A552" s="42" t="n">
         <v>6090001</v>
       </c>
-      <c r="B550" s="3" t="inlineStr">
+      <c r="B552" s="3" t="inlineStr">
         <is>
           <t>焚天·燃尽</t>
         </is>
       </c>
-      <c r="C550" s="30" t="inlineStr">
+      <c r="C552" s="30" t="inlineStr">
         <is>
           <t>满火球释放时法术穿透大幅提升。</t>
         </is>
       </c>
-      <c r="E550" s="30" t="inlineStr">
+      <c r="E552" s="30" t="inlineStr">
         <is>
           <t>每次造成伤害时，结算1回合的灼烧增益
 扣除对方1回合的灼烧结算的气血</t>
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" s="42" t="n">
-        <v>6090002</v>
-      </c>
-      <c r="B551" s="3" t="inlineStr">
-        <is>
-          <t>焚天·满溢</t>
-        </is>
-      </c>
-      <c r="C551" s="30" t="inlineStr">
-        <is>
-          <t>攻击时有概率附加灼烧。</t>
-        </is>
-      </c>
-      <c r="E551" s="30" t="inlineStr">
-        <is>
-          <t>满火球+20%的法术穿透</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" s="42" t="n">
-        <v>7010001</v>
-      </c>
-      <c r="B552" s="3" t="inlineStr">
-        <is>
-          <t>生生不息·护幼</t>
-        </is>
-      </c>
-      <c r="C552" s="30" t="inlineStr">
-        <is>
-          <t>召唤宠物时自动为其附加生息。</t>
-        </is>
-      </c>
-      <c r="E552" s="30" t="inlineStr">
-        <is>
-          <t>己方战斗中召唤宠物时，附加1层【生息】</t>
-        </is>
-      </c>
-    </row>
     <row r="553" ht="27" customHeight="1" s="57">
       <c r="A553" s="42" t="n">
-        <v>7010002</v>
+        <v>6090002</v>
       </c>
       <c r="B553" s="3" t="inlineStr">
         <is>
-          <t>生生不息·厚积</t>
+          <t>焚天·满溢</t>
         </is>
       </c>
       <c r="C553" s="30" t="inlineStr">
         <is>
-          <t>生息每回合额外回复一定比例最大气血。</t>
+          <t>攻击时有概率附加灼烧。</t>
         </is>
       </c>
       <c r="E553" s="30" t="inlineStr">
         <is>
-          <t>【生息】每回合额外目标回复2%的最大气血，不超过等级*境界倍率*2</t>
+          <t>满火球+20%的法术穿透</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="42" t="n">
-        <v>7020001</v>
+        <v>7010001</v>
       </c>
       <c r="B554" s="3" t="inlineStr">
         <is>
-          <t>回春术·妙手</t>
+          <t>生生不息·护幼</t>
         </is>
       </c>
       <c r="C554" s="30" t="inlineStr">
         <is>
-          <t>目标没有生息时有概率额外附加一层。</t>
+          <t>召唤宠物时自动为其附加生息。</t>
         </is>
       </c>
       <c r="E554" s="30" t="inlineStr">
         <is>
-          <t>目标未存在生息时，以30%概率额外附加1层生息</t>
+          <t>己方战斗中召唤宠物时，附加1层【生息】</t>
         </is>
       </c>
     </row>
     <row r="555" ht="27" customHeight="1" s="57">
       <c r="A555" s="42" t="n">
-        <v>7020002</v>
+        <v>7010002</v>
       </c>
       <c r="B555" s="3" t="inlineStr">
         <is>
-          <t>回春术·兽愈</t>
+          <t>生生不息·厚积</t>
         </is>
       </c>
       <c r="C555" s="30" t="inlineStr">
         <is>
-          <t>治疗时有概率同时治疗气血最低的宠物。</t>
+          <t>生息每回合额外回复一定比例最大气血。</t>
         </is>
       </c>
       <c r="E555" s="30" t="inlineStr">
         <is>
-          <t>30%概率同时对气血最低宠物单位释放1次，造成50%的治疗结果</t>
+          <t>【生息】每回合额外目标回复2%的最大气血，不超过等级*境界倍率*2</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="42" t="n">
-        <v>7030001</v>
+        <v>7020001</v>
       </c>
       <c r="B556" s="3" t="inlineStr">
         <is>
-          <t>飞花·斩获</t>
+          <t>回春术·妙手</t>
         </is>
       </c>
       <c r="C556" s="30" t="inlineStr">
         <is>
-          <t>击败敌方时附加生息的概率大幅提升。</t>
+          <t>目标没有生息时有概率额外附加一层。</t>
         </is>
       </c>
       <c r="E556" s="30" t="inlineStr">
         <is>
-          <t>击败敌方目标时，增加50%的附加概率（共计70%）</t>
+          <t>目标未存在生息时，以30%概率额外附加1层生息</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="42" t="n">
-        <v>7030002</v>
+        <v>7020002</v>
       </c>
       <c r="B557" s="3" t="inlineStr">
         <is>
-          <t>飞花·滋长</t>
+          <t>回春术·兽愈</t>
         </is>
       </c>
       <c r="C557" s="30" t="inlineStr">
         <is>
-          <t>友方身上的生息越多，飞花伤害越高。</t>
+          <t>治疗时有概率同时治疗气血最低的宠物。</t>
         </is>
       </c>
       <c r="E557" s="30" t="inlineStr">
         <is>
-          <t>己方每有1名存在【生息】的友方，该技能伤害+10%</t>
+          <t>30%概率同时对气血最低宠物单位释放1次，造成50%的治疗结果</t>
         </is>
       </c>
     </row>
     <row r="558" ht="40.5" customHeight="1" s="57">
       <c r="A558" s="42" t="n">
+        <v>7030001</v>
+      </c>
+      <c r="B558" s="3" t="inlineStr">
+        <is>
+          <t>飞花·斩获</t>
+        </is>
+      </c>
+      <c r="C558" s="30" t="inlineStr">
+        <is>
+          <t>击败敌方时附加生息的概率大幅提升。</t>
+        </is>
+      </c>
+      <c r="E558" s="30" t="inlineStr">
+        <is>
+          <t>击败敌方目标时，增加50%的附加概率（共计70%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="42" t="n">
+        <v>7030002</v>
+      </c>
+      <c r="B559" s="3" t="inlineStr">
+        <is>
+          <t>飞花·滋长</t>
+        </is>
+      </c>
+      <c r="C559" s="30" t="inlineStr">
+        <is>
+          <t>友方身上的生息越多，飞花伤害越高。</t>
+        </is>
+      </c>
+      <c r="E559" s="30" t="inlineStr">
+        <is>
+          <t>己方每有1名存在【生息】的友方，该技能伤害+10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="42" t="n">
         <v>7040001</v>
       </c>
-      <c r="B558" s="3" t="inlineStr">
+      <c r="B560" s="3" t="inlineStr">
         <is>
           <t>铁壁·金身</t>
         </is>
       </c>
-      <c r="C558" s="30" t="inlineStr">
+      <c r="C560" s="30" t="inlineStr">
         <is>
           <t>低血目标额外获得物理抗暴提升。</t>
         </is>
       </c>
-      <c r="E558" s="30" t="inlineStr">
+      <c r="E560" s="30" t="inlineStr">
         <is>
           <t>目标生命值低于30%时，额外附加【金身】
 【金身】：提升5%物理抗暴并降低20%的物理被爆伤结果</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" s="42" t="n">
-        <v>7040002</v>
-      </c>
-      <c r="B559" s="3" t="inlineStr">
-        <is>
-          <t>铁壁·护生</t>
-        </is>
-      </c>
-      <c r="C559" s="30" t="inlineStr">
-        <is>
-          <t>召唤宠物时自动附加铁壁。</t>
-        </is>
-      </c>
-      <c r="E559" s="30" t="inlineStr">
-        <is>
-          <t>己方召唤的宠物出场时，附加1层【铁壁】</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" s="42" t="n">
-        <v>7050001</v>
-      </c>
-      <c r="B560" s="3" t="inlineStr">
-        <is>
-          <t>绽放·金铁</t>
-        </is>
-      </c>
-      <c r="C560" s="30" t="inlineStr">
-        <is>
-          <t>绽放时额外附加铁壁与金身双重防护。</t>
-        </is>
-      </c>
-      <c r="E560" s="30" t="inlineStr">
-        <is>
-          <t>【绽放】时，附加1层【铁壁】与【金身】</t>
-        </is>
-      </c>
-    </row>
     <row r="561">
       <c r="A561" s="42" t="n">
-        <v>7050002</v>
+        <v>7040002</v>
       </c>
       <c r="B561" s="3" t="inlineStr">
         <is>
-          <t>绽放·赐怒</t>
+          <t>铁壁·护生</t>
         </is>
       </c>
       <c r="C561" s="30" t="inlineStr">
         <is>
-          <t>绽放概率提升，且绽放后回复目标愤怒。</t>
+          <t>召唤宠物时自动附加铁壁。</t>
         </is>
       </c>
       <c r="E561" s="30" t="inlineStr">
         <is>
-          <t>【绽放】概率提高20%，绽放后回复目标6点愤怒</t>
+          <t>己方召唤的宠物出场时，附加1层【铁壁】</t>
         </is>
       </c>
     </row>
     <row r="562" ht="27" customHeight="1" s="57">
       <c r="A562" s="42" t="n">
-        <v>7060001</v>
+        <v>7050001</v>
       </c>
       <c r="B562" s="3" t="inlineStr">
         <is>
-          <t>醍醐·急救</t>
+          <t>绽放·金铁</t>
         </is>
       </c>
       <c r="C562" s="30" t="inlineStr">
         <is>
-          <t>低血目标的结算治疗量大幅增加，同时回复内伤。</t>
+          <t>绽放时额外附加铁壁与金身双重防护。</t>
         </is>
       </c>
       <c r="E562" s="30" t="inlineStr">
         <is>
-          <t>气血低于 50% 的目标，结算治疗倍率额外 +50%。同时回复治疗结果15%的内伤</t>
+          <t>【绽放】时，附加1层【铁壁】与【金身】</t>
         </is>
       </c>
     </row>
     <row r="563" ht="27" customHeight="1" s="57">
       <c r="A563" s="42" t="n">
-        <v>7060002</v>
+        <v>7050002</v>
       </c>
       <c r="B563" s="3" t="inlineStr">
         <is>
-          <t>醍醐·驱毒</t>
+          <t>绽放·赐怒</t>
         </is>
       </c>
       <c r="C563" s="30" t="inlineStr">
         <is>
-          <t>结算时每层生息有概率清除目标身上的减益。</t>
+          <t>绽放概率提升，且绽放后回复目标愤怒。</t>
         </is>
       </c>
       <c r="E563" s="30" t="inlineStr">
         <is>
-          <t>结算时，每层生息以30%概率清除结算单位1个非封印减益</t>
+          <t>【绽放】概率提高20%，绽放后回复目标6点愤怒</t>
         </is>
       </c>
     </row>
     <row r="564" ht="40.5" customHeight="1" s="57">
       <c r="A564" s="42" t="n">
+        <v>7060001</v>
+      </c>
+      <c r="B564" s="3" t="inlineStr">
+        <is>
+          <t>醍醐·急救</t>
+        </is>
+      </c>
+      <c r="C564" s="30" t="inlineStr">
+        <is>
+          <t>低血目标的结算治疗量大幅增加，同时回复内伤。</t>
+        </is>
+      </c>
+      <c r="E564" s="30" t="inlineStr">
+        <is>
+          <t>气血低于 50% 的目标，结算治疗倍率额外 +50%。同时回复治疗结果15%的内伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="40.5" customHeight="1" s="57">
+      <c r="A565" s="42" t="n">
+        <v>7060002</v>
+      </c>
+      <c r="B565" s="3" t="inlineStr">
+        <is>
+          <t>醍醐·驱毒</t>
+        </is>
+      </c>
+      <c r="C565" s="30" t="inlineStr">
+        <is>
+          <t>结算时每层生息有概率清除目标身上的减益。</t>
+        </is>
+      </c>
+      <c r="E565" s="30" t="inlineStr">
+        <is>
+          <t>结算时，每层生息以30%概率清除结算单位1个非封印减益</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="27" customHeight="1" s="57">
+      <c r="A566" s="42" t="n">
         <v>7070001</v>
       </c>
-      <c r="B564" s="3" t="inlineStr">
+      <c r="B566" s="3" t="inlineStr">
         <is>
           <t>逢春·免死</t>
         </is>
       </c>
-      <c r="C564" s="30" t="inlineStr">
+      <c r="C566" s="30" t="inlineStr">
         <is>
           <t>复活后附加免死效果，致命伤害下保住性命。</t>
         </is>
       </c>
-      <c r="E564" s="30" t="inlineStr">
+      <c r="E566" s="30" t="inlineStr">
         <is>
           <t>附加【免死】状态1回合
 使其本回合免死1次，受到致命伤害时免死并回复1血，同时清除免死状态</t>
         </is>
       </c>
     </row>
-    <row r="565" ht="40.5" customHeight="1" s="57">
-      <c r="A565" s="42" t="n">
+    <row r="567" ht="27" customHeight="1" s="57">
+      <c r="A567" s="42" t="n">
         <v>7070002</v>
       </c>
-      <c r="B565" s="3" t="inlineStr">
+      <c r="B567" s="3" t="inlineStr">
         <is>
           <t>逢春·药引</t>
         </is>
       </c>
-      <c r="C565" s="30" t="inlineStr">
+      <c r="C567" s="30" t="inlineStr">
         <is>
           <t>复活后附加药引效果，药品回复能力提升。</t>
         </is>
       </c>
-      <c r="E565" s="30" t="inlineStr">
+      <c r="E567" s="30" t="inlineStr">
         <is>
           <t>复活后，附加【药引】状态2回合，
 使其2回合内受到药品回复效果增加30%（包括回蓝回血）</t>
         </is>
       </c>
     </row>
-    <row r="566" ht="27" customHeight="1" s="57">
-      <c r="A566" s="42" t="n">
-        <v>7080001</v>
-      </c>
-      <c r="B566" s="3" t="inlineStr">
-        <is>
-          <t>枯荣·转虚</t>
-        </is>
-      </c>
-      <c r="C566" s="30" t="inlineStr">
-        <is>
-          <t>敌方宠物满层虚弱离场时传染给物伤最高的敌方。</t>
-        </is>
-      </c>
-      <c r="E566" s="30" t="inlineStr">
-        <is>
-          <t>对方宠物单位3层【虚弱】离场时，转移1层【虚弱】层数给对方物伤最高单位上</t>
-        </is>
-      </c>
-    </row>
-    <row r="567" ht="27" customHeight="1" s="57">
-      <c r="A567" s="42" t="n">
-        <v>7080002</v>
-      </c>
-      <c r="B567" s="3" t="inlineStr">
-        <is>
-          <t>枯荣·趁虚</t>
-        </is>
-      </c>
-      <c r="C567" s="30" t="inlineStr">
-        <is>
-          <t>我方宠物攻击被虚弱的目标时物理伤害提升。</t>
-        </is>
-      </c>
-      <c r="E567" s="30" t="inlineStr">
-        <is>
-          <t>我方宠物物理攻击【虚弱】单位时，物理伤害结果+10%</t>
-        </is>
-      </c>
-    </row>
     <row r="568" ht="27" customHeight="1" s="57">
       <c r="A568" s="42" t="n">
-        <v>7090001</v>
+        <v>7080001</v>
       </c>
       <c r="B568" s="3" t="inlineStr">
         <is>
-          <t>万象复苏·大愈</t>
+          <t>枯荣·转虚</t>
         </is>
       </c>
       <c r="C568" s="30" t="inlineStr">
         <is>
-          <t>复活多人时额外回复大量内伤。</t>
+          <t>敌方宠物满层虚弱离场时传染给物伤最高的敌方。</t>
         </is>
       </c>
       <c r="E568" s="30" t="inlineStr">
         <is>
-          <t>若复活=2人，额外回复30%回复结果(总计50%）的内伤</t>
+          <t>对方宠物单位3层【虚弱】离场时，转移1层【虚弱】层数给对方物伤最高单位上</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="42" t="n">
-        <v>7090002</v>
+        <v>7080002</v>
       </c>
       <c r="B569" s="3" t="inlineStr">
         <is>
-          <t>万象复苏·遍洒</t>
+          <t>枯荣·趁虚</t>
         </is>
       </c>
       <c r="C569" s="30" t="inlineStr">
         <is>
-          <t>同时为所有非人物单位附加生息持续回血。</t>
+          <t>我方宠物攻击被虚弱的目标时物理伤害提升。</t>
         </is>
       </c>
       <c r="E569" s="30" t="inlineStr">
         <is>
-          <t>为全体非人物单位额外附加1层【生息】。</t>
+          <t>我方宠物物理攻击【虚弱】单位时，物理伤害结果+10%</t>
         </is>
       </c>
     </row>
     <row r="570" ht="27" customHeight="1" s="57">
       <c r="A570" s="42" t="n">
-        <v>8010001</v>
+        <v>7090001</v>
       </c>
       <c r="B570" s="3" t="inlineStr">
         <is>
-          <t>化形·执念</t>
+          <t>万象复苏·大愈</t>
         </is>
       </c>
       <c r="C570" s="30" t="inlineStr">
         <is>
-          <t>封印未触发化形时下次成功概率持续提升。</t>
+          <t>复活多人时额外回复大量内伤。</t>
         </is>
       </c>
       <c r="E570" s="30" t="inlineStr">
         <is>
-          <t>封印命中后未获得化形时，下一次成功施加封印时获得化形的概率增加20%，可叠加3次</t>
+          <t>若复活=2人，额外回复30%回复结果(总计50%）的内伤</t>
         </is>
       </c>
     </row>
     <row r="571" ht="27" customHeight="1" s="57">
       <c r="A571" s="42" t="n">
-        <v>8010002</v>
+        <v>7090002</v>
       </c>
       <c r="B571" s="3" t="inlineStr">
         <is>
-          <t>化形·突袭</t>
+          <t>万象复苏·遍洒</t>
         </is>
       </c>
       <c r="C571" s="30" t="inlineStr">
         <is>
-          <t>获得化形时有概率立刻对随机敌方发起攻击。</t>
+          <t>同时为所有非人物单位附加生息持续回血。</t>
         </is>
       </c>
       <c r="E571" s="30" t="inlineStr">
         <is>
-          <t>宠物获得化形时，50% 概率立刻对敌方随机目标释放 1 次法术攻击或普通攻击（优先释放法术）</t>
+          <t>为全体非人物单位额外附加1层【生息】。</t>
         </is>
       </c>
     </row>
     <row r="572" ht="27" customHeight="1" s="57">
       <c r="A572" s="42" t="n">
-        <v>8020001</v>
+        <v>8010001</v>
       </c>
       <c r="B572" s="3" t="inlineStr">
         <is>
-          <t>醉生梦死·破灵</t>
+          <t>化形·执念</t>
         </is>
       </c>
       <c r="C572" s="30" t="inlineStr">
         <is>
-          <t>封印成功时有概率附加脆弱或裂魂。</t>
+          <t>封印未触发化形时下次成功概率持续提升。</t>
         </is>
       </c>
       <c r="E572" s="30" t="inlineStr">
         <is>
-          <t>封印成功时，30%概率为对方附加【脆弱】或【裂魂】效果</t>
+          <t>封印命中后未获得化形时，下一次成功施加封印时获得化形的概率增加20%，可叠加3次</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="42" t="n">
-        <v>8020002</v>
+        <v>8010002</v>
       </c>
       <c r="B573" s="3" t="inlineStr">
         <is>
-          <t>醉生梦死·必化</t>
+          <t>化形·突袭</t>
         </is>
       </c>
       <c r="C573" s="30" t="inlineStr">
         <is>
-          <t>两个目标均封印成功时必定触发宠物化形。</t>
+          <t>获得化形时有概率立刻对随机敌方发起攻击。</t>
         </is>
       </c>
       <c r="E573" s="30" t="inlineStr">
         <is>
-          <t>两个目标均封印成功时，必定触发【化形】</t>
+          <t>宠物获得化形时，50% 概率立刻对敌方随机目标释放 1 次法术攻击或普通攻击（优先释放法术）</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="42" t="n">
-        <v>8030001</v>
+        <v>8020001</v>
       </c>
       <c r="B574" s="3" t="inlineStr">
         <is>
-          <t>霓裳·恃速</t>
+          <t>醉生梦死·破灵</t>
         </is>
       </c>
       <c r="C574" s="30" t="inlineStr">
         <is>
-          <t>攻击速度低于自身的目标时伤害大幅提升。</t>
+          <t>封印成功时有概率附加脆弱或裂魂。</t>
         </is>
       </c>
       <c r="E574" s="30" t="inlineStr">
         <is>
-          <t>攻击速度低于自身的目标时，增加50%的技能伤害</t>
+          <t>封印成功时，30%概率为对方附加【脆弱】或【裂魂】效果</t>
         </is>
       </c>
     </row>
     <row r="575" ht="27" customHeight="1" s="57">
       <c r="A575" s="42" t="n">
-        <v>8030002</v>
+        <v>8020002</v>
       </c>
       <c r="B575" s="3" t="inlineStr">
         <is>
-          <t>霓裳·克灵</t>
+          <t>醉生梦死·必化</t>
         </is>
       </c>
       <c r="C575" s="30" t="inlineStr">
         <is>
-          <t>攻击宠物时封禁概率大幅提升。</t>
+          <t>两个目标均封印成功时必定触发宠物化形。</t>
         </is>
       </c>
       <c r="E575" s="30" t="inlineStr">
         <is>
-          <t>攻击非人物单位时，【封技】概率额外增加 12%。(累计20%）</t>
+          <t>两个目标均封印成功时，必定触发【化形】</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="42" t="n">
-        <v>8040001</v>
+        <v>8030001</v>
       </c>
       <c r="B576" s="3" t="inlineStr">
         <is>
-          <t>幻惑·蛊毒</t>
+          <t>霓裳·恃速</t>
         </is>
       </c>
       <c r="C576" s="30" t="inlineStr">
         <is>
-          <t>每剥离一个增益就附加一层蛊毒持续伤害。</t>
+          <t>攻击速度低于自身的目标时伤害大幅提升。</t>
         </is>
       </c>
       <c r="E576" s="30" t="inlineStr">
         <is>
-          <t>目标每被移除一个增益效果，为目标附加1层【蛊毒】</t>
+          <t>攻击速度低于自身的目标时，增加50%的技能伤害</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="42" t="n">
-        <v>8040002</v>
+        <v>8030002</v>
       </c>
       <c r="B577" s="3" t="inlineStr">
         <is>
-          <t>幻惑·偷取</t>
+          <t>霓裳·克灵</t>
         </is>
       </c>
       <c r="C577" s="30" t="inlineStr">
         <is>
-          <t>剥离增益时有概率将其偷取到自身。</t>
+          <t>攻击宠物时封禁概率大幅提升。</t>
         </is>
       </c>
       <c r="E577" s="30" t="inlineStr">
         <is>
-          <t>目标被驱散增益效果时，30%概率将其偷窃到自身上</t>
+          <t>攻击非人物单位时，【封技】概率额外增加 12%。(累计20%）</t>
         </is>
       </c>
     </row>
     <row r="578" ht="27" customHeight="1" s="57">
       <c r="A578" s="42" t="n">
-        <v>8050001</v>
+        <v>8040001</v>
       </c>
       <c r="B578" s="3" t="inlineStr">
         <is>
-          <t>擅变·同气</t>
+          <t>幻惑·蛊毒</t>
         </is>
       </c>
       <c r="C578" s="30" t="inlineStr">
         <is>
-          <t>场上每存在一种化形类型，所有宠物伤害与减免均提升。</t>
+          <t>每剥离一个增益就附加一层蛊毒持续伤害。</t>
         </is>
       </c>
       <c r="E578" s="30" t="inlineStr">
         <is>
-          <t>己方宠物每存在1种类型化形时，增加己方所有在场宠物5%的伤害结果与5%的伤害减免</t>
+          <t>目标每被移除一个增益效果，为目标附加1层【蛊毒】</t>
         </is>
       </c>
     </row>
     <row r="579" ht="27" customHeight="1" s="57">
       <c r="A579" s="42" t="n">
-        <v>8050002</v>
+        <v>8040002</v>
       </c>
       <c r="B579" s="3" t="inlineStr">
         <is>
-          <t>擅变·传承</t>
+          <t>幻惑·偷取</t>
         </is>
       </c>
       <c r="C579" s="30" t="inlineStr">
         <is>
-          <t>化形宠物倒地时有概率将化形传承给其他宠物。</t>
+          <t>剥离增益时有概率将其偷取到自身。</t>
         </is>
       </c>
       <c r="E579" s="30" t="inlineStr">
         <is>
-          <t>化形宠物倒地时，50%概率减少1回合将其继承给未存在化形的宠物上</t>
+          <t>目标被驱散增益效果时，30%概率将其偷窃到自身上</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="42" t="n">
-        <v>8060001</v>
+        <v>8050001</v>
       </c>
       <c r="B580" s="3" t="inlineStr">
         <is>
-          <t>妖雾·反蛊</t>
+          <t>擅变·同气</t>
         </is>
       </c>
       <c r="C580" s="30" t="inlineStr">
         <is>
-          <t>成功闪避时为攻击者附加蛊毒。</t>
+          <t>场上每存在一种化形类型，所有宠物伤害与减免均提升。</t>
         </is>
       </c>
       <c r="E580" s="30" t="inlineStr">
         <is>
-          <t>成功躲避攻击时，为攻击来源单位附加1层【蛊毒】</t>
+          <t>己方宠物每存在1种类型化形时，增加己方所有在场宠物5%的伤害结果与5%的伤害减免</t>
         </is>
       </c>
     </row>
     <row r="581" ht="27" customHeight="1" s="57">
       <c r="A581" s="42" t="n">
+        <v>8050002</v>
+      </c>
+      <c r="B581" s="3" t="inlineStr">
+        <is>
+          <t>擅变·传承</t>
+        </is>
+      </c>
+      <c r="C581" s="30" t="inlineStr">
+        <is>
+          <t>化形宠物倒地时有概率将化形传承给其他宠物。</t>
+        </is>
+      </c>
+      <c r="E581" s="30" t="inlineStr">
+        <is>
+          <t>化形宠物倒地时，50%概率减少1回合将其继承给未存在化形的宠物上</t>
+        </is>
+      </c>
+    </row>
+    <row r="582" ht="27" customHeight="1" s="57">
+      <c r="A582" s="42" t="n">
+        <v>8060001</v>
+      </c>
+      <c r="B582" s="3" t="inlineStr">
+        <is>
+          <t>妖雾·反蛊</t>
+        </is>
+      </c>
+      <c r="C582" s="30" t="inlineStr">
+        <is>
+          <t>成功闪避时为攻击者附加蛊毒。</t>
+        </is>
+      </c>
+      <c r="E582" s="30" t="inlineStr">
+        <is>
+          <t>成功躲避攻击时，为攻击来源单位附加1层【蛊毒】</t>
+        </is>
+      </c>
+    </row>
+    <row r="583" ht="27" customHeight="1" s="57">
+      <c r="A583" s="42" t="n">
         <v>8060002</v>
       </c>
-      <c r="B581" s="3" t="inlineStr">
+      <c r="B583" s="3" t="inlineStr">
         <is>
           <t>妖雾·窃怒</t>
         </is>
       </c>
-      <c r="C581" s="30" t="inlineStr">
+      <c r="C583" s="30" t="inlineStr">
         <is>
           <t>成功闪避时回复愤怒。</t>
         </is>
       </c>
-      <c r="E581" s="30" t="inlineStr">
+      <c r="E583" s="30" t="inlineStr">
         <is>
           <t>成功躲避攻击时，为自身回复3点愤怒
 每回合至多回复15点</t>
         </is>
       </c>
     </row>
-    <row r="582" ht="27" customHeight="1" s="57">
-      <c r="A582" s="42" t="n">
-        <v>8070001</v>
-      </c>
-      <c r="B582" s="3" t="inlineStr">
-        <is>
-          <t>绝息·削抗</t>
-        </is>
-      </c>
-      <c r="C582" s="30" t="inlineStr">
-        <is>
-          <t>释放后削弱目标的封印抵抗能力。</t>
-        </is>
-      </c>
-      <c r="E582" s="30" t="inlineStr">
-        <is>
-          <t>释放后，附加【削抗】DEBUFF，使其封印抵抗降低 10%，持续 4 回合</t>
-        </is>
-      </c>
-    </row>
-    <row r="583" ht="27" customHeight="1" s="57">
-      <c r="A583" s="42" t="n">
-        <v>8070002</v>
-      </c>
-      <c r="B583" s="3" t="inlineStr">
-        <is>
-          <t>绝息·追绝</t>
-        </is>
-      </c>
-      <c r="C583" s="30" t="inlineStr">
-        <is>
-          <t>绝息目标被击败时绝息效果延长传递。</t>
-        </is>
-      </c>
-      <c r="E583" s="30" t="inlineStr">
-        <is>
-          <t>【绝息】目标被击败时，其【绝息】持续时间延长1回合</t>
-        </is>
-      </c>
-    </row>
     <row r="584">
       <c r="A584" s="42" t="n">
-        <v>8080001</v>
+        <v>8070001</v>
       </c>
       <c r="B584" s="3" t="inlineStr">
         <is>
-          <t>裂魂爪·深创</t>
+          <t>绝息·削抗</t>
         </is>
       </c>
       <c r="C584" s="30" t="inlineStr">
         <is>
-          <t>目标重伤层数越多固定伤害越高。</t>
+          <t>释放后削弱目标的封印抵抗能力。</t>
         </is>
       </c>
       <c r="E584" s="30" t="inlineStr">
         <is>
-          <t>每层【重伤】增加该技能30%的固定伤害</t>
+          <t>释放后，附加【削抗】DEBUFF，使其封印抵抗降低 10%，持续 4 回合</t>
         </is>
       </c>
     </row>
     <row r="585" ht="27" customHeight="1" s="57">
       <c r="A585" s="42" t="n">
+        <v>8070002</v>
+      </c>
+      <c r="B585" s="3" t="inlineStr">
+        <is>
+          <t>绝息·追绝</t>
+        </is>
+      </c>
+      <c r="C585" s="30" t="inlineStr">
+        <is>
+          <t>绝息目标被击败时绝息效果延长传递。</t>
+        </is>
+      </c>
+      <c r="E585" s="30" t="inlineStr">
+        <is>
+          <t>【绝息】目标被击败时，其【绝息】持续时间延长1回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="42" t="n">
+        <v>8080001</v>
+      </c>
+      <c r="B586" s="3" t="inlineStr">
+        <is>
+          <t>裂魂爪·深创</t>
+        </is>
+      </c>
+      <c r="C586" s="30" t="inlineStr">
+        <is>
+          <t>目标重伤层数越多固定伤害越高。</t>
+        </is>
+      </c>
+      <c r="E586" s="30" t="inlineStr">
+        <is>
+          <t>每层【重伤】增加该技能30%的固定伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="587" ht="27" customHeight="1" s="57">
+      <c r="A587" s="42" t="n">
         <v>8080002</v>
       </c>
-      <c r="B585" s="3" t="inlineStr">
+      <c r="B587" s="3" t="inlineStr">
         <is>
           <t>裂魂爪·兽怒</t>
         </is>
       </c>
-      <c r="C585" s="30" t="inlineStr">
+      <c r="C587" s="30" t="inlineStr">
         <is>
           <t>化形宠物攻击重伤目标时暴击伤害大幅提升。</t>
         </is>
       </c>
-      <c r="E585" s="30" t="inlineStr">
+      <c r="E587" s="30" t="inlineStr">
         <is>
           <t>己方【化形】宠物对【重伤】目标攻击时
 增加30%的暴击伤害结果</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" s="42" t="n">
+    <row r="588">
+      <c r="A588" s="42" t="n">
         <v>8090001</v>
       </c>
-      <c r="B586" s="3" t="inlineStr">
+      <c r="B588" s="3" t="inlineStr">
         <is>
           <t>上古妖形·重置</t>
         </is>
       </c>
-      <c r="C586" s="30" t="inlineStr">
+      <c r="C588" s="30" t="inlineStr">
         <is>
           <t>进化后化形持续时间重置为满。</t>
         </is>
       </c>
-      <c r="E586" s="30" t="inlineStr">
+      <c r="E588" s="30" t="inlineStr">
         <is>
           <t>释放后，进化后的化形持续时间重置为4回合</t>
         </is>
       </c>
     </row>
-    <row r="587" ht="27" customHeight="1" s="57">
-      <c r="A587" s="42" t="n">
+    <row r="589">
+      <c r="A589" s="42" t="n">
         <v>8090002</v>
       </c>
-      <c r="B587" s="3" t="inlineStr">
+      <c r="B589" s="3" t="inlineStr">
         <is>
           <t>上古妖形·赐形</t>
         </is>
       </c>
-      <c r="C587" s="30" t="inlineStr">
+      <c r="C589" s="30" t="inlineStr">
         <is>
           <t>释放时额外为一个宠物赋予进化后的化形。</t>
         </is>
       </c>
-      <c r="E587" s="30" t="inlineStr">
+      <c r="E589" s="30" t="inlineStr">
         <is>
           <t>释放时，随机为我方1个宠物单位赋予1个进化后的化形</t>
         </is>
@@ -30070,79 +30111,66 @@
       </c>
     </row>
     <row r="161" ht="32.25" customHeight="1" s="57">
-      <c r="A161" s="6" t="n">
-        <v>900023</v>
-      </c>
-      <c r="B161" s="43" t="inlineStr">
-        <is>
-          <t>水清决</t>
-        </is>
-      </c>
-      <c r="C161" s="6" t="n"/>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>damage,int</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="inlineStr">
+      <c r="A161" s="98" t="n">
+        <v>900015</v>
+      </c>
+      <c r="B161" s="98" t="n"/>
+      <c r="C161" s="98" t="n"/>
+      <c r="D161" s="98" t="n"/>
+      <c r="E161" s="98" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="J161" s="43" t="n"/>
-      <c r="K161" s="43" t="n"/>
-      <c r="M161" s="3" t="inlineStr">
-        <is>
-          <t>CurrMP,1,10</t>
-        </is>
-      </c>
-      <c r="O161" s="3" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="Q161" s="3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="S161" s="3" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
-      <c r="U161" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V161" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W161" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB161" s="7" t="inlineStr">
-        <is>
-          <t>code.Spell_300001</t>
-        </is>
-      </c>
-      <c r="AE161" s="3" t="inlineStr">
-        <is>
-          <t>BaseAttack</t>
-        </is>
-      </c>
-      <c r="AG161" s="3" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
+      <c r="F161" s="98" t="n"/>
+      <c r="G161" s="98" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="H161" s="98" t="n"/>
+      <c r="I161" s="98" t="n"/>
+      <c r="J161" s="99" t="n"/>
+      <c r="K161" s="99" t="n"/>
+      <c r="L161" s="98" t="n"/>
+      <c r="M161" s="98" t="n"/>
+      <c r="N161" s="98" t="n"/>
+      <c r="O161" s="98" t="n"/>
+      <c r="P161" s="98" t="n"/>
+      <c r="Q161" s="98" t="n"/>
+      <c r="R161" s="98" t="n"/>
+      <c r="S161" s="98" t="n"/>
+      <c r="T161" s="98" t="n"/>
+      <c r="U161" s="99" t="n"/>
+      <c r="V161" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="W161" s="98" t="n"/>
+      <c r="X161" s="98" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y161" s="98" t="n"/>
+      <c r="Z161" s="98" t="n"/>
+      <c r="AA161" s="98" t="n"/>
+      <c r="AB161" s="98" t="n"/>
+      <c r="AC161" s="98" t="n"/>
+      <c r="AD161" s="98" t="n"/>
+      <c r="AE161" s="98" t="n"/>
+      <c r="AF161" s="98" t="n"/>
+      <c r="AG161" s="98" t="n"/>
+      <c r="AH161" s="98" t="n"/>
+      <c r="AI161" s="98" t="n"/>
+      <c r="AJ161" s="98" t="n"/>
+      <c r="AK161" s="98" t="n"/>
+      <c r="AL161" s="98" t="n"/>
     </row>
     <row r="162" ht="32.25" customHeight="1" s="57">
       <c r="A162" s="6" t="n">
-        <v>900024</v>
+        <v>900023</v>
       </c>
       <c r="B162" s="43" t="inlineStr">
         <is>
-          <t>冰清决</t>
+          <t>水清决</t>
         </is>
       </c>
       <c r="C162" s="6" t="n"/>
@@ -30205,11 +30233,11 @@
     </row>
     <row r="163" ht="32.25" customHeight="1" s="57">
       <c r="A163" s="6" t="n">
-        <v>900025</v>
+        <v>900024</v>
       </c>
       <c r="B163" s="43" t="inlineStr">
         <is>
-          <t>玉清诀</t>
+          <t>冰清决</t>
         </is>
       </c>
       <c r="C163" s="6" t="n"/>
@@ -30272,11 +30300,11 @@
     </row>
     <row r="164" ht="32.25" customHeight="1" s="57">
       <c r="A164" s="6" t="n">
-        <v>900026</v>
+        <v>900025</v>
       </c>
       <c r="B164" s="43" t="inlineStr">
         <is>
-          <t>晶清决</t>
+          <t>玉清诀</t>
         </is>
       </c>
       <c r="C164" s="6" t="n"/>
@@ -30339,11 +30367,11 @@
     </row>
     <row r="165" ht="32.25" customHeight="1" s="57">
       <c r="A165" s="6" t="n">
-        <v>900027</v>
+        <v>900026</v>
       </c>
       <c r="B165" s="43" t="inlineStr">
         <is>
-          <t>笑里藏刀</t>
+          <t>晶清决</t>
         </is>
       </c>
       <c r="C165" s="6" t="n"/>
@@ -30406,11 +30434,11 @@
     </row>
     <row r="166" ht="32.25" customHeight="1" s="57">
       <c r="A166" s="6" t="n">
-        <v>900028</v>
+        <v>900027</v>
       </c>
       <c r="B166" s="43" t="inlineStr">
         <is>
-          <t>野兽之力</t>
+          <t>笑里藏刀</t>
         </is>
       </c>
       <c r="C166" s="6" t="n"/>
@@ -30473,11 +30501,11 @@
     </row>
     <row r="167" ht="32.25" customHeight="1" s="57">
       <c r="A167" s="6" t="n">
-        <v>900029</v>
+        <v>900028</v>
       </c>
       <c r="B167" s="43" t="inlineStr">
         <is>
-          <t>魔兽之印</t>
+          <t>野兽之力</t>
         </is>
       </c>
       <c r="C167" s="6" t="n"/>
@@ -30540,11 +30568,11 @@
     </row>
     <row r="168" ht="32.25" customHeight="1" s="57">
       <c r="A168" s="6" t="n">
-        <v>900030</v>
+        <v>900029</v>
       </c>
       <c r="B168" s="43" t="inlineStr">
         <is>
-          <t>圣甲之灵</t>
+          <t>魔兽之印</t>
         </is>
       </c>
       <c r="C168" s="6" t="n"/>
@@ -30607,11 +30635,11 @@
     </row>
     <row r="169" ht="32.25" customHeight="1" s="57">
       <c r="A169" s="6" t="n">
-        <v>900031</v>
+        <v>900030</v>
       </c>
       <c r="B169" s="43" t="inlineStr">
         <is>
-          <t>罗汉金钟</t>
+          <t>圣甲之灵</t>
         </is>
       </c>
       <c r="C169" s="6" t="n"/>
@@ -30674,11 +30702,11 @@
     </row>
     <row r="170" ht="32.25" customHeight="1" s="57">
       <c r="A170" s="6" t="n">
-        <v>900032</v>
+        <v>900031</v>
       </c>
       <c r="B170" s="43" t="inlineStr">
         <is>
-          <t>放下屠刀</t>
+          <t>罗汉金钟</t>
         </is>
       </c>
       <c r="C170" s="6" t="n"/>
@@ -30741,11 +30769,11 @@
     </row>
     <row r="171" ht="32.25" customHeight="1" s="57">
       <c r="A171" s="6" t="n">
-        <v>900033</v>
+        <v>900032</v>
       </c>
       <c r="B171" s="43" t="inlineStr">
         <is>
-          <t>破血狂攻</t>
+          <t>放下屠刀</t>
         </is>
       </c>
       <c r="C171" s="6" t="n"/>
@@ -30808,11 +30836,11 @@
     </row>
     <row r="172" ht="32.25" customHeight="1" s="57">
       <c r="A172" s="6" t="n">
-        <v>900034</v>
+        <v>900033</v>
       </c>
       <c r="B172" s="43" t="inlineStr">
         <is>
-          <t>弱点击破</t>
+          <t>破血狂攻</t>
         </is>
       </c>
       <c r="C172" s="6" t="n"/>
@@ -30875,11 +30903,11 @@
     </row>
     <row r="173" ht="32.25" customHeight="1" s="57">
       <c r="A173" s="6" t="n">
-        <v>900035</v>
+        <v>900034</v>
       </c>
       <c r="B173" s="43" t="inlineStr">
         <is>
-          <t>破碎无双</t>
+          <t>弱点击破</t>
         </is>
       </c>
       <c r="C173" s="6" t="n"/>
@@ -30942,11 +30970,11 @@
     </row>
     <row r="174" ht="32.25" customHeight="1" s="57">
       <c r="A174" s="6" t="n">
-        <v>900036</v>
+        <v>900035</v>
       </c>
       <c r="B174" s="43" t="inlineStr">
         <is>
-          <t>气疗术</t>
+          <t>破碎无双</t>
         </is>
       </c>
       <c r="C174" s="6" t="n"/>
@@ -30957,7 +30985,7 @@
       </c>
       <c r="E174" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F174" s="19" t="n"/>
@@ -31013,11 +31041,11 @@
     </row>
     <row r="175" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A175" s="6" t="n">
-        <v>900037</v>
+        <v>900036</v>
       </c>
       <c r="B175" s="43" t="inlineStr">
         <is>
-          <t>心疗术</t>
+          <t>气疗术</t>
         </is>
       </c>
       <c r="C175" s="6" t="n"/>
@@ -31087,11 +31115,11 @@
     </row>
     <row r="176" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A176" s="6" t="n">
-        <v>900038</v>
+        <v>900037</v>
       </c>
       <c r="B176" s="43" t="inlineStr">
         <is>
-          <t>命疗术</t>
+          <t>心疗术</t>
         </is>
       </c>
       <c r="C176" s="6" t="n"/>
@@ -31161,11 +31189,11 @@
     </row>
     <row r="177" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A177" s="6" t="n">
-        <v>900039</v>
+        <v>900038</v>
       </c>
       <c r="B177" s="43" t="inlineStr">
         <is>
-          <t>起死回生</t>
+          <t>命疗术</t>
         </is>
       </c>
       <c r="C177" s="6" t="n"/>
@@ -31235,11 +31263,11 @@
     </row>
     <row r="178" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A178" s="6" t="n">
-        <v>900040</v>
+        <v>900039</v>
       </c>
       <c r="B178" s="43" t="inlineStr">
         <is>
-          <t>回魂咒</t>
+          <t>起死回生</t>
         </is>
       </c>
       <c r="C178" s="6" t="n"/>
@@ -31309,11 +31337,11 @@
     </row>
     <row r="179" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A179" s="6" t="n">
-        <v>900041</v>
+        <v>900040</v>
       </c>
       <c r="B179" s="43" t="inlineStr">
         <is>
-          <t>测试技能</t>
+          <t>回魂咒</t>
         </is>
       </c>
       <c r="C179" s="6" t="n"/>
@@ -31324,7 +31352,7 @@
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F179" s="19" t="n"/>
@@ -31334,6 +31362,11 @@
       <c r="J179" s="43" t="n"/>
       <c r="K179" s="43" t="n"/>
       <c r="L179" s="0" t="n"/>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>CurrMP,1,10</t>
+        </is>
+      </c>
       <c r="O179" s="3" t="inlineStr">
         <is>
           <t>enemy</t>
@@ -31383,154 +31416,233 @@
     </row>
     <row r="180" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A180" s="6" t="n">
-        <v>1145142</v>
-      </c>
-      <c r="B180" s="6" t="inlineStr">
+        <v>900041</v>
+      </c>
+      <c r="B180" s="43" t="inlineStr">
         <is>
           <t>测试技能</t>
         </is>
       </c>
-      <c r="C180" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D180" s="98" t="n"/>
-      <c r="E180" s="0" t="inlineStr">
+      <c r="C180" s="6" t="n"/>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>damage,int</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="F180" s="0" t="inlineStr">
-        <is>
-          <t>attack_damage</t>
-        </is>
-      </c>
-      <c r="G180" s="0" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H180" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="F180" s="19" t="n"/>
+      <c r="G180" s="19" t="n"/>
+      <c r="H180" s="19" t="n"/>
       <c r="I180" s="19" t="n"/>
-      <c r="J180" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" s="19" t="n"/>
-      <c r="L180" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="J180" s="43" t="n"/>
+      <c r="K180" s="43" t="n"/>
+      <c r="L180" s="0" t="n"/>
       <c r="M180" s="98" t="n"/>
       <c r="N180" s="98" t="n"/>
-      <c r="O180" s="11" t="n"/>
+      <c r="O180" s="3" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
       <c r="P180" s="98" t="n"/>
-      <c r="Q180" s="11" t="n"/>
+      <c r="Q180" s="3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
       <c r="R180" s="98" t="n"/>
-      <c r="S180" s="11" t="n"/>
-      <c r="T180" s="0" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="U180" s="11" t="n"/>
-      <c r="V180" s="11" t="n"/>
-      <c r="W180" s="11" t="n"/>
-      <c r="X180" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y180" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="S180" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+      <c r="T180" s="0" t="n"/>
+      <c r="U180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X180" s="0" t="n"/>
+      <c r="Y180" s="0" t="n"/>
       <c r="Z180" s="98" t="n"/>
       <c r="AA180" s="98" t="n"/>
-      <c r="AB180" s="19" t="n"/>
+      <c r="AB180" s="7" t="inlineStr">
+        <is>
+          <t>code.Spell_300001</t>
+        </is>
+      </c>
       <c r="AC180" s="98" t="n"/>
       <c r="AD180" s="98" t="n"/>
-      <c r="AE180" s="11" t="n"/>
-      <c r="AF180" s="0" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AG180" s="11" t="n"/>
-      <c r="AH180" s="98" t="n"/>
+      <c r="AE180" s="3" t="inlineStr">
+        <is>
+          <t>BaseAttack</t>
+        </is>
+      </c>
+      <c r="AF180" s="0" t="n"/>
+      <c r="AG180" s="3" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="AH180" s="11" t="n"/>
       <c r="AI180" s="21" t="n"/>
       <c r="AJ180" s="98" t="n"/>
       <c r="AK180" s="21" t="n"/>
       <c r="AL180" s="98" t="n"/>
     </row>
     <row r="181" ht="16.5" customHeight="1" s="57">
-      <c r="A181" s="98" t="n"/>
-      <c r="B181" s="98" t="n"/>
-      <c r="C181" s="98" t="n">
+      <c r="A181" s="6" t="n">
+        <v>1145142</v>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>测试技能</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D181" s="98" t="n"/>
-      <c r="E181" s="98" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="F181" s="98" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="G181" s="98" t="inlineStr">
+      <c r="E181" s="0" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="F181" s="0" t="inlineStr">
+        <is>
+          <t>attack_damage</t>
+        </is>
+      </c>
+      <c r="G181" s="0" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="H181" s="98" t="b">
+      <c r="H181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" s="19" t="n"/>
+      <c r="J181" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I181" s="98" t="n"/>
-      <c r="J181" s="99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" s="99" t="n"/>
-      <c r="L181" s="98" t="b">
+      <c r="K181" s="19" t="n"/>
+      <c r="L181" s="0" t="n">
         <v>0</v>
       </c>
       <c r="M181" s="98" t="n"/>
       <c r="N181" s="98" t="n"/>
-      <c r="O181" s="98" t="n"/>
+      <c r="O181" s="11" t="n"/>
       <c r="P181" s="98" t="n"/>
-      <c r="Q181" s="98" t="n"/>
+      <c r="Q181" s="11" t="n"/>
       <c r="R181" s="98" t="n"/>
-      <c r="S181" s="98" t="n"/>
-      <c r="T181" s="98" t="n"/>
-      <c r="U181" s="99" t="n"/>
-      <c r="V181" s="98" t="n"/>
-      <c r="W181" s="98" t="n"/>
-      <c r="X181" s="98" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y181" s="98" t="n">
+      <c r="S181" s="11" t="n"/>
+      <c r="T181" s="0" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="U181" s="11" t="n"/>
+      <c r="V181" s="11" t="n"/>
+      <c r="W181" s="11" t="n"/>
+      <c r="X181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y181" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Z181" s="98" t="n"/>
       <c r="AA181" s="98" t="n"/>
-      <c r="AB181" s="98" t="n"/>
+      <c r="AB181" s="19" t="n"/>
       <c r="AC181" s="98" t="n"/>
       <c r="AD181" s="98" t="n"/>
-      <c r="AE181" s="98" t="n"/>
-      <c r="AF181" s="98" t="inlineStr">
+      <c r="AE181" s="11" t="n"/>
+      <c r="AF181" s="0" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="AG181" s="98" t="n"/>
+      <c r="AG181" s="11" t="n"/>
       <c r="AH181" s="98" t="n"/>
-      <c r="AI181" s="98" t="n"/>
+      <c r="AI181" s="21" t="n"/>
       <c r="AJ181" s="98" t="n"/>
-      <c r="AK181" s="98" t="n"/>
+      <c r="AK181" s="21" t="n"/>
       <c r="AL181" s="98" t="n"/>
     </row>
     <row r="182" ht="16.5" customHeight="1" s="57">
-      <c r="A182" s="6" t="n"/>
-      <c r="B182" s="6" t="n"/>
-      <c r="C182" s="6" t="n"/>
+      <c r="A182" s="98" t="n"/>
+      <c r="B182" s="98" t="n"/>
+      <c r="C182" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" s="98" t="n"/>
+      <c r="E182" s="98" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F182" s="98" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G182" s="98" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H182" s="98" t="b">
+        <v>0</v>
+      </c>
+      <c r="I182" s="98" t="n"/>
+      <c r="J182" s="99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" s="99" t="n"/>
+      <c r="L182" s="98" t="b">
+        <v>0</v>
+      </c>
+      <c r="M182" s="98" t="n"/>
+      <c r="N182" s="98" t="n"/>
+      <c r="O182" s="98" t="n"/>
+      <c r="P182" s="98" t="n"/>
+      <c r="Q182" s="98" t="n"/>
+      <c r="R182" s="98" t="n"/>
+      <c r="S182" s="98" t="n"/>
+      <c r="T182" s="98" t="n"/>
+      <c r="U182" s="99" t="n"/>
+      <c r="V182" s="98" t="n"/>
+      <c r="W182" s="98" t="n"/>
+      <c r="X182" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y182" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z182" s="98" t="n"/>
+      <c r="AA182" s="98" t="n"/>
+      <c r="AB182" s="98" t="n"/>
+      <c r="AC182" s="98" t="n"/>
+      <c r="AD182" s="98" t="n"/>
+      <c r="AE182" s="98" t="n"/>
+      <c r="AF182" s="98" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AG182" s="98" t="n"/>
+      <c r="AH182" s="98" t="n"/>
+      <c r="AI182" s="98" t="n"/>
+      <c r="AJ182" s="98" t="n"/>
+      <c r="AK182" s="98" t="n"/>
+      <c r="AL182" s="98" t="n"/>
     </row>
     <row r="183" ht="16.5" customHeight="1" s="57">
       <c r="A183" s="6" t="n"/>

--- a/resources/combat/spell.xlsx
+++ b/resources/combat/spell.xlsx
@@ -3900,7 +3900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E589"/>
+  <dimension ref="A1:E591"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" style="42" min="1" max="1"/>
@@ -12549,54 +12549,38 @@
       </c>
     </row>
     <row r="377" ht="16.5" customHeight="1" s="57">
-      <c r="A377" s="6" t="n">
-        <v>100001</v>
+      <c r="A377" s="42" t="n">
+        <v>8600</v>
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>物理暴击 + {rate}%</t>
-        </is>
-      </c>
-      <c r="C377" s="30" t="inlineStr">
-        <is>
-          <t>装备特效</t>
-        </is>
-      </c>
+          <t>焚天决·起手</t>
+        </is>
+      </c>
+      <c r="C377" s="30" t="n"/>
       <c r="D377" s="0" t="n"/>
-      <c r="E377" s="30" t="inlineStr">
-        <is>
-          <t>装备特效</t>
-        </is>
-      </c>
+      <c r="E377" s="30" t="n"/>
     </row>
     <row r="378" ht="16.5" customHeight="1" s="57">
-      <c r="A378" s="6" t="n">
-        <v>100002</v>
+      <c r="A378" s="42" t="n">
+        <v>8601</v>
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>法术暴击 + {rate}%</t>
-        </is>
-      </c>
-      <c r="C378" s="30" t="inlineStr">
-        <is>
-          <t>装备特效</t>
-        </is>
-      </c>
+          <t>焚天决·进阶</t>
+        </is>
+      </c>
+      <c r="C378" s="30" t="n"/>
       <c r="D378" s="0" t="n"/>
-      <c r="E378" s="30" t="inlineStr">
-        <is>
-          <t>装备特效</t>
-        </is>
-      </c>
+      <c r="E378" s="30" t="n"/>
     </row>
     <row r="379" ht="16.5" customHeight="1" s="57">
       <c r="A379" s="6" t="n">
-        <v>100003</v>
+        <v>100001</v>
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>物理抗暴 + {rate}%</t>
+          <t>物理暴击 + {rate}%</t>
         </is>
       </c>
       <c r="C379" s="30" t="inlineStr">
@@ -12613,11 +12597,11 @@
     </row>
     <row r="380" ht="16.5" customHeight="1" s="57">
       <c r="A380" s="6" t="n">
-        <v>100004</v>
+        <v>100002</v>
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>法术抗暴 + {rate}%</t>
+          <t>法术暴击 + {rate}%</t>
         </is>
       </c>
       <c r="C380" s="30" t="inlineStr">
@@ -12634,11 +12618,11 @@
     </row>
     <row r="381" ht="16.5" customHeight="1" s="57">
       <c r="A381" s="6" t="n">
-        <v>100005</v>
+        <v>100003</v>
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>封印命中 + {seal}</t>
+          <t>物理抗暴 + {rate}%</t>
         </is>
       </c>
       <c r="C381" s="30" t="inlineStr">
@@ -12655,11 +12639,11 @@
     </row>
     <row r="382" ht="16.5" customHeight="1" s="57">
       <c r="A382" s="6" t="n">
-        <v>100006</v>
+        <v>100004</v>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>抵抗封印 + {seal}</t>
+          <t>法术抗暴 + {rate}%</t>
         </is>
       </c>
       <c r="C382" s="30" t="inlineStr">
@@ -12676,11 +12660,11 @@
     </row>
     <row r="383" ht="16.5" customHeight="1" s="57">
       <c r="A383" s="6" t="n">
-        <v>100007</v>
+        <v>100005</v>
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>物理伤害 + {rate}%</t>
+          <t>封印命中 + {seal}</t>
         </is>
       </c>
       <c r="C383" s="30" t="inlineStr">
@@ -12697,11 +12681,11 @@
     </row>
     <row r="384" ht="16.5" customHeight="1" s="57">
       <c r="A384" s="6" t="n">
-        <v>100008</v>
+        <v>100006</v>
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>法术伤害 + {rate}%</t>
+          <t>抵抗封印 + {seal}</t>
         </is>
       </c>
       <c r="C384" s="30" t="inlineStr">
@@ -12718,11 +12702,11 @@
     </row>
     <row r="385" ht="16.5" customHeight="1" s="57">
       <c r="A385" s="6" t="n">
-        <v>100009</v>
+        <v>100007</v>
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>物理防御 + {rate}%</t>
+          <t>物理伤害 + {rate}%</t>
         </is>
       </c>
       <c r="C385" s="30" t="inlineStr">
@@ -12739,11 +12723,11 @@
     </row>
     <row r="386" ht="16.5" customHeight="1" s="57">
       <c r="A386" s="6" t="n">
-        <v>100010</v>
+        <v>100008</v>
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>法术防御 + {rate}%</t>
+          <t>法术伤害 + {rate}%</t>
         </is>
       </c>
       <c r="C386" s="30" t="inlineStr">
@@ -12760,11 +12744,11 @@
     </row>
     <row r="387" ht="16.5" customHeight="1" s="57">
       <c r="A387" s="6" t="n">
-        <v>100011</v>
+        <v>100009</v>
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>治疗强度 + {rate}%</t>
+          <t>物理防御 + {rate}%</t>
         </is>
       </c>
       <c r="C387" s="30" t="inlineStr">
@@ -12781,11 +12765,11 @@
     </row>
     <row r="388" ht="16.5" customHeight="1" s="57">
       <c r="A388" s="6" t="n">
-        <v>100012</v>
+        <v>100010</v>
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>暴击倍率 + {rate}%</t>
+          <t>法术防御 + {rate}%</t>
         </is>
       </c>
       <c r="C388" s="30" t="inlineStr">
@@ -12802,11 +12786,11 @@
     </row>
     <row r="389" ht="16.5" customHeight="1" s="57">
       <c r="A389" s="6" t="n">
-        <v>100013</v>
+        <v>100011</v>
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>物理攻击 + {rate}%</t>
+          <t>治疗强度 + {rate}%</t>
         </is>
       </c>
       <c r="C389" s="30" t="inlineStr">
@@ -12823,11 +12807,11 @@
     </row>
     <row r="390" ht="16.5" customHeight="1" s="57">
       <c r="A390" s="6" t="n">
-        <v>100014</v>
+        <v>100012</v>
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>法术攻击 + {rate}%</t>
+          <t>暴击倍率 + {rate}%</t>
         </is>
       </c>
       <c r="C390" s="30" t="inlineStr">
@@ -12844,11 +12828,11 @@
     </row>
     <row r="391" ht="16.5" customHeight="1" s="57">
       <c r="A391" s="6" t="n">
-        <v>100015</v>
+        <v>100013</v>
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>物理暴击 + {rate}%</t>
+          <t>物理攻击 + {rate}%</t>
         </is>
       </c>
       <c r="C391" s="30" t="inlineStr">
@@ -12865,11 +12849,11 @@
     </row>
     <row r="392" ht="16.5" customHeight="1" s="57">
       <c r="A392" s="6" t="n">
-        <v>100016</v>
+        <v>100014</v>
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>法术暴击 + {rate}%</t>
+          <t>法术攻击 + {rate}%</t>
         </is>
       </c>
       <c r="C392" s="30" t="inlineStr">
@@ -12886,11 +12870,11 @@
     </row>
     <row r="393" ht="16.5" customHeight="1" s="57">
       <c r="A393" s="6" t="n">
-        <v>100017</v>
+        <v>100015</v>
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>物理抗暴 + {rate}%</t>
+          <t>物理暴击 + {rate}%</t>
         </is>
       </c>
       <c r="C393" s="30" t="inlineStr">
@@ -12907,11 +12891,11 @@
     </row>
     <row r="394" ht="16.5" customHeight="1" s="57">
       <c r="A394" s="6" t="n">
-        <v>100018</v>
+        <v>100016</v>
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>法术抗暴 + {rate}%</t>
+          <t>法术暴击 + {rate}%</t>
         </is>
       </c>
       <c r="C394" s="30" t="inlineStr">
@@ -12928,11 +12912,11 @@
     </row>
     <row r="395" ht="16.5" customHeight="1" s="57">
       <c r="A395" s="6" t="n">
-        <v>100019</v>
+        <v>100017</v>
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>封印命中 + {seal}</t>
+          <t>物理抗暴 + {rate}%</t>
         </is>
       </c>
       <c r="C395" s="30" t="inlineStr">
@@ -12949,11 +12933,11 @@
     </row>
     <row r="396" ht="16.5" customHeight="1" s="57">
       <c r="A396" s="6" t="n">
-        <v>100020</v>
+        <v>100018</v>
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>抵抗封印 + {seal}</t>
+          <t>法术抗暴 + {rate}%</t>
         </is>
       </c>
       <c r="C396" s="30" t="inlineStr">
@@ -12970,11 +12954,11 @@
     </row>
     <row r="397" ht="16.5" customHeight="1" s="57">
       <c r="A397" s="6" t="n">
-        <v>100021</v>
+        <v>100019</v>
       </c>
       <c r="B397" s="3" t="inlineStr">
         <is>
-          <t>物理伤害 + {rate}%</t>
+          <t>封印命中 + {seal}</t>
         </is>
       </c>
       <c r="C397" s="30" t="inlineStr">
@@ -12991,11 +12975,11 @@
     </row>
     <row r="398" ht="16.5" customHeight="1" s="57">
       <c r="A398" s="6" t="n">
-        <v>100022</v>
+        <v>100020</v>
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>法术伤害 + {rate}%</t>
+          <t>抵抗封印 + {seal}</t>
         </is>
       </c>
       <c r="C398" s="30" t="inlineStr">
@@ -13012,11 +12996,11 @@
     </row>
     <row r="399" ht="16.5" customHeight="1" s="57">
       <c r="A399" s="6" t="n">
-        <v>100023</v>
+        <v>100021</v>
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>物理防御 + {rate}%</t>
+          <t>物理伤害 + {rate}%</t>
         </is>
       </c>
       <c r="C399" s="30" t="inlineStr">
@@ -13033,11 +13017,11 @@
     </row>
     <row r="400" ht="16.5" customHeight="1" s="57">
       <c r="A400" s="6" t="n">
-        <v>100024</v>
+        <v>100022</v>
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>法术防御 + {rate}%</t>
+          <t>法术伤害 + {rate}%</t>
         </is>
       </c>
       <c r="C400" s="30" t="inlineStr">
@@ -13054,11 +13038,11 @@
     </row>
     <row r="401" ht="16.5" customHeight="1" s="57">
       <c r="A401" s="6" t="n">
-        <v>100025</v>
+        <v>100023</v>
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>治疗强度 + {rate}%</t>
+          <t>物理防御 + {rate}%</t>
         </is>
       </c>
       <c r="C401" s="30" t="inlineStr">
@@ -13075,11 +13059,11 @@
     </row>
     <row r="402" ht="16.5" customHeight="1" s="57">
       <c r="A402" s="6" t="n">
-        <v>100026</v>
+        <v>100024</v>
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>暴击倍率 + {rate}%</t>
+          <t>法术防御 + {rate}%</t>
         </is>
       </c>
       <c r="C402" s="30" t="inlineStr">
@@ -13096,11 +13080,11 @@
     </row>
     <row r="403" ht="16.5" customHeight="1" s="57">
       <c r="A403" s="6" t="n">
-        <v>100027</v>
+        <v>100025</v>
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
-          <t>物理攻击 + {rate}%</t>
+          <t>治疗强度 + {rate}%</t>
         </is>
       </c>
       <c r="C403" s="30" t="inlineStr">
@@ -13117,11 +13101,11 @@
     </row>
     <row r="404" ht="16.5" customHeight="1" s="57">
       <c r="A404" s="6" t="n">
-        <v>100028</v>
+        <v>100026</v>
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>法术攻击 + {rate}%</t>
+          <t>暴击倍率 + {rate}%</t>
         </is>
       </c>
       <c r="C404" s="30" t="inlineStr">
@@ -13137,138 +13121,138 @@
       </c>
     </row>
     <row r="405" ht="16.5" customHeight="1" s="57">
-      <c r="A405" s="32" t="n">
-        <v>110001</v>
-      </c>
-      <c r="B405" s="33" t="inlineStr">
-        <is>
-          <t>加血条</t>
-        </is>
-      </c>
-      <c r="C405" s="34" t="inlineStr">
-        <is>
-          <t>增加生命上限</t>
+      <c r="A405" s="6" t="n">
+        <v>100027</v>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
+          <t>物理攻击 + {rate}%</t>
+        </is>
+      </c>
+      <c r="C405" s="30" t="inlineStr">
+        <is>
+          <t>装备特效</t>
         </is>
       </c>
       <c r="D405" s="0" t="n"/>
-      <c r="E405" s="34" t="inlineStr">
-        <is>
-          <t>增加生命上限</t>
+      <c r="E405" s="30" t="inlineStr">
+        <is>
+          <t>装备特效</t>
         </is>
       </c>
     </row>
     <row r="406" ht="16.5" customHeight="1" s="57">
-      <c r="A406" s="32" t="n">
-        <v>110002</v>
-      </c>
-      <c r="B406" s="33" t="inlineStr">
-        <is>
-          <t>吸血</t>
-        </is>
-      </c>
-      <c r="C406" s="34" t="inlineStr">
-        <is>
-          <t>攻击时吸血，回复值等于真实攻击值</t>
+      <c r="A406" s="6" t="n">
+        <v>100028</v>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>法术攻击 + {rate}%</t>
+        </is>
+      </c>
+      <c r="C406" s="30" t="inlineStr">
+        <is>
+          <t>装备特效</t>
         </is>
       </c>
       <c r="D406" s="0" t="n"/>
-      <c r="E406" s="34" t="inlineStr">
-        <is>
-          <t>攻击时吸血，回复值等于真实攻击值</t>
+      <c r="E406" s="30" t="inlineStr">
+        <is>
+          <t>装备特效</t>
         </is>
       </c>
     </row>
     <row r="407" ht="16.5" customHeight="1" s="57">
       <c r="A407" s="32" t="n">
-        <v>110003</v>
+        <v>110001</v>
       </c>
       <c r="B407" s="33" t="inlineStr">
         <is>
-          <t>单体穿透</t>
+          <t>加血条</t>
         </is>
       </c>
       <c r="C407" s="34" t="inlineStr">
         <is>
-          <t>使用单体技能时，额外增加{rate}%的物法穿透</t>
+          <t>增加生命上限</t>
         </is>
       </c>
       <c r="D407" s="0" t="n"/>
       <c r="E407" s="34" t="inlineStr">
         <is>
-          <t>使用单体技能时，额外增加{rate}%的物法穿透</t>
+          <t>增加生命上限</t>
         </is>
       </c>
     </row>
     <row r="408" ht="16.5" customHeight="1" s="57">
       <c r="A408" s="32" t="n">
-        <v>110004</v>
+        <v>110002</v>
       </c>
       <c r="B408" s="33" t="inlineStr">
         <is>
-          <t>疾速穿透</t>
+          <t>吸血</t>
         </is>
       </c>
       <c r="C408" s="34" t="inlineStr">
         <is>
-          <t>攻击速度较快单位时，额外增加{rate}%的物法穿透</t>
+          <t>攻击时吸血，回复值等于真实攻击值</t>
         </is>
       </c>
       <c r="D408" s="0" t="n"/>
       <c r="E408" s="34" t="inlineStr">
         <is>
+          <t>攻击时吸血，回复值等于真实攻击值</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" ht="16.5" customHeight="1" s="57">
+      <c r="A409" s="32" t="n">
+        <v>110003</v>
+      </c>
+      <c r="B409" s="33" t="inlineStr">
+        <is>
+          <t>单体穿透</t>
+        </is>
+      </c>
+      <c r="C409" s="34" t="inlineStr">
+        <is>
+          <t>使用单体技能时，额外增加{rate}%的物法穿透</t>
+        </is>
+      </c>
+      <c r="D409" s="0" t="n"/>
+      <c r="E409" s="34" t="inlineStr">
+        <is>
+          <t>使用单体技能时，额外增加{rate}%的物法穿透</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="16.5" customHeight="1" s="57">
+      <c r="A410" s="32" t="n">
+        <v>110004</v>
+      </c>
+      <c r="B410" s="33" t="inlineStr">
+        <is>
+          <t>疾速穿透</t>
+        </is>
+      </c>
+      <c r="C410" s="34" t="inlineStr">
+        <is>
           <t>攻击速度较快单位时，额外增加{rate}%的物法穿透</t>
         </is>
       </c>
-    </row>
-    <row r="409" ht="16.5" customHeight="1" s="57">
-      <c r="A409" s="21" t="n">
-        <v>200002</v>
-      </c>
-      <c r="B409" s="19" t="inlineStr">
-        <is>
-          <t>反击</t>
-        </is>
-      </c>
-      <c r="C409" s="20" t="inlineStr">
-        <is>
-          <t>机制技能</t>
-        </is>
-      </c>
-      <c r="D409" s="19" t="n"/>
-      <c r="E409" s="20" t="inlineStr">
-        <is>
-          <t>机制技能</t>
-        </is>
-      </c>
-    </row>
-    <row r="410" ht="16.5" customHeight="1" s="57">
-      <c r="A410" s="21" t="n">
-        <v>200003</v>
-      </c>
-      <c r="B410" s="19" t="inlineStr">
-        <is>
-          <t>反震</t>
-        </is>
-      </c>
-      <c r="C410" s="20" t="inlineStr">
-        <is>
-          <t>机制技能</t>
-        </is>
-      </c>
-      <c r="D410" s="19" t="n"/>
-      <c r="E410" s="20" t="inlineStr">
-        <is>
-          <t>机制技能</t>
+      <c r="D410" s="0" t="n"/>
+      <c r="E410" s="34" t="inlineStr">
+        <is>
+          <t>攻击速度较快单位时，额外增加{rate}%的物法穿透</t>
         </is>
       </c>
     </row>
     <row r="411" ht="16.5" customHeight="1" s="57">
       <c r="A411" s="21" t="n">
-        <v>200004</v>
+        <v>200002</v>
       </c>
       <c r="B411" s="19" t="inlineStr">
         <is>
-          <t>法术反击</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="C411" s="20" t="inlineStr">
@@ -13285,11 +13269,11 @@
     </row>
     <row r="412" ht="16.5" customHeight="1" s="57">
       <c r="A412" s="21" t="n">
-        <v>200005</v>
+        <v>200003</v>
       </c>
       <c r="B412" s="19" t="inlineStr">
         <is>
-          <t>物理追击</t>
+          <t>反震</t>
         </is>
       </c>
       <c r="C412" s="20" t="inlineStr">
@@ -13306,11 +13290,11 @@
     </row>
     <row r="413" ht="16.5" customHeight="1" s="57">
       <c r="A413" s="21" t="n">
-        <v>200006</v>
+        <v>200004</v>
       </c>
       <c r="B413" s="19" t="inlineStr">
         <is>
-          <t>法术追击</t>
+          <t>法术反击</t>
         </is>
       </c>
       <c r="C413" s="20" t="inlineStr">
@@ -13327,11 +13311,11 @@
     </row>
     <row r="414" ht="16.5" customHeight="1" s="57">
       <c r="A414" s="21" t="n">
-        <v>200007</v>
+        <v>200005</v>
       </c>
       <c r="B414" s="19" t="inlineStr">
         <is>
-          <t>召唤宠物</t>
+          <t>物理追击</t>
         </is>
       </c>
       <c r="C414" s="20" t="inlineStr">
@@ -13347,75 +13331,75 @@
       </c>
     </row>
     <row r="415" ht="16.5" customHeight="1" s="57">
-      <c r="A415" s="36" t="n">
+      <c r="A415" s="21" t="n">
+        <v>200006</v>
+      </c>
+      <c r="B415" s="19" t="inlineStr">
+        <is>
+          <t>法术追击</t>
+        </is>
+      </c>
+      <c r="C415" s="20" t="inlineStr">
+        <is>
+          <t>机制技能</t>
+        </is>
+      </c>
+      <c r="D415" s="19" t="n"/>
+      <c r="E415" s="20" t="inlineStr">
+        <is>
+          <t>机制技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="16.5" customHeight="1" s="57">
+      <c r="A416" s="21" t="n">
+        <v>200007</v>
+      </c>
+      <c r="B416" s="19" t="inlineStr">
+        <is>
+          <t>召唤宠物</t>
+        </is>
+      </c>
+      <c r="C416" s="20" t="inlineStr">
+        <is>
+          <t>机制技能</t>
+        </is>
+      </c>
+      <c r="D416" s="19" t="n"/>
+      <c r="E416" s="20" t="inlineStr">
+        <is>
+          <t>机制技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="16.5" customHeight="1" s="57">
+      <c r="A417" s="36" t="n">
         <v>210001</v>
       </c>
-      <c r="B415" s="37" t="inlineStr">
+      <c r="B417" s="37" t="inlineStr">
         <is>
           <t>闪现被动辅助</t>
         </is>
       </c>
-      <c r="C415" s="38" t="inlineStr">
+      <c r="C417" s="38" t="inlineStr">
         <is>
           <t>用于辅助闪被动的实现，加在宠物主人英雄上</t>
         </is>
       </c>
-      <c r="D415" s="16" t="n"/>
-      <c r="E415" s="38" t="inlineStr">
+      <c r="D417" s="16" t="n"/>
+      <c r="E417" s="38" t="inlineStr">
         <is>
           <t>用于辅助闪被动的实现，加在宠物主人英雄上</t>
-        </is>
-      </c>
-    </row>
-    <row r="416" ht="16.5" customHeight="1" s="57">
-      <c r="A416" s="6" t="n">
-        <v>600003</v>
-      </c>
-      <c r="B416" s="3" t="inlineStr">
-        <is>
-          <t>被动：共享</t>
-        </is>
-      </c>
-      <c r="C416" s="30" t="inlineStr">
-        <is>
-          <t>被动测试</t>
-        </is>
-      </c>
-      <c r="D416" s="0" t="n"/>
-      <c r="E416" s="30" t="inlineStr">
-        <is>
-          <t>被动测试</t>
-        </is>
-      </c>
-    </row>
-    <row r="417" ht="16.5" customHeight="1" s="57">
-      <c r="A417" s="6" t="n">
-        <v>600004</v>
-      </c>
-      <c r="B417" s="3" t="inlineStr">
-        <is>
-          <t>被动：独立</t>
-        </is>
-      </c>
-      <c r="C417" s="30" t="inlineStr">
-        <is>
-          <t>被动测试</t>
-        </is>
-      </c>
-      <c r="D417" s="0" t="n"/>
-      <c r="E417" s="30" t="inlineStr">
-        <is>
-          <t>被动测试</t>
         </is>
       </c>
     </row>
     <row r="418" ht="16.5" customHeight="1" s="57">
       <c r="A418" s="6" t="n">
-        <v>600005</v>
+        <v>600003</v>
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>被动：独立</t>
+          <t>被动：共享</t>
         </is>
       </c>
       <c r="C418" s="30" t="inlineStr">
@@ -13432,7 +13416,7 @@
     </row>
     <row r="419" ht="16.5" customHeight="1" s="57">
       <c r="A419" s="6" t="n">
-        <v>600006</v>
+        <v>600004</v>
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
@@ -13453,7 +13437,7 @@
     </row>
     <row r="420" ht="16.5" customHeight="1" s="57">
       <c r="A420" s="6" t="n">
-        <v>600007</v>
+        <v>600005</v>
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
@@ -13474,7 +13458,7 @@
     </row>
     <row r="421" ht="16.5" customHeight="1" s="57">
       <c r="A421" s="6" t="n">
-        <v>600008</v>
+        <v>600006</v>
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
@@ -13495,7 +13479,7 @@
     </row>
     <row r="422" ht="16.5" customHeight="1" s="57">
       <c r="A422" s="6" t="n">
-        <v>600009</v>
+        <v>600007</v>
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
@@ -13516,7 +13500,7 @@
     </row>
     <row r="423" ht="16.5" customHeight="1" s="57">
       <c r="A423" s="6" t="n">
-        <v>600010</v>
+        <v>600008</v>
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
@@ -13536,99 +13520,111 @@
       </c>
     </row>
     <row r="424" ht="16.5" customFormat="1" customHeight="1" s="68">
-      <c r="A424" s="65" t="n">
+      <c r="A424" s="6" t="n">
+        <v>600009</v>
+      </c>
+      <c r="B424" s="3" t="inlineStr">
+        <is>
+          <t>被动：独立</t>
+        </is>
+      </c>
+      <c r="C424" s="30" t="inlineStr">
+        <is>
+          <t>被动测试</t>
+        </is>
+      </c>
+      <c r="D424" s="0" t="n"/>
+      <c r="E424" s="30" t="inlineStr">
+        <is>
+          <t>被动测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="16.5" customHeight="1" s="57">
+      <c r="A425" s="6" t="n">
+        <v>600010</v>
+      </c>
+      <c r="B425" s="3" t="inlineStr">
+        <is>
+          <t>被动：独立</t>
+        </is>
+      </c>
+      <c r="C425" s="30" t="inlineStr">
+        <is>
+          <t>被动测试</t>
+        </is>
+      </c>
+      <c r="D425" s="0" t="n"/>
+      <c r="E425" s="30" t="inlineStr">
+        <is>
+          <t>被动测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="16.5" customHeight="1" s="57">
+      <c r="A426" s="65" t="n">
         <v>900001</v>
       </c>
-      <c r="B424" s="66" t="inlineStr">
+      <c r="B426" s="66" t="inlineStr">
         <is>
           <t>单体攻击</t>
         </is>
       </c>
-      <c r="C424" s="67" t="inlineStr">
+      <c r="C426" s="67" t="inlineStr">
         <is>
           <t>对单个目标造成100点伤害</t>
         </is>
       </c>
-      <c r="D424" s="66" t="n">
+      <c r="D426" s="66" t="n">
         <v>1001</v>
       </c>
-      <c r="E424" s="67" t="inlineStr">
+      <c r="E426" s="67" t="inlineStr">
         <is>
           <t>对单个目标造成100点伤害</t>
         </is>
       </c>
     </row>
-    <row r="425" ht="16.5" customHeight="1" s="57">
-      <c r="A425" s="42" t="n">
+    <row r="427" ht="16.5" customHeight="1" s="57">
+      <c r="A427" s="42" t="n">
         <v>900015</v>
       </c>
-      <c r="B425" s="3" t="inlineStr">
+      <c r="B427" s="3" t="inlineStr">
         <is>
           <t>朱雀流火</t>
         </is>
       </c>
-      <c r="C425" s="30" t="inlineStr">
+      <c r="C427" s="30" t="inlineStr">
         <is>
           <t>对 3 个目标各 160% 伤害</t>
         </is>
       </c>
-      <c r="D425" s="43" t="n"/>
-      <c r="E425" s="30" t="n"/>
-    </row>
-    <row r="426" ht="16.5" customHeight="1" s="57">
-      <c r="A426" s="42" t="n">
+      <c r="D427" s="43" t="n"/>
+      <c r="E427" s="30" t="n"/>
+    </row>
+    <row r="428" ht="16.5" customHeight="1" s="57">
+      <c r="A428" s="42" t="n">
         <v>900016</v>
       </c>
-      <c r="B426" s="3" t="inlineStr">
+      <c r="B428" s="3" t="inlineStr">
         <is>
           <t>朱雀焚天</t>
         </is>
       </c>
-      <c r="C426" s="30" t="inlineStr">
+      <c r="C428" s="30" t="inlineStr">
         <is>
           <t>「焚天朱雀」（原句：新增传说灵兽「焚天朱雀」，model_id 1075，品质 3、元素 fire，）</t>
         </is>
       </c>
-      <c r="D426" s="43" t="n"/>
-      <c r="E426" s="30" t="n"/>
-    </row>
-    <row r="427" ht="16.5" customHeight="1" s="57">
-      <c r="A427" s="6" t="n">
-        <v>900023</v>
-      </c>
-      <c r="B427" s="43" t="inlineStr">
-        <is>
-          <t>水清决</t>
-        </is>
-      </c>
-      <c r="D427" s="43" t="inlineStr">
-        <is>
-          <t>icon_spell_009</t>
-        </is>
-      </c>
-    </row>
-    <row r="428" ht="16.5" customHeight="1" s="57">
-      <c r="A428" s="6" t="n">
-        <v>900024</v>
-      </c>
-      <c r="B428" s="43" t="inlineStr">
-        <is>
-          <t>冰清决</t>
-        </is>
-      </c>
-      <c r="D428" s="43" t="inlineStr">
-        <is>
-          <t>icon_spell_009</t>
-        </is>
-      </c>
+      <c r="D428" s="43" t="n"/>
+      <c r="E428" s="30" t="n"/>
     </row>
     <row r="429" ht="16.5" customHeight="1" s="57">
       <c r="A429" s="6" t="n">
-        <v>900025</v>
+        <v>900023</v>
       </c>
       <c r="B429" s="43" t="inlineStr">
         <is>
-          <t>玉清诀</t>
+          <t>水清决</t>
         </is>
       </c>
       <c r="D429" s="43" t="inlineStr">
@@ -13639,11 +13635,11 @@
     </row>
     <row r="430" ht="16.5" customHeight="1" s="57">
       <c r="A430" s="6" t="n">
-        <v>900026</v>
+        <v>900024</v>
       </c>
       <c r="B430" s="43" t="inlineStr">
         <is>
-          <t>晶清决</t>
+          <t>冰清决</t>
         </is>
       </c>
       <c r="D430" s="43" t="inlineStr">
@@ -13654,176 +13650,176 @@
     </row>
     <row r="431" ht="16.5" customHeight="1" s="57">
       <c r="A431" s="6" t="n">
-        <v>900027</v>
+        <v>900025</v>
       </c>
       <c r="B431" s="43" t="inlineStr">
         <is>
-          <t>笑里藏刀</t>
+          <t>玉清诀</t>
         </is>
       </c>
       <c r="D431" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_012</t>
+          <t>icon_spell_009</t>
         </is>
       </c>
     </row>
     <row r="432" ht="16.5" customHeight="1" s="57">
       <c r="A432" s="6" t="n">
-        <v>900028</v>
+        <v>900026</v>
       </c>
       <c r="B432" s="43" t="inlineStr">
         <is>
-          <t>野兽之力</t>
+          <t>晶清决</t>
         </is>
       </c>
       <c r="D432" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_016</t>
+          <t>icon_spell_009</t>
         </is>
       </c>
     </row>
     <row r="433" ht="16.5" customHeight="1" s="57">
       <c r="A433" s="6" t="n">
-        <v>900029</v>
+        <v>900027</v>
       </c>
       <c r="B433" s="43" t="inlineStr">
         <is>
-          <t>魔兽之印</t>
+          <t>笑里藏刀</t>
         </is>
       </c>
       <c r="D433" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_015</t>
+          <t>icon_spell_012</t>
         </is>
       </c>
     </row>
     <row r="434" ht="16.5" customHeight="1" s="57">
       <c r="A434" s="6" t="n">
-        <v>900030</v>
+        <v>900028</v>
       </c>
       <c r="B434" s="43" t="inlineStr">
         <is>
-          <t>圣甲之灵</t>
+          <t>野兽之力</t>
         </is>
       </c>
       <c r="D434" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_019</t>
+          <t>icon_spell_016</t>
         </is>
       </c>
     </row>
     <row r="435" ht="16.5" customHeight="1" s="57">
       <c r="A435" s="6" t="n">
-        <v>900031</v>
+        <v>900029</v>
       </c>
       <c r="B435" s="43" t="inlineStr">
         <is>
-          <t>罗汉金钟</t>
+          <t>魔兽之印</t>
         </is>
       </c>
       <c r="D435" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_004</t>
+          <t>icon_spell_015</t>
         </is>
       </c>
     </row>
     <row r="436" ht="16.5" customHeight="1" s="57">
       <c r="A436" s="6" t="n">
-        <v>900032</v>
+        <v>900030</v>
       </c>
       <c r="B436" s="43" t="inlineStr">
         <is>
-          <t>放下屠刀</t>
+          <t>圣甲之灵</t>
         </is>
       </c>
       <c r="D436" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_025</t>
+          <t>icon_spell_019</t>
         </is>
       </c>
     </row>
     <row r="437" ht="16.5" customHeight="1" s="57">
       <c r="A437" s="6" t="n">
-        <v>900033</v>
+        <v>900031</v>
       </c>
       <c r="B437" s="43" t="inlineStr">
         <is>
-          <t>破血狂攻</t>
+          <t>罗汉金钟</t>
         </is>
       </c>
       <c r="D437" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_038</t>
+          <t>icon_spell_004</t>
         </is>
       </c>
     </row>
     <row r="438" ht="16.5" customHeight="1" s="57">
       <c r="A438" s="6" t="n">
-        <v>900034</v>
+        <v>900032</v>
       </c>
       <c r="B438" s="43" t="inlineStr">
         <is>
-          <t>弱点击破</t>
+          <t>放下屠刀</t>
         </is>
       </c>
       <c r="D438" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_008</t>
+          <t>icon_spell_025</t>
         </is>
       </c>
     </row>
     <row r="439" ht="16.5" customHeight="1" s="57">
       <c r="A439" s="6" t="n">
-        <v>900035</v>
+        <v>900033</v>
       </c>
       <c r="B439" s="43" t="inlineStr">
         <is>
-          <t>破碎无双</t>
+          <t>破血狂攻</t>
         </is>
       </c>
       <c r="D439" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_030</t>
+          <t>icon_spell_038</t>
         </is>
       </c>
     </row>
     <row r="440" ht="16.5" customHeight="1" s="57">
       <c r="A440" s="6" t="n">
-        <v>900036</v>
+        <v>900034</v>
       </c>
       <c r="B440" s="43" t="inlineStr">
         <is>
-          <t>气疗术</t>
+          <t>弱点击破</t>
         </is>
       </c>
       <c r="D440" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_017</t>
+          <t>icon_spell_008</t>
         </is>
       </c>
     </row>
     <row r="441" ht="16.5" customHeight="1" s="57">
       <c r="A441" s="6" t="n">
-        <v>900037</v>
+        <v>900035</v>
       </c>
       <c r="B441" s="43" t="inlineStr">
         <is>
-          <t>心疗术</t>
+          <t>破碎无双</t>
         </is>
       </c>
       <c r="D441" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_017</t>
+          <t>icon_spell_030</t>
         </is>
       </c>
     </row>
     <row r="442" ht="16.5" customHeight="1" s="57">
       <c r="A442" s="6" t="n">
-        <v>900038</v>
+        <v>900036</v>
       </c>
       <c r="B442" s="43" t="inlineStr">
         <is>
-          <t>命疗术</t>
+          <t>气疗术</t>
         </is>
       </c>
       <c r="D442" s="43" t="inlineStr">
@@ -13834,701 +13830,735 @@
     </row>
     <row r="443" ht="16.5" customHeight="1" s="57">
       <c r="A443" s="6" t="n">
-        <v>900039</v>
+        <v>900037</v>
       </c>
       <c r="B443" s="43" t="inlineStr">
         <is>
-          <t>起死回生</t>
+          <t>心疗术</t>
         </is>
       </c>
       <c r="C443" s="30" t="n"/>
       <c r="D443" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_024</t>
+          <t>icon_spell_017</t>
         </is>
       </c>
       <c r="E443" s="30" t="n"/>
     </row>
     <row r="444" ht="16.5" customHeight="1" s="57">
       <c r="A444" s="6" t="n">
-        <v>900040</v>
+        <v>900038</v>
       </c>
       <c r="B444" s="43" t="inlineStr">
         <is>
-          <t>回魂咒</t>
+          <t>命疗术</t>
         </is>
       </c>
       <c r="C444" s="30" t="n"/>
       <c r="D444" s="43" t="inlineStr">
         <is>
-          <t>icon_spell_024</t>
+          <t>icon_spell_017</t>
         </is>
       </c>
       <c r="E444" s="30" t="n"/>
     </row>
     <row r="445" ht="16.5" customHeight="1" s="57">
       <c r="A445" s="6" t="n">
-        <v>900041</v>
+        <v>900039</v>
       </c>
       <c r="B445" s="43" t="inlineStr">
         <is>
-          <t>测试技能</t>
-        </is>
-      </c>
-      <c r="C445" s="30" t="inlineStr">
-        <is>
-          <t>对单个目标造成{damage}点伤害</t>
-        </is>
-      </c>
-      <c r="D445" s="43" t="n">
-        <v>1001</v>
-      </c>
-      <c r="E445" s="30" t="inlineStr">
-        <is>
-          <t>对单个目标造成{damage}点伤害</t>
-        </is>
-      </c>
+          <t>起死回生</t>
+        </is>
+      </c>
+      <c r="C445" s="30" t="n"/>
+      <c r="D445" s="43" t="inlineStr">
+        <is>
+          <t>icon_spell_024</t>
+        </is>
+      </c>
+      <c r="E445" s="30" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="6" t="n">
-        <v>1010001</v>
-      </c>
-      <c r="B446" s="3" t="inlineStr">
-        <is>
-          <t>御剑·养剑</t>
-        </is>
-      </c>
-      <c r="C446" s="100" t="inlineStr">
-        <is>
-          <t>开局即获得额外飞剑，加速进入战斗节奏。</t>
-        </is>
-      </c>
-      <c r="D446" s="0" t="n"/>
-      <c r="E446" s="30" t="inlineStr">
-        <is>
-          <t>首回合立即获得2把飞剑</t>
-        </is>
-      </c>
+        <v>900040</v>
+      </c>
+      <c r="B446" s="43" t="inlineStr">
+        <is>
+          <t>回魂咒</t>
+        </is>
+      </c>
+      <c r="C446" s="30" t="n"/>
+      <c r="D446" s="43" t="inlineStr">
+        <is>
+          <t>icon_spell_024</t>
+        </is>
+      </c>
+      <c r="E446" s="30" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="6" t="n">
+        <v>900041</v>
+      </c>
+      <c r="B447" s="43" t="inlineStr">
+        <is>
+          <t>测试技能</t>
+        </is>
+      </c>
+      <c r="C447" s="30" t="inlineStr">
+        <is>
+          <t>对单个目标造成{damage}点伤害</t>
+        </is>
+      </c>
+      <c r="D447" s="43" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E447" s="30" t="inlineStr">
+        <is>
+          <t>对单个目标造成{damage}点伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="6" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="B448" s="3" t="inlineStr">
+        <is>
+          <t>御剑·养剑</t>
+        </is>
+      </c>
+      <c r="C448" s="100" t="inlineStr">
+        <is>
+          <t>开局即获得额外飞剑，加速进入战斗节奏。</t>
+        </is>
+      </c>
+      <c r="D448" s="0" t="n"/>
+      <c r="E448" s="30" t="inlineStr">
+        <is>
+          <t>首回合立即获得2把飞剑</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" ht="27" customHeight="1" s="57">
+      <c r="A449" s="6" t="n">
         <v>1010002</v>
       </c>
-      <c r="B447" s="3" t="inlineStr">
+      <c r="B449" s="3" t="inlineStr">
         <is>
           <t>御剑·嗜杀</t>
         </is>
       </c>
-      <c r="C447" s="100" t="inlineStr">
+      <c r="C449" s="100" t="inlineStr">
         <is>
           <t>击败敌方时额外获得飞剑，杀敌越多剑越多。</t>
         </is>
       </c>
-      <c r="D447" s="0" t="n"/>
-      <c r="E447" s="30" t="inlineStr">
+      <c r="D449" s="0" t="n"/>
+      <c r="E449" s="30" t="inlineStr">
         <is>
           <t>造成击败时获得1把飞剑</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" s="42" t="n">
-        <v>1020001</v>
-      </c>
-      <c r="B448" s="3" t="inlineStr">
-        <is>
-          <t>诛仙·不息</t>
-        </is>
-      </c>
-      <c r="C448" s="30" t="inlineStr">
-        <is>
-          <t>诛仙释放后有概率不进入休息，保持战斗节奏。</t>
-        </is>
-      </c>
-      <c r="E448" s="30" t="inlineStr">
-        <is>
-          <t>诛仙释放后20%概率不进入休息状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="449" ht="27" customHeight="1" s="57">
-      <c r="A449" s="42" t="n">
-        <v>1020002</v>
-      </c>
-      <c r="B449" s="3" t="inlineStr">
-        <is>
-          <t>诛仙·三绝</t>
-        </is>
-      </c>
-      <c r="C449" s="30" t="inlineStr">
-        <is>
-          <t>三段剑击的暴击概率逐段递增，越到后段越容易暴击。</t>
-        </is>
-      </c>
-      <c r="E449" s="30" t="inlineStr">
-        <is>
-          <t>三诛仙次斩击顺次额外增加10%/20%/30%暴击概率</t>
         </is>
       </c>
     </row>
     <row r="450" ht="40.5" customHeight="1" s="57">
       <c r="A450" s="42" t="n">
-        <v>1030001</v>
+        <v>1020001</v>
       </c>
       <c r="B450" s="3" t="inlineStr">
         <is>
-          <t>万剑·漫天</t>
+          <t>诛仙·不息</t>
         </is>
       </c>
       <c r="C450" s="30" t="inlineStr">
         <is>
-          <t>飞剑覆盖范围扩大，可攻击更多目标。</t>
+          <t>诛仙释放后有概率不进入休息，保持战斗节奏。</t>
         </is>
       </c>
       <c r="E450" s="30" t="inlineStr">
         <is>
-          <t>增加1个攻击目标（共4个）</t>
+          <t>诛仙释放后20%概率不进入休息状态</t>
         </is>
       </c>
     </row>
     <row r="451" ht="27" customHeight="1" s="57">
       <c r="A451" s="42" t="n">
-        <v>1030002</v>
+        <v>1020002</v>
       </c>
       <c r="B451" s="3" t="inlineStr">
         <is>
-          <t>万剑·化劲</t>
+          <t>诛仙·三绝</t>
         </is>
       </c>
       <c r="C451" s="30" t="inlineStr">
         <is>
-          <t>放弃暴击，将暴击率转化为稳定的伤害增幅。</t>
+          <t>三段剑击的暴击概率逐段递增，越到后段越容易暴击。</t>
         </is>
       </c>
       <c r="E451" s="30" t="inlineStr">
         <is>
-          <t>该技能不触发物理暴击，基于物理暴击率X%增幅玩家的基础伤害伤害X%×2</t>
+          <t>三诛仙次斩击顺次额外增加10%/20%/30%暴击概率</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="42" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="B452" s="3" t="inlineStr">
+        <is>
+          <t>万剑·漫天</t>
+        </is>
+      </c>
+      <c r="C452" s="30" t="inlineStr">
+        <is>
+          <t>飞剑覆盖范围扩大，可攻击更多目标。</t>
+        </is>
+      </c>
+      <c r="E452" s="30" t="inlineStr">
+        <is>
+          <t>增加1个攻击目标（共4个）</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="42" t="n">
+        <v>1030002</v>
+      </c>
+      <c r="B453" s="3" t="inlineStr">
+        <is>
+          <t>万剑·化劲</t>
+        </is>
+      </c>
+      <c r="C453" s="30" t="inlineStr">
+        <is>
+          <t>放弃暴击，将暴击率转化为稳定的伤害增幅。</t>
+        </is>
+      </c>
+      <c r="E453" s="30" t="inlineStr">
+        <is>
+          <t>该技能不触发物理暴击，基于物理暴击率X%增幅玩家的基础伤害伤害X%×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="27" customHeight="1" s="57">
+      <c r="A454" s="42" t="n">
         <v>1040001</v>
       </c>
-      <c r="B452" s="3" t="inlineStr">
+      <c r="B454" s="3" t="inlineStr">
         <is>
           <t>杀意·连破</t>
         </is>
       </c>
-      <c r="C452" s="30" t="inlineStr">
+      <c r="C454" s="30" t="inlineStr">
         <is>
           <t>击败敌方后杀意持续延长，连杀不止。</t>
         </is>
       </c>
-      <c r="E452" s="30" t="inlineStr">
+      <c r="E454" s="30" t="inlineStr">
         <is>
           <t>【杀意】状态下，主动单体攻击造成任意击败延长杀意效果1-2回合
 70%概率1回合，30%概率2回合</t>
         </is>
       </c>
     </row>
-    <row r="453">
-      <c r="A453" s="42" t="n">
-        <v>1040002</v>
-      </c>
-      <c r="B453" s="3" t="inlineStr">
-        <is>
-          <t>杀意·觉醒</t>
-        </is>
-      </c>
-      <c r="C453" s="30" t="inlineStr">
-        <is>
-          <t>诛仙击败时有概率触发杀意，连锁爆发。</t>
-        </is>
-      </c>
-      <c r="E453" s="30" t="inlineStr">
-        <is>
-          <t>诛仙击败非人物单位时，10%附加【杀意】并立刻触发1次【杀意】效果</t>
-        </is>
-      </c>
-    </row>
-    <row r="454" ht="27" customHeight="1" s="57">
-      <c r="A454" s="42" t="n">
-        <v>1050001</v>
-      </c>
-      <c r="B454" s="3" t="inlineStr">
-        <is>
-          <t>剑魄·锋芒</t>
-        </is>
-      </c>
-      <c r="C454" s="30" t="inlineStr">
-        <is>
-          <t>飞剑追击的伤害上限提升。</t>
-        </is>
-      </c>
-      <c r="E454" s="30" t="inlineStr">
-        <is>
-          <t>飞剑伤害提升至最大气血8%</t>
-        </is>
-      </c>
-    </row>
     <row r="455">
       <c r="A455" s="42" t="n">
-        <v>1050002</v>
+        <v>1040002</v>
       </c>
       <c r="B455" s="3" t="inlineStr">
         <is>
-          <t>剑魄·聚剑</t>
+          <t>杀意·觉醒</t>
         </is>
       </c>
       <c r="C455" s="30" t="inlineStr">
         <is>
-          <t>飞剑容量扩大，宠物击败敌方时也可为主人获得飞剑。</t>
+          <t>诛仙击败时有概率触发杀意，连锁爆发。</t>
         </is>
       </c>
       <c r="E455" s="30" t="inlineStr">
         <is>
-          <t>飞剑上限+2(至5)，宠物击败30%概率获得飞剑</t>
+          <t>诛仙击败非人物单位时，10%附加【杀意】并立刻触发1次【杀意】效果</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="42" t="n">
-        <v>1060001</v>
+        <v>1050001</v>
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>天罡护体·先觉</t>
+          <t>剑魄·锋芒</t>
         </is>
       </c>
       <c r="C456" s="30" t="inlineStr">
         <is>
-          <t>面对高速敌方时格挡概率额外提升，以静制动。</t>
+          <t>飞剑追击的伤害上限提升。</t>
         </is>
       </c>
       <c r="E456" s="30" t="inlineStr">
         <is>
-          <t>对方速度速度高于自身时，【罡气】增加10%格挡概率</t>
+          <t>飞剑伤害提升至最大气血8%</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="42" t="n">
-        <v>1060002</v>
+        <v>1050002</v>
       </c>
       <c r="B457" s="3" t="inlineStr">
         <is>
-          <t>天罡护体·传罡</t>
+          <t>剑魄·聚剑</t>
         </is>
       </c>
       <c r="C457" s="30" t="inlineStr">
         <is>
-          <t>释放时将罡气同步传递给宠物，人宠共同受到护体。</t>
+          <t>飞剑容量扩大，宠物击败敌方时也可为主人获得飞剑。</t>
         </is>
       </c>
       <c r="E457" s="30" t="inlineStr">
         <is>
-          <t>主动释放时，己方物攻最高宠物获3回合【罡气】效果</t>
+          <t>飞剑上限+2(至5)，宠物击败30%概率获得飞剑</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="42" t="n">
-        <v>1070001</v>
+        <v>1060001</v>
       </c>
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>追风·风驰</t>
+          <t>天罡护体·先觉</t>
         </is>
       </c>
       <c r="C458" s="30" t="inlineStr">
         <is>
-          <t>神速状态下击败低速目标可延长神速持续时间。</t>
+          <t>面对高速敌方时格挡概率额外提升，以静制动。</t>
         </is>
       </c>
       <c r="E458" s="30" t="inlineStr">
         <is>
-          <t>神速下击败速度低于自身单位时，延长1回合【神速】</t>
+          <t>对方速度速度高于自身时，【罡气】增加10%格挡概率</t>
         </is>
       </c>
     </row>
     <row r="459" ht="27" customHeight="1" s="57">
       <c r="A459" s="42" t="n">
-        <v>1070002</v>
+        <v>1060002</v>
       </c>
       <c r="B459" s="3" t="inlineStr">
         <is>
-          <t>追风·破速</t>
+          <t>天罡护体·传罡</t>
         </is>
       </c>
       <c r="C459" s="30" t="inlineStr">
         <is>
-          <t>神速状态下击败敌方可附加虚弱削弱效果。</t>
+          <t>释放时将罡气同步传递给宠物，人宠共同受到护体。</t>
         </is>
       </c>
       <c r="E459" s="30" t="inlineStr">
         <is>
-          <t>神速下击败对方时，附加1层【虚弱】</t>
+          <t>主动释放时，己方物攻最高宠物获3回合【罡气】效果</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="42" t="n">
-        <v>1080001</v>
+        <v>1070001</v>
       </c>
       <c r="B460" s="3" t="inlineStr">
         <is>
-          <t>破军·趁危</t>
+          <t>追风·风驰</t>
         </is>
       </c>
       <c r="C460" s="30" t="inlineStr">
         <is>
-          <t>攻击重伤目标时暴击概率大幅提升，趁危追命。</t>
+          <t>神速状态下击败低速目标可延长神速持续时间。</t>
         </is>
       </c>
       <c r="E460" s="30" t="inlineStr">
         <is>
-          <t>对【重伤】单位，增加15%暴击率</t>
+          <t>神速下击败速度低于自身单位时，延长1回合【神速】</t>
         </is>
       </c>
     </row>
     <row r="461" ht="27" customHeight="1" s="57">
       <c r="A461" s="42" t="n">
-        <v>1080002</v>
+        <v>1070002</v>
       </c>
       <c r="B461" s="3" t="inlineStr">
         <is>
-          <t>破军·协攻</t>
+          <t>追风·破速</t>
         </is>
       </c>
       <c r="C461" s="30" t="inlineStr">
         <is>
-          <t>释放时宠物同步获得攻击力提升，人宠协攻。</t>
+          <t>神速状态下击败敌方可附加虚弱削弱效果。</t>
         </is>
       </c>
       <c r="E461" s="30" t="inlineStr">
         <is>
-          <t>释放后，我方物攻最高宠物单位本回合也增加20%物理攻击</t>
+          <t>神速下击败对方时，附加1层【虚弱】</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="42" t="n">
-        <v>1090001</v>
+        <v>1080001</v>
       </c>
       <c r="B462" s="3" t="inlineStr">
         <is>
-          <t>生死决·入骨</t>
+          <t>破军·趁危</t>
         </is>
       </c>
       <c r="C462" s="30" t="inlineStr">
         <is>
-          <t>获胜后为败方施加多层重伤，后续治疗难以恢复。</t>
+          <t>攻击重伤目标时暴击概率大幅提升，趁危追命。</t>
         </is>
       </c>
       <c r="E462" s="30" t="inlineStr">
         <is>
-          <t>获胜时，为倒地单位附加3层【重伤】</t>
+          <t>对【重伤】单位，增加15%暴击率</t>
         </is>
       </c>
     </row>
     <row r="463" ht="27" customHeight="1" s="57">
       <c r="A463" s="42" t="n">
+        <v>1080002</v>
+      </c>
+      <c r="B463" s="3" t="inlineStr">
+        <is>
+          <t>破军·协攻</t>
+        </is>
+      </c>
+      <c r="C463" s="30" t="inlineStr">
+        <is>
+          <t>释放时宠物同步获得攻击力提升，人宠协攻。</t>
+        </is>
+      </c>
+      <c r="E463" s="30" t="inlineStr">
+        <is>
+          <t>释放后，我方物攻最高宠物单位本回合也增加20%物理攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="27" customHeight="1" s="57">
+      <c r="A464" s="42" t="n">
+        <v>1090001</v>
+      </c>
+      <c r="B464" s="3" t="inlineStr">
+        <is>
+          <t>生死决·入骨</t>
+        </is>
+      </c>
+      <c r="C464" s="30" t="inlineStr">
+        <is>
+          <t>获胜后为败方施加多层重伤，后续治疗难以恢复。</t>
+        </is>
+      </c>
+      <c r="E464" s="30" t="inlineStr">
+        <is>
+          <t>获胜时，为倒地单位附加3层【重伤】</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="42" t="n">
         <v>1090002</v>
       </c>
-      <c r="B463" s="3" t="inlineStr">
+      <c r="B465" s="3" t="inlineStr">
         <is>
           <t>生死决·回生</t>
         </is>
       </c>
-      <c r="C463" s="30" t="inlineStr">
+      <c r="C465" s="30" t="inlineStr">
         <is>
           <t>获胜后回复全体友方气血，化险为夷。</t>
         </is>
       </c>
-      <c r="E463" s="30" t="inlineStr">
+      <c r="E465" s="30" t="inlineStr">
         <is>
           <t>获胜回复全体15%气血
 不超过自身最大气血的20%</t>
         </is>
       </c>
     </row>
-    <row r="464" ht="27" customHeight="1" s="57">
-      <c r="A464" s="42" t="n">
-        <v>2010001</v>
-      </c>
-      <c r="B464" s="3" t="inlineStr">
-        <is>
-          <t>驭风·乘胜</t>
-        </is>
-      </c>
-      <c r="C464" s="30" t="inlineStr">
-        <is>
-          <t>击败敌方时有概率额外积累风势。</t>
-        </is>
-      </c>
-      <c r="E464" s="30" t="inlineStr">
-        <is>
-          <t>造成击败时，20%概率增加1层【风势】</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" s="42" t="n">
-        <v>2010002</v>
-      </c>
-      <c r="B465" s="3" t="inlineStr">
-        <is>
-          <t>驭风·化伤</t>
-        </is>
-      </c>
-      <c r="C465" s="30" t="inlineStr">
-        <is>
-          <t>每次进入狂风时法术伤害持续提升。</t>
-        </is>
-      </c>
-      <c r="E465" s="30" t="inlineStr">
-        <is>
-          <t>每次进入【狂风】时，附加【化伤】增益，增加2%的法术伤害结果，可叠加5次</t>
-        </is>
-      </c>
-    </row>
     <row r="466" ht="27" customHeight="1" s="57">
       <c r="A466" s="42" t="n">
-        <v>2020001</v>
+        <v>2010001</v>
       </c>
       <c r="B466" s="3" t="inlineStr">
         <is>
-          <t>扶摇·连追</t>
+          <t>驭风·乘胜</t>
         </is>
       </c>
       <c r="C466" s="30" t="inlineStr">
         <is>
-          <t>追击击败时再次追击，连杀不断。</t>
+          <t>击败敌方时有概率额外积累风势。</t>
         </is>
       </c>
       <c r="E466" s="30" t="inlineStr">
         <is>
-          <t>追击造成击败时，再以40%法伤结果追击1次气血最低目标</t>
+          <t>造成击败时，20%概率增加1层【风势】</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="42" t="n">
-        <v>2020002</v>
+        <v>2010002</v>
       </c>
       <c r="B467" s="3" t="inlineStr">
         <is>
-          <t>扶摇·蓄暴</t>
+          <t>驭风·化伤</t>
         </is>
       </c>
       <c r="C467" s="30" t="inlineStr">
         <is>
-          <t>低风势时法术暴击大幅提升，蓄势待发。</t>
+          <t>每次进入狂风时法术伤害持续提升。</t>
         </is>
       </c>
       <c r="E467" s="30" t="inlineStr">
         <is>
-          <t>风势小于等于3时，额外增加20%的法术暴击</t>
+          <t>每次进入【狂风】时，附加【化伤】增益，增加2%的法术伤害结果，可叠加5次</t>
         </is>
       </c>
     </row>
     <row r="468" ht="27" customHeight="1" s="57">
       <c r="A468" s="42" t="n">
-        <v>2030001</v>
+        <v>2020001</v>
       </c>
       <c r="B468" s="3" t="inlineStr">
         <is>
-          <t>罡风·凌速</t>
+          <t>扶摇·连追</t>
         </is>
       </c>
       <c r="C468" s="30" t="inlineStr">
         <is>
-          <t>攻击速度低于自身的目标时暴击率额外提升。</t>
+          <t>追击击败时再次追击，连杀不断。</t>
         </is>
       </c>
       <c r="E468" s="30" t="inlineStr">
         <is>
-          <t>自身速度高于攻击目标时，对攻击目标额外增加5%法术暴击率</t>
+          <t>追击造成击败时，再以40%法伤结果追击1次气血最低目标</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="42" t="n">
-        <v>2030002</v>
+        <v>2020002</v>
       </c>
       <c r="B469" s="3" t="inlineStr">
         <is>
-          <t>罡风·扩散</t>
+          <t>扶摇·蓄暴</t>
         </is>
       </c>
       <c r="C469" s="30" t="inlineStr">
         <is>
-          <t>风势充足时攻击范围扩大，覆盖更多目标。</t>
+          <t>低风势时法术暴击大幅提升，蓄势待发。</t>
         </is>
       </c>
       <c r="E469" s="30" t="inlineStr">
         <is>
-          <t>风势≥4层时，增加1个攻击目标</t>
+          <t>风势小于等于3时，额外增加20%的法术暴击</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="42" t="n">
+        <v>2030001</v>
+      </c>
+      <c r="B470" s="3" t="inlineStr">
+        <is>
+          <t>罡风·凌速</t>
+        </is>
+      </c>
+      <c r="C470" s="30" t="inlineStr">
+        <is>
+          <t>攻击速度低于自身的目标时暴击率额外提升。</t>
+        </is>
+      </c>
+      <c r="E470" s="30" t="inlineStr">
+        <is>
+          <t>自身速度高于攻击目标时，对攻击目标额外增加5%法术暴击率</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="42" t="n">
+        <v>2030002</v>
+      </c>
+      <c r="B471" s="3" t="inlineStr">
+        <is>
+          <t>罡风·扩散</t>
+        </is>
+      </c>
+      <c r="C471" s="30" t="inlineStr">
+        <is>
+          <t>风势充足时攻击范围扩大，覆盖更多目标。</t>
+        </is>
+      </c>
+      <c r="E471" s="30" t="inlineStr">
+        <is>
+          <t>风势≥4层时，增加1个攻击目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="27" customHeight="1" s="57">
+      <c r="A472" s="42" t="n">
         <v>2040001</v>
       </c>
-      <c r="B470" s="3" t="inlineStr">
+      <c r="B472" s="3" t="inlineStr">
         <is>
           <t>乘风·连杀</t>
         </is>
       </c>
-      <c r="C470" s="30" t="inlineStr">
+      <c r="C472" s="30" t="inlineStr">
         <is>
           <t>单回合连续击败时有概率自动附加乘风效果。</t>
         </is>
       </c>
-      <c r="E470" s="30" t="inlineStr">
+      <c r="E472" s="30" t="inlineStr">
         <is>
           <t>自身单回合击败2个及以上的目标时
 50%概率为自身附加【乘风】效果</t>
         </is>
       </c>
     </row>
-    <row r="471">
-      <c r="A471" s="42" t="n">
-        <v>2040002</v>
-      </c>
-      <c r="B471" s="3" t="inlineStr">
-        <is>
-          <t>乘风·传功</t>
-        </is>
-      </c>
-      <c r="C471" s="30" t="inlineStr">
-        <is>
-          <t>释放时有概率同时为宠物附加相同效果。</t>
-        </is>
-      </c>
-      <c r="E471" s="30" t="inlineStr">
-        <is>
-          <t>50%同时给法攻最高宠物释放</t>
-        </is>
-      </c>
-    </row>
-    <row r="472" ht="27" customHeight="1" s="57">
-      <c r="A472" s="42" t="n">
-        <v>2050001</v>
-      </c>
-      <c r="B472" s="3" t="inlineStr">
-        <is>
-          <t>裂空·续力</t>
-        </is>
-      </c>
-      <c r="C472" s="30" t="inlineStr">
-        <is>
-          <t>进入狂风时延长自身所有增益效果的持续时间。</t>
-        </is>
-      </c>
-      <c r="E472" s="30" t="inlineStr">
-        <is>
-          <t>进入【狂风】状态时，延长自身所有增益效果1回合</t>
-        </is>
-      </c>
-    </row>
     <row r="473">
       <c r="A473" s="42" t="n">
-        <v>2050002</v>
+        <v>2040002</v>
       </c>
       <c r="B473" s="3" t="inlineStr">
         <is>
-          <t>裂空·回气</t>
+          <t>乘风·传功</t>
         </is>
       </c>
       <c r="C473" s="30" t="inlineStr">
         <is>
-          <t>进入狂风时回复愤怒与法宝灵气。</t>
+          <t>释放时有概率同时为宠物附加相同效果。</t>
         </is>
       </c>
       <c r="E473" s="30" t="inlineStr">
         <is>
-          <t>进入狂风+10愤怒+1法宝灵气</t>
+          <t>50%同时给法攻最高宠物释放</t>
         </is>
       </c>
     </row>
     <row r="474" ht="27" customHeight="1" s="57">
       <c r="A474" s="42" t="n">
-        <v>2060001</v>
+        <v>2050001</v>
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>拂柳·灵动</t>
+          <t>裂空·续力</t>
         </is>
       </c>
       <c r="C474" s="30" t="inlineStr">
         <is>
-          <t>面对低速敌方时闪避能力额外提升。</t>
+          <t>进入狂风时延长自身所有增益效果的持续时间。</t>
         </is>
       </c>
       <c r="E474" s="30" t="inlineStr">
         <is>
-          <t>受到速度低于自身的单位攻击时，【拂柳】附加的物理闪避额外+10%</t>
+          <t>进入【狂风】状态时，延长自身所有增益效果1回合</t>
         </is>
       </c>
     </row>
     <row r="475" ht="54" customHeight="1" s="57">
       <c r="A475" s="42" t="n">
-        <v>2060002</v>
+        <v>2050002</v>
       </c>
       <c r="B475" s="3" t="inlineStr">
         <is>
-          <t>拂柳·存护</t>
+          <t>裂空·回气</t>
         </is>
       </c>
       <c r="C475" s="30" t="inlineStr">
         <is>
-          <t>被复活时有概率自动附加拂柳效果。</t>
+          <t>进入狂风时回复愤怒与法宝灵气。</t>
         </is>
       </c>
       <c r="E475" s="30" t="inlineStr">
         <is>
-          <t>被复活时30%概率附加【拂柳】</t>
+          <t>进入狂风+10愤怒+1法宝灵气</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="42" t="n">
-        <v>2070001</v>
+        <v>2060001</v>
       </c>
       <c r="B476" s="3" t="inlineStr">
         <is>
-          <t>祭风·竭力</t>
+          <t>拂柳·灵动</t>
         </is>
       </c>
       <c r="C476" s="30" t="inlineStr">
         <is>
-          <t>风势为零时额外消耗气血多获得一层风势。</t>
+          <t>面对低速敌方时闪避能力额外提升。</t>
         </is>
       </c>
       <c r="E476" s="30" t="inlineStr">
         <is>
-          <t>风势为0时，额外消耗10%最大气血获得1层风势（获得4层）</t>
+          <t>受到速度低于自身的单位攻击时，【拂柳】附加的物理闪避额外+10%</t>
         </is>
       </c>
     </row>
     <row r="477" ht="27" customHeight="1" s="57">
       <c r="A477" s="42" t="n">
+        <v>2060002</v>
+      </c>
+      <c r="B477" s="3" t="inlineStr">
+        <is>
+          <t>拂柳·存护</t>
+        </is>
+      </c>
+      <c r="C477" s="30" t="inlineStr">
+        <is>
+          <t>被复活时有概率自动附加拂柳效果。</t>
+        </is>
+      </c>
+      <c r="E477" s="30" t="inlineStr">
+        <is>
+          <t>被复活时30%概率附加【拂柳】</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="27" customHeight="1" s="57">
+      <c r="A478" s="42" t="n">
+        <v>2070001</v>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>祭风·竭力</t>
+        </is>
+      </c>
+      <c r="C478" s="30" t="inlineStr">
+        <is>
+          <t>风势为零时额外消耗气血多获得一层风势。</t>
+        </is>
+      </c>
+      <c r="E478" s="30" t="inlineStr">
+        <is>
+          <t>风势为0时，额外消耗10%最大气血获得1层风势（获得4层）</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="42" t="n">
         <v>2070002</v>
       </c>
-      <c r="B477" s="3" t="inlineStr">
+      <c r="B479" s="3" t="inlineStr">
         <is>
           <t>祭风·满溢</t>
         </is>
       </c>
-      <c r="C477" s="30" t="inlineStr">
+      <c r="C479" s="30" t="inlineStr">
         <is>
           <t>风势溢出时转化为法术伤害加成。</t>
         </is>
       </c>
-      <c r="E477" s="30" t="inlineStr">
+      <c r="E479" s="30" t="inlineStr">
         <is>
           <t>使用宁静时如果风势溢出(超过5层）
 附加【满溢】增益，持续2回合，
@@ -14537,852 +14567,852 @@
         </is>
       </c>
     </row>
-    <row r="478" ht="27" customHeight="1" s="57">
-      <c r="A478" s="42" t="n">
-        <v>2080001</v>
-      </c>
-      <c r="B478" s="3" t="inlineStr">
-        <is>
-          <t>碎空·穿透</t>
-        </is>
-      </c>
-      <c r="C478" s="30" t="inlineStr">
-        <is>
-          <t>攻击高速目标时削弱概率大幅提升。</t>
-        </is>
-      </c>
-      <c r="E478" s="30" t="inlineStr">
-        <is>
-          <t>对方速度高于自身时，【碎灵】附加概率增加15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" s="42" t="n">
-        <v>2080002</v>
-      </c>
-      <c r="B479" s="3" t="inlineStr">
-        <is>
-          <t>碎空·凝元</t>
-        </is>
-      </c>
-      <c r="C479" s="30" t="inlineStr">
-        <is>
-          <t>成功削弱时同步为宠物附加法伤增益。</t>
-        </is>
-      </c>
-      <c r="E479" s="30" t="inlineStr">
-        <is>
-          <t>该技能每次成功附加【碎灵】时，为我方宠物法伤最高单位附加1层【凝元】</t>
-        </is>
-      </c>
-    </row>
     <row r="480" ht="27" customHeight="1" s="57">
       <c r="A480" s="42" t="n">
+        <v>2080001</v>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>碎空·穿透</t>
+        </is>
+      </c>
+      <c r="C480" s="30" t="inlineStr">
+        <is>
+          <t>攻击高速目标时削弱概率大幅提升。</t>
+        </is>
+      </c>
+      <c r="E480" s="30" t="inlineStr">
+        <is>
+          <t>对方速度高于自身时，【碎灵】附加概率增加15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="42" t="n">
+        <v>2080002</v>
+      </c>
+      <c r="B481" s="3" t="inlineStr">
+        <is>
+          <t>碎空·凝元</t>
+        </is>
+      </c>
+      <c r="C481" s="30" t="inlineStr">
+        <is>
+          <t>成功削弱时同步为宠物附加法伤增益。</t>
+        </is>
+      </c>
+      <c r="E481" s="30" t="inlineStr">
+        <is>
+          <t>该技能每次成功附加【碎灵】时，为我方宠物法伤最高单位附加1层【凝元】</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="42" t="n">
         <v>2090001</v>
       </c>
-      <c r="B480" s="3" t="inlineStr">
+      <c r="B482" s="3" t="inlineStr">
         <is>
           <t>大风起·先声</t>
         </is>
       </c>
-      <c r="C480" s="30" t="inlineStr">
+      <c r="C482" s="30" t="inlineStr">
         <is>
           <t>作为狂风首个指令时法术伤害大幅提升。</t>
         </is>
       </c>
-      <c r="E480" s="30" t="inlineStr">
+      <c r="E482" s="30" t="inlineStr">
         <is>
           <t>【狂风】下首个指令为该技能时
 增加30%的法术伤害结果</t>
         </is>
       </c>
     </row>
-    <row r="481">
-      <c r="A481" s="42" t="n">
+    <row r="483" ht="40.5" customHeight="1" s="57">
+      <c r="A483" s="42" t="n">
         <v>2090002</v>
       </c>
-      <c r="B481" s="3" t="inlineStr">
+      <c r="B483" s="3" t="inlineStr">
         <is>
           <t>大风起·余怒</t>
         </is>
       </c>
-      <c r="C481" s="30" t="inlineStr">
+      <c r="C483" s="30" t="inlineStr">
         <is>
           <t>作为狂风第二指令时回复大量愤怒。</t>
         </is>
       </c>
-      <c r="E481" s="30" t="inlineStr">
+      <c r="E483" s="30" t="inlineStr">
         <is>
           <t>【狂风】下第二个指令为该技能时，回复20点愤怒</t>
         </is>
       </c>
     </row>
-    <row r="482">
-      <c r="A482" s="42" t="n">
+    <row r="484">
+      <c r="A484" s="42" t="n">
         <v>3010001</v>
       </c>
-      <c r="B482" s="3" t="inlineStr">
+      <c r="B484" s="3" t="inlineStr">
         <is>
           <t>灵泉·凝灵</t>
         </is>
       </c>
-      <c r="C482" s="30" t="inlineStr">
+      <c r="C484" s="30" t="inlineStr">
         <is>
           <t>积蓄灵泉的同时持续提升治疗暴击能力。</t>
         </is>
       </c>
-      <c r="E482" s="30" t="inlineStr">
+      <c r="E484" s="30" t="inlineStr">
         <is>
           <t>战斗中每累计获得2滴灵泉，获得1层【洗心】增益，
 【洗心】：增加自身1%治疗暴击，至多叠加10层</t>
         </is>
       </c>
     </row>
-    <row r="483" ht="40.5" customHeight="1" s="57">
-      <c r="A483" s="42" t="n">
-        <v>3010002</v>
-      </c>
-      <c r="B483" s="3" t="inlineStr">
-        <is>
-          <t>灵泉·护佑</t>
-        </is>
-      </c>
-      <c r="C483" s="30" t="inlineStr">
-        <is>
-          <t>灵泉治疗时有概率为目标附加法术减免。</t>
-        </is>
-      </c>
-      <c r="E483" s="30" t="inlineStr">
-        <is>
-          <t>灵泉治疗时40%概率附加1层【灵护】</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" s="42" t="n">
-        <v>3020001</v>
-      </c>
-      <c r="B484" s="3" t="inlineStr">
-        <is>
-          <t>甘露·连弹</t>
-        </is>
-      </c>
-      <c r="C484" s="30" t="inlineStr">
-        <is>
-          <t>甘露弹射次数增加，覆盖更多队友。</t>
-        </is>
-      </c>
-      <c r="E484" s="30" t="inlineStr">
-        <is>
-          <t>弹射次数+1，对第四名目标回复50%治疗结果</t>
-        </is>
-      </c>
-    </row>
     <row r="485" ht="40.5" customHeight="1" s="57">
       <c r="A485" s="42" t="n">
+        <v>3010002</v>
+      </c>
+      <c r="B485" s="3" t="inlineStr">
+        <is>
+          <t>灵泉·护佑</t>
+        </is>
+      </c>
+      <c r="C485" s="30" t="inlineStr">
+        <is>
+          <t>灵泉治疗时有概率为目标附加法术减免。</t>
+        </is>
+      </c>
+      <c r="E485" s="30" t="inlineStr">
+        <is>
+          <t>灵泉治疗时40%概率附加1层【灵护】</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="40.5" customHeight="1" s="57">
+      <c r="A486" s="42" t="n">
+        <v>3020001</v>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>甘露·连弹</t>
+        </is>
+      </c>
+      <c r="C486" s="30" t="inlineStr">
+        <is>
+          <t>甘露弹射次数增加，覆盖更多队友。</t>
+        </is>
+      </c>
+      <c r="E486" s="30" t="inlineStr">
+        <is>
+          <t>弹射次数+1，对第四名目标回复50%治疗结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="42" t="n">
         <v>3020002</v>
       </c>
-      <c r="B485" s="3" t="inlineStr">
+      <c r="B487" s="3" t="inlineStr">
         <is>
           <t>甘露·滋养</t>
         </is>
       </c>
-      <c r="C485" s="30" t="inlineStr">
+      <c r="C487" s="30" t="inlineStr">
         <is>
           <t>每次弹射额外回复目标一定比例的最大生命。</t>
         </is>
       </c>
-      <c r="E485" s="30" t="inlineStr">
+      <c r="E487" s="30" t="inlineStr">
         <is>
           <t>该技能增加目标8%/6%/4%最大生命值的回复
 额外的治疗回复效果不超过目标单位的等级*境界倍率*10</t>
         </is>
       </c>
     </row>
-    <row r="486" ht="40.5" customHeight="1" s="57">
-      <c r="A486" s="42" t="n">
+    <row r="488">
+      <c r="A488" s="42" t="n">
         <v>3030001</v>
       </c>
-      <c r="B486" s="3" t="inlineStr">
+      <c r="B488" s="3" t="inlineStr">
         <is>
           <t>沧浪·夺泉</t>
         </is>
       </c>
-      <c r="C486" s="30" t="inlineStr">
+      <c r="C488" s="30" t="inlineStr">
         <is>
           <t>击败敌方时必定获得灵泉。</t>
         </is>
       </c>
-      <c r="E486" s="30" t="inlineStr">
+      <c r="E488" s="30" t="inlineStr">
         <is>
           <t>该技能造成击败时，额外获得1滴灵泉</t>
         </is>
       </c>
     </row>
-    <row r="487">
-      <c r="A487" s="42" t="n">
+    <row r="489" ht="27" customHeight="1" s="57">
+      <c r="A489" s="42" t="n">
         <v>3030002</v>
       </c>
-      <c r="B487" s="3" t="inlineStr">
+      <c r="B489" s="3" t="inlineStr">
         <is>
           <t>沧浪·暗涌</t>
         </is>
       </c>
-      <c r="C487" s="30" t="inlineStr">
+      <c r="C489" s="30" t="inlineStr">
         <is>
           <t>每回合未使用该技能时获得灵泉的概率持续增长。</t>
         </is>
       </c>
-      <c r="E487" s="30" t="inlineStr">
+      <c r="E489" s="30" t="inlineStr">
         <is>
           <t>未使用该技能时，每回合结束时增加沧浪20%获得灵泉的概率
 可叠加至多4层，释放后重置</t>
         </is>
       </c>
     </row>
-    <row r="488">
-      <c r="A488" s="42" t="n">
+    <row r="490" ht="27" customHeight="1" s="57">
+      <c r="A490" s="42" t="n">
         <v>3040001</v>
       </c>
-      <c r="B488" s="3" t="inlineStr">
+      <c r="B490" s="3" t="inlineStr">
         <is>
           <t>护灵诀·固本</t>
         </is>
       </c>
-      <c r="C488" s="30" t="inlineStr">
+      <c r="C490" s="30" t="inlineStr">
         <is>
           <t>首目标额外获得法术抗暴能力提升。</t>
         </is>
       </c>
-      <c r="E488" s="30" t="inlineStr">
+      <c r="E490" s="30" t="inlineStr">
         <is>
           <t>对首目标额外附加1层【固本】
 【固本】：提升5%法术抗暴并降低20%的法术被爆伤结果</t>
         </is>
       </c>
     </row>
-    <row r="489" ht="27" customHeight="1" s="57">
-      <c r="A489" s="42" t="n">
-        <v>3040002</v>
-      </c>
-      <c r="B489" s="3" t="inlineStr">
-        <is>
-          <t>护灵诀·迎新</t>
-        </is>
-      </c>
-      <c r="C489" s="30" t="inlineStr">
-        <is>
-          <t>召唤宠物出场时自动附加灵护。</t>
-        </is>
-      </c>
-      <c r="E489" s="30" t="inlineStr">
-        <is>
-          <t>我方召唤宠物时，为其附加1层【灵护】</t>
-        </is>
-      </c>
-    </row>
-    <row r="490" ht="27" customHeight="1" s="57">
-      <c r="A490" s="42" t="n">
-        <v>3050001</v>
-      </c>
-      <c r="B490" s="3" t="inlineStr">
-        <is>
-          <t>潮汐·归泉</t>
-        </is>
-      </c>
-      <c r="C490" s="30" t="inlineStr">
-        <is>
-          <t>友方倒地或离场时有概率获得灵泉。</t>
-        </is>
-      </c>
-      <c r="E490" s="30" t="inlineStr">
-        <is>
-          <t>己方单位被击败或离场时，30%概率获得1滴灵泉。</t>
-        </is>
-      </c>
-    </row>
     <row r="491">
       <c r="A491" s="42" t="n">
-        <v>3050002</v>
+        <v>3040002</v>
       </c>
       <c r="B491" s="3" t="inlineStr">
         <is>
-          <t>潮汐·涌泉</t>
+          <t>护灵诀·迎新</t>
         </is>
       </c>
       <c r="C491" s="30" t="inlineStr">
         <is>
-          <t>灵泉容量扩大，且每次灵泉治疗量增加。</t>
+          <t>召唤宠物出场时自动附加灵护。</t>
         </is>
       </c>
       <c r="E491" s="30" t="inlineStr">
         <is>
-          <t>灵泉存储上限+1，增加目标最大生命5%的治疗量（合计8%）</t>
+          <t>我方召唤宠物时，为其附加1层【灵护】</t>
         </is>
       </c>
     </row>
     <row r="492" ht="40.5" customHeight="1" s="57">
       <c r="A492" s="42" t="n">
-        <v>3060001</v>
+        <v>3050001</v>
       </c>
       <c r="B492" s="3" t="inlineStr">
         <is>
-          <t>明镜止水·厚报</t>
+          <t>潮汐·归泉</t>
         </is>
       </c>
       <c r="C492" s="30" t="inlineStr">
         <is>
-          <t>友方气血极低时水镜回复量大幅提升。</t>
+          <t>友方倒地或离场时有概率获得灵泉。</t>
         </is>
       </c>
       <c r="E492" s="30" t="inlineStr">
         <is>
-          <t>受击后气血小于最大气血10%时，回复所受伤害70%的气血</t>
+          <t>己方单位被击败或离场时，30%概率获得1滴灵泉。</t>
         </is>
       </c>
     </row>
     <row r="493" ht="27" customHeight="1" s="57">
       <c r="A493" s="42" t="n">
-        <v>3060002</v>
+        <v>3050002</v>
       </c>
       <c r="B493" s="3" t="inlineStr">
         <is>
-          <t>明镜止水·延时</t>
+          <t>潮汐·涌泉</t>
         </is>
       </c>
       <c r="C493" s="30" t="inlineStr">
         <is>
-          <t>水镜持续时间延长。</t>
+          <t>灵泉容量扩大，且每次灵泉治疗量增加。</t>
         </is>
       </c>
       <c r="E493" s="30" t="inlineStr">
         <is>
-          <t>【水镜】持续时间增加1回合</t>
+          <t>灵泉存储上限+1，增加目标最大生命5%的治疗量（合计8%）</t>
         </is>
       </c>
     </row>
     <row r="494" ht="27" customHeight="1" s="57">
       <c r="A494" s="42" t="n">
+        <v>3060001</v>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>明镜止水·厚报</t>
+        </is>
+      </c>
+      <c r="C494" s="30" t="inlineStr">
+        <is>
+          <t>友方气血极低时水镜回复量大幅提升。</t>
+        </is>
+      </c>
+      <c r="E494" s="30" t="inlineStr">
+        <is>
+          <t>受击后气血小于最大气血10%时，回复所受伤害70%的气血</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" ht="27" customHeight="1" s="57">
+      <c r="A495" s="42" t="n">
+        <v>3060002</v>
+      </c>
+      <c r="B495" s="3" t="inlineStr">
+        <is>
+          <t>明镜止水·延时</t>
+        </is>
+      </c>
+      <c r="C495" s="30" t="inlineStr">
+        <is>
+          <t>水镜持续时间延长。</t>
+        </is>
+      </c>
+      <c r="E495" s="30" t="inlineStr">
+        <is>
+          <t>【水镜】持续时间增加1回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="42" t="n">
         <v>3070001</v>
       </c>
-      <c r="B494" s="3" t="inlineStr">
+      <c r="B496" s="3" t="inlineStr">
         <is>
           <t>渡生·泉愈</t>
         </is>
       </c>
-      <c r="C494" s="30" t="inlineStr">
+      <c r="C496" s="30" t="inlineStr">
         <is>
           <t>有灵泉时消耗一滴额外触发灵泉治疗。</t>
         </is>
       </c>
-      <c r="E494" s="30" t="inlineStr">
+      <c r="E496" s="30" t="inlineStr">
         <is>
           <t>存在灵泉时，消耗1点灵泉，复活时立刻触发1次灵泉回复
 同时额外回复相同气血的内伤</t>
         </is>
       </c>
     </row>
-    <row r="495" ht="27" customHeight="1" s="57">
-      <c r="A495" s="42" t="n">
-        <v>3070002</v>
-      </c>
-      <c r="B495" s="3" t="inlineStr">
-        <is>
-          <t>渡生·净化</t>
-        </is>
-      </c>
-      <c r="C495" s="30" t="inlineStr">
-        <is>
-          <t>复活后为目标转化一个减益为增益。</t>
-        </is>
-      </c>
-      <c r="E495" s="30" t="inlineStr">
-        <is>
-          <t>复活后，随机转化1个可净化的非封印减益变为1个随机门派增益</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" s="42" t="n">
-        <v>3080001</v>
-      </c>
-      <c r="B496" s="3" t="inlineStr">
-        <is>
-          <t>断脉·借力</t>
-        </is>
-      </c>
-      <c r="C496" s="30" t="inlineStr">
-        <is>
-          <t>我方法术攻击被断脉的目标时伤害提升。</t>
-        </is>
-      </c>
-      <c r="E496" s="30" t="inlineStr">
-        <is>
-          <t>我方召唤灵法术攻击【断脉】单位时，法术伤害结果+10%</t>
-        </is>
-      </c>
-    </row>
     <row r="497" ht="27" customHeight="1" s="57">
       <c r="A497" s="42" t="n">
-        <v>3080002</v>
+        <v>3070002</v>
       </c>
       <c r="B497" s="3" t="inlineStr">
         <is>
-          <t>断脉·传脉</t>
+          <t>渡生·净化</t>
         </is>
       </c>
       <c r="C497" s="30" t="inlineStr">
         <is>
-          <t>敌方宠物满层断脉离场时会传染给法伤最高的敌方。</t>
+          <t>复活后为目标转化一个减益为增益。</t>
         </is>
       </c>
       <c r="E497" s="30" t="inlineStr">
         <is>
-          <t>对方宠物单位3层【断脉】离场时，给对方法伤最高单位附加1层【断脉】</t>
+          <t>复活后，随机转化1个可净化的非封印减益变为1个随机门派增益</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="42" t="n">
-        <v>3090001</v>
+        <v>3080001</v>
       </c>
       <c r="B498" s="3" t="inlineStr">
         <is>
-          <t>海纳百川·补泉</t>
+          <t>断脉·借力</t>
         </is>
       </c>
       <c r="C498" s="30" t="inlineStr">
         <is>
-          <t>释放后立即获得灵泉。</t>
+          <t>我方法术攻击被断脉的目标时伤害提升。</t>
         </is>
       </c>
       <c r="E498" s="30" t="inlineStr">
         <is>
-          <t>释放后，获得2滴灵泉</t>
+          <t>我方召唤灵法术攻击【断脉】单位时，法术伤害结果+10%</t>
         </is>
       </c>
     </row>
     <row r="499" ht="27" customHeight="1" s="57">
       <c r="A499" s="42" t="n">
-        <v>3090002</v>
+        <v>3080002</v>
       </c>
       <c r="B499" s="3" t="inlineStr">
         <is>
-          <t>海纳百川·分润</t>
+          <t>断脉·传脉</t>
         </is>
       </c>
       <c r="C499" s="30" t="inlineStr">
         <is>
-          <t>共患期间友方受治疗时将部分效果分配给全队。</t>
+          <t>敌方宠物满层断脉离场时会传染给法伤最高的敌方。</t>
         </is>
       </c>
       <c r="E499" s="30" t="inlineStr">
         <is>
-          <t>【共患】期间，任意友方受到治疗时，将治疗结果的 10% 额外分配给其他存活的【共患】单位</t>
+          <t>对方宠物单位3层【断脉】离场时，给对方法伤最高单位附加1层【断脉】</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="42" t="n">
-        <v>4010001</v>
+        <v>3090001</v>
       </c>
       <c r="B500" s="3" t="inlineStr">
         <is>
-          <t>画符·印痕</t>
+          <t>海纳百川·补泉</t>
         </is>
       </c>
       <c r="C500" s="30" t="inlineStr">
         <is>
-          <t>释放被强化的封印技能后封印命中提升。</t>
+          <t>释放后立即获得灵泉。</t>
         </is>
       </c>
       <c r="E500" s="30" t="inlineStr">
         <is>
-          <t>释放强化后的封印技能时，增加3%的封印命中</t>
+          <t>释放后，获得2滴灵泉</t>
         </is>
       </c>
     </row>
     <row r="501" ht="27" customHeight="1" s="57">
       <c r="A501" s="42" t="n">
-        <v>4010002</v>
+        <v>3090002</v>
       </c>
       <c r="B501" s="3" t="inlineStr">
         <is>
-          <t>画符·金甲</t>
+          <t>海纳百川·分润</t>
         </is>
       </c>
       <c r="C501" s="30" t="inlineStr">
         <is>
-          <t>释放被强化的非封印技能后获得物法减免提升。</t>
+          <t>共患期间友方受治疗时将部分效果分配给全队。</t>
         </is>
       </c>
       <c r="E501" s="30" t="inlineStr">
         <is>
-          <t>释放强化后的非封印技能时，本回合增加5%的物法减免</t>
+          <t>【共患】期间，任意友方受到治疗时，将治疗结果的 10% 额外分配给其他存活的【共患】单位</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="42" t="n">
-        <v>4020001</v>
+        <v>4010001</v>
       </c>
       <c r="B502" s="3" t="inlineStr">
         <is>
-          <t>失心·抢先</t>
+          <t>画符·印痕</t>
         </is>
       </c>
       <c r="C502" s="30" t="inlineStr">
         <is>
-          <t>速度高于目标时封印命中上限提升，先手制敌。</t>
+          <t>释放被强化的封印技能后封印命中提升。</t>
         </is>
       </c>
       <c r="E502" s="30" t="inlineStr">
         <is>
-          <t>自身速度高于目标时，封印命中上限额外增加5%</t>
+          <t>释放强化后的封印技能时，增加3%的封印命中</t>
         </is>
       </c>
     </row>
     <row r="503" ht="40.5" customHeight="1" s="57">
       <c r="A503" s="42" t="n">
-        <v>4020002</v>
+        <v>4010002</v>
       </c>
       <c r="B503" s="3" t="inlineStr">
         <is>
-          <t>失心·追击</t>
+          <t>画符·金甲</t>
         </is>
       </c>
       <c r="C503" s="30" t="inlineStr">
         <is>
-          <t>封印命中时有概率使宠物追击目标。</t>
+          <t>释放被强化的非封印技能后获得物法减免提升。</t>
         </is>
       </c>
       <c r="E503" s="30" t="inlineStr">
         <is>
-          <t>封印命中时，25%概率己方随机宠物对该目标追击 1 次，优先使用技能</t>
+          <t>释放强化后的非封印技能时，本回合增加5%的物法减免</t>
         </is>
       </c>
     </row>
     <row r="504" ht="40.5" customHeight="1" s="57">
       <c r="A504" s="42" t="n">
-        <v>4030001</v>
+        <v>4020001</v>
       </c>
       <c r="B504" s="3" t="inlineStr">
         <is>
-          <t>天雷·克兽</t>
+          <t>失心·抢先</t>
         </is>
       </c>
       <c r="C504" s="30" t="inlineStr">
         <is>
-          <t>攻击宠物时封禁概率额外提升。</t>
+          <t>速度高于目标时封印命中上限提升，先手制敌。</t>
         </is>
       </c>
       <c r="E504" s="30" t="inlineStr">
         <is>
-          <t>首目标为非人物单位时，封技概率额外增加 5%</t>
+          <t>自身速度高于目标时，封印命中上限额外增加5%</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="42" t="n">
+        <v>4020002</v>
+      </c>
+      <c r="B505" s="3" t="inlineStr">
+        <is>
+          <t>失心·追击</t>
+        </is>
+      </c>
+      <c r="C505" s="30" t="inlineStr">
+        <is>
+          <t>封印命中时有概率使宠物追击目标。</t>
+        </is>
+      </c>
+      <c r="E505" s="30" t="inlineStr">
+        <is>
+          <t>封印命中时，25%概率己方随机宠物对该目标追击 1 次，优先使用技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="42" t="n">
+        <v>4030001</v>
+      </c>
+      <c r="B506" s="3" t="inlineStr">
+        <is>
+          <t>天雷·克兽</t>
+        </is>
+      </c>
+      <c r="C506" s="30" t="inlineStr">
+        <is>
+          <t>攻击宠物时封禁概率额外提升。</t>
+        </is>
+      </c>
+      <c r="E506" s="30" t="inlineStr">
+        <is>
+          <t>首目标为非人物单位时，封技概率额外增加 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="42" t="n">
         <v>4030002</v>
       </c>
-      <c r="B505" s="3" t="inlineStr">
+      <c r="B507" s="3" t="inlineStr">
         <is>
           <t>天雷·连击</t>
         </is>
       </c>
-      <c r="C505" s="30" t="inlineStr">
+      <c r="C507" s="30" t="inlineStr">
         <is>
           <t>首目标处于封印状态时自动追击另一个随机目标。</t>
         </is>
       </c>
-      <c r="E505" s="30" t="inlineStr">
+      <c r="E507" s="30" t="inlineStr">
         <is>
           <t>天雷对首目标造成伤害时，若目标当前处于任意封印状态，
 以 30% 伤害结果追击 1 次随机目标</t>
         </is>
       </c>
     </row>
-    <row r="506">
-      <c r="A506" s="42" t="n">
+    <row r="508" ht="27" customHeight="1" s="57">
+      <c r="A508" s="42" t="n">
         <v>4040001</v>
       </c>
-      <c r="B506" s="3" t="inlineStr">
+      <c r="B508" s="3" t="inlineStr">
         <is>
           <t>定身术·感染</t>
         </is>
       </c>
-      <c r="C506" s="30" t="inlineStr">
+      <c r="C508" s="30" t="inlineStr">
         <is>
           <t>击败被缴械/定身的宠物时有概率传染给其主人。</t>
         </is>
       </c>
-      <c r="E506" s="30" t="inlineStr">
+      <c r="E508" s="30" t="inlineStr">
         <is>
           <t>己方单体技能击败【缴械】或【定身】的宠物目标时，以30%概率传染到其主人上
 传染（继承效果与剩余回合数）</t>
         </is>
       </c>
     </row>
-    <row r="507">
-      <c r="A507" s="42" t="n">
-        <v>4040002</v>
-      </c>
-      <c r="B507" s="3" t="inlineStr">
-        <is>
-          <t>定身术·回怒</t>
-        </is>
-      </c>
-      <c r="C507" s="30" t="inlineStr">
-        <is>
-          <t>命中时回复愤怒。</t>
-        </is>
-      </c>
-      <c r="E507" s="30" t="inlineStr">
-        <is>
-          <t>该技能命中时，回复自身5点愤怒</t>
-        </is>
-      </c>
-    </row>
-    <row r="508" ht="27" customHeight="1" s="57">
-      <c r="A508" s="42" t="n">
-        <v>4050001</v>
-      </c>
-      <c r="B508" s="3" t="inlineStr">
-        <is>
-          <t>律令·三符</t>
-        </is>
-      </c>
-      <c r="C508" s="30" t="inlineStr">
-        <is>
-          <t>有概率额外获得更多符箓。</t>
-        </is>
-      </c>
-      <c r="E508" s="30" t="inlineStr">
-        <is>
-          <t>30%概率获取符箓时额外增加1个随机符箓获取</t>
-        </is>
-      </c>
-    </row>
     <row r="509" ht="40.5" customHeight="1" s="57">
       <c r="A509" s="42" t="n">
-        <v>4050002</v>
+        <v>4040002</v>
       </c>
       <c r="B509" s="3" t="inlineStr">
         <is>
-          <t>律令·选符</t>
+          <t>定身术·回怒</t>
         </is>
       </c>
       <c r="C509" s="30" t="inlineStr">
         <is>
-          <t>符箓必定至少强化一个封印技能。</t>
+          <t>命中时回复愤怒。</t>
         </is>
       </c>
       <c r="E509" s="30" t="inlineStr">
         <is>
-          <t>符箓强化时，强化至少1个封印技能</t>
+          <t>该技能命中时，回复自身5点愤怒</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="42" t="n">
+        <v>4050001</v>
+      </c>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>律令·三符</t>
+        </is>
+      </c>
+      <c r="C510" s="30" t="inlineStr">
+        <is>
+          <t>有概率额外获得更多符箓。</t>
+        </is>
+      </c>
+      <c r="E510" s="30" t="inlineStr">
+        <is>
+          <t>30%概率获取符箓时额外增加1个随机符箓获取</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="27" customHeight="1" s="57">
+      <c r="A511" s="42" t="n">
+        <v>4050002</v>
+      </c>
+      <c r="B511" s="3" t="inlineStr">
+        <is>
+          <t>律令·选符</t>
+        </is>
+      </c>
+      <c r="C511" s="30" t="inlineStr">
+        <is>
+          <t>符箓必定至少强化一个封印技能。</t>
+        </is>
+      </c>
+      <c r="E511" s="30" t="inlineStr">
+        <is>
+          <t>符箓强化时，强化至少1个封印技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="27" customHeight="1" s="57">
+      <c r="A512" s="42" t="n">
         <v>4060001</v>
       </c>
-      <c r="B510" s="3" t="inlineStr">
+      <c r="B512" s="3" t="inlineStr">
         <is>
           <t>斗转·增效</t>
         </is>
       </c>
-      <c r="C510" s="30" t="inlineStr">
+      <c r="C512" s="30" t="inlineStr">
         <is>
           <t>释放后自身封印命中持续提升。</t>
         </is>
       </c>
-      <c r="E510" s="30" t="inlineStr">
+      <c r="E512" s="30" t="inlineStr">
         <is>
           <t>释放后自身附加【斗转】增益
 【斗转】：获得4回合5%封印命中</t>
         </is>
       </c>
     </row>
-    <row r="511" ht="27" customHeight="1" s="57">
-      <c r="A511" s="42" t="n">
+    <row r="513" ht="27" customHeight="1" s="57">
+      <c r="A513" s="42" t="n">
         <v>4060002</v>
       </c>
-      <c r="B511" s="3" t="inlineStr">
+      <c r="B513" s="3" t="inlineStr">
         <is>
           <t>斗转·碎灵</t>
         </is>
       </c>
-      <c r="C511" s="30" t="inlineStr">
+      <c r="C513" s="30" t="inlineStr">
         <is>
           <t>斗转期间目标攻击自身后会被附加法防削弱。</t>
         </is>
       </c>
-      <c r="E511" s="30" t="inlineStr">
+      <c r="E513" s="30" t="inlineStr">
         <is>
           <t>斗转期间，目标每次攻击自身后，为其附加1层【碎灵】
 （1次出手算1次结算）</t>
         </is>
       </c>
     </row>
-    <row r="512" ht="27" customHeight="1" s="57">
-      <c r="A512" s="42" t="n">
-        <v>4070001</v>
-      </c>
-      <c r="B512" s="3" t="inlineStr">
-        <is>
-          <t>金光咒·再生</t>
-        </is>
-      </c>
-      <c r="C512" s="30" t="inlineStr">
-        <is>
-          <t>被复活时有概率自动获得金光咒效果。</t>
-        </is>
-      </c>
-      <c r="E512" s="30" t="inlineStr">
-        <is>
-          <t>被复活时，30%概率为自身附加【金光】技能</t>
-        </is>
-      </c>
-    </row>
-    <row r="513" ht="27" customHeight="1" s="57">
-      <c r="A513" s="42" t="n">
-        <v>4070002</v>
-      </c>
-      <c r="B513" s="3" t="inlineStr">
-        <is>
-          <t>金光咒·危照</t>
-        </is>
-      </c>
-      <c r="C513" s="30" t="inlineStr">
-        <is>
-          <t>内伤严重时金光咒获得强化的概率大幅提升，危难时金光护身。</t>
-        </is>
-      </c>
-      <c r="E513" s="30" t="inlineStr">
-        <is>
-          <t>自身内伤超过30%时，该技能获得符箓强化概率增加至50%</t>
-        </is>
-      </c>
-    </row>
     <row r="514">
       <c r="A514" s="42" t="n">
-        <v>4080001</v>
+        <v>4070001</v>
       </c>
       <c r="B514" s="3" t="inlineStr">
         <is>
-          <t>断念·制速</t>
+          <t>金光咒·再生</t>
         </is>
       </c>
       <c r="C514" s="30" t="inlineStr">
         <is>
-          <t>全场最快时命中率与上限大幅提升。</t>
+          <t>被复活时有概率自动获得金光咒效果。</t>
         </is>
       </c>
       <c r="E514" s="30" t="inlineStr">
         <is>
-          <t>自身速度为全场1速时，增加该技能的命中率与上限10%</t>
+          <t>被复活时，30%概率为自身附加【金光】技能</t>
         </is>
       </c>
     </row>
     <row r="515" ht="54" customHeight="1" s="57">
       <c r="A515" s="42" t="n">
-        <v>4080002</v>
+        <v>4070002</v>
       </c>
       <c r="B515" s="3" t="inlineStr">
         <is>
-          <t>断念·深化</t>
+          <t>金光咒·危照</t>
         </is>
       </c>
       <c r="C515" s="30" t="inlineStr">
         <is>
-          <t>成功延长多个减益时额外多延长一回合。</t>
+          <t>内伤严重时金光咒获得强化的概率大幅提升，危难时金光护身。</t>
         </is>
       </c>
       <c r="E515" s="30" t="inlineStr">
         <is>
-          <t>成功延长对方4个及以上的减益时，额外延长1回合减益效果</t>
+          <t>自身内伤超过30%时，该技能获得符箓强化概率增加至50%</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="42" t="n">
-        <v>4090001</v>
+        <v>4080001</v>
       </c>
       <c r="B516" s="3" t="inlineStr">
         <is>
-          <t>夺魄·不休</t>
+          <t>断念·制速</t>
         </is>
       </c>
       <c r="C516" s="30" t="inlineStr">
         <is>
-          <t>释放后不进入休息，但混乱命中率降低。</t>
+          <t>全场最快时命中率与上限大幅提升。</t>
         </is>
       </c>
       <c r="E516" s="30" t="inlineStr">
         <is>
-          <t>释放后自身不会休息，但混乱命中率为50%</t>
+          <t>自身速度为全场1速时，增加该技能的命中率与上限10%</t>
         </is>
       </c>
     </row>
     <row r="517" ht="81" customHeight="1" s="57">
       <c r="A517" s="42" t="n">
+        <v>4080002</v>
+      </c>
+      <c r="B517" s="3" t="inlineStr">
+        <is>
+          <t>断念·深化</t>
+        </is>
+      </c>
+      <c r="C517" s="30" t="inlineStr">
+        <is>
+          <t>成功延长多个减益时额外多延长一回合。</t>
+        </is>
+      </c>
+      <c r="E517" s="30" t="inlineStr">
+        <is>
+          <t>成功延长对方4个及以上的减益时，额外延长1回合减益效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="42" t="n">
+        <v>4090001</v>
+      </c>
+      <c r="B518" s="3" t="inlineStr">
+        <is>
+          <t>夺魄·不休</t>
+        </is>
+      </c>
+      <c r="C518" s="30" t="inlineStr">
+        <is>
+          <t>释放后不进入休息，但混乱命中率降低。</t>
+        </is>
+      </c>
+      <c r="E518" s="30" t="inlineStr">
+        <is>
+          <t>释放后自身不会休息，但混乱命中率为50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="42" t="n">
         <v>4090002</v>
       </c>
-      <c r="B517" s="3" t="inlineStr">
+      <c r="B519" s="3" t="inlineStr">
         <is>
           <t>夺魄·反噬</t>
         </is>
       </c>
-      <c r="C517" s="30" t="inlineStr">
+      <c r="C519" s="30" t="inlineStr">
         <is>
           <t>混乱目标攻击我方时不造成伤害反而治疗受击者；攻击敌方时伤害增加。</t>
         </is>
       </c>
-      <c r="E517" s="30" t="inlineStr">
+      <c r="E519" s="30" t="inlineStr">
         <is>
           <t>混乱目标对我方单位造成伤害时，不会造成伤害并回复受击单位造成伤害30% 的气血
 混乱目标对敌方单位造成伤害时，增加30%伤害结果</t>
         </is>
       </c>
     </row>
-    <row r="518">
-      <c r="A518" s="42" t="n">
+    <row r="520" ht="40.5" customHeight="1" s="57">
+      <c r="A520" s="42" t="n">
         <v>5010001</v>
       </c>
-      <c r="B518" s="3" t="inlineStr">
+      <c r="B520" s="3" t="inlineStr">
         <is>
           <t>御兽·先发</t>
         </is>
       </c>
-      <c r="C518" s="30" t="inlineStr">
+      <c r="C520" s="30" t="inlineStr">
         <is>
           <t>战斗首回合结束时立即获得1个灵兽技能</t>
         </is>
       </c>
-      <c r="E518" s="30" t="inlineStr">
+      <c r="E520" s="30" t="inlineStr">
         <is>
           <t>首回合结束时，获得1个额外的宠物技能</t>
         </is>
       </c>
     </row>
-    <row r="519">
-      <c r="A519" s="42" t="n">
+    <row r="521">
+      <c r="A521" s="42" t="n">
         <v>5010002</v>
       </c>
-      <c r="B519" s="3" t="inlineStr">
+      <c r="B521" s="3" t="inlineStr">
         <is>
           <t>御兽·积威</t>
         </is>
       </c>
-      <c r="C519" s="30" t="inlineStr">
+      <c r="C521" s="30" t="inlineStr">
         <is>
           <t>获得灵兽技能时，自身物理伤害结果增加</t>
         </is>
       </c>
-      <c r="E519" s="30" t="inlineStr">
+      <c r="E521" s="30" t="inlineStr">
         <is>
           <t>每获得过1个宠物被动技能+1%物理伤害结果(至多10层)
 获得宠物技能石，增加1层BUFF【积威】（BUFFID 501），
@@ -15391,141 +15421,141 @@
         </is>
       </c>
     </row>
-    <row r="520" ht="40.5" customHeight="1" s="57">
-      <c r="A520" s="42" t="n">
-        <v>5020001</v>
-      </c>
-      <c r="B520" s="3" t="inlineStr">
-        <is>
-          <t>裂地枪·蓄力</t>
-        </is>
-      </c>
-      <c r="C520" s="30" t="inlineStr">
-        <is>
-          <t>持有的灵兽技能越多，裂地枪伤害越高。</t>
-        </is>
-      </c>
-      <c r="E520" s="30" t="inlineStr">
-        <is>
-          <t>每持有1个宠物被动技能，本技能+5%技能伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" s="42" t="n">
-        <v>5020002</v>
-      </c>
-      <c r="B521" s="3" t="inlineStr">
-        <is>
-          <t>裂地枪·广域</t>
-        </is>
-      </c>
-      <c r="C521" s="30" t="inlineStr">
-        <is>
-          <t>灵兽技能充足时攻击范围扩大，覆盖更多目标。</t>
-        </is>
-      </c>
-      <c r="E521" s="30" t="inlineStr">
-        <is>
-          <t>拥有宠物被动技能≥3时，该技能攻击目标+1</t>
-        </is>
-      </c>
-    </row>
     <row r="522">
       <c r="A522" s="42" t="n">
-        <v>5030001</v>
+        <v>5020001</v>
       </c>
       <c r="B522" s="3" t="inlineStr">
         <is>
-          <t>啸天·压制</t>
+          <t>裂地枪·蓄力</t>
         </is>
       </c>
       <c r="C522" s="30" t="inlineStr">
         <is>
-          <t>攻击速度高于自身的目标时伤害大幅提升。</t>
+          <t>持有的灵兽技能越多，裂地枪伤害越高。</t>
         </is>
       </c>
       <c r="E522" s="30" t="inlineStr">
         <is>
-          <t>目标速度高与自身时，该技能伤害结果增加30%</t>
+          <t>每持有1个宠物被动技能，本技能+5%技能伤害</t>
         </is>
       </c>
     </row>
     <row r="523" ht="27" customHeight="1" s="57">
       <c r="A523" s="42" t="n">
-        <v>5030002</v>
+        <v>5020002</v>
       </c>
       <c r="B523" s="3" t="inlineStr">
         <is>
-          <t>啸天·夺技</t>
+          <t>裂地枪·广域</t>
         </is>
       </c>
       <c r="C523" s="30" t="inlineStr">
         <is>
-          <t>击败宠物时获得灵兽技能的概率大幅提升。</t>
+          <t>灵兽技能充足时攻击范围扩大，覆盖更多目标。</t>
         </is>
       </c>
       <c r="E523" s="30" t="inlineStr">
         <is>
-          <t>击败宠物+50%获技能，优先该宠物技能</t>
+          <t>拥有宠物被动技能≥3时，该技能攻击目标+1</t>
         </is>
       </c>
     </row>
     <row r="524" ht="94.5" customHeight="1" s="57">
       <c r="A524" s="42" t="n">
-        <v>5040001</v>
+        <v>5030001</v>
       </c>
       <c r="B524" s="3" t="inlineStr">
         <is>
-          <t>共鸣·同化</t>
+          <t>啸天·压制</t>
         </is>
       </c>
       <c r="C524" s="30" t="inlineStr">
         <is>
-          <t>共鸣宠物击败敌方时，自身获得其一个宠物被动技能。</t>
+          <t>攻击速度高于自身的目标时伤害大幅提升。</t>
         </is>
       </c>
       <c r="E524" s="30" t="inlineStr">
         <is>
-          <t>共鸣宠物击败时，自身获得其一个可获得的宠物被动</t>
+          <t>目标速度高与自身时，该技能伤害结果增加30%</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="42" t="n">
-        <v>5040002</v>
+        <v>5030002</v>
       </c>
       <c r="B525" s="3" t="inlineStr">
         <is>
-          <t>共鸣·通感</t>
+          <t>啸天·夺技</t>
         </is>
       </c>
       <c r="C525" s="30" t="inlineStr">
         <is>
-          <t>建立共鸣时，自身获得共鸣宠物的一个技能。</t>
+          <t>击败宠物时获得灵兽技能的概率大幅提升。</t>
         </is>
       </c>
       <c r="E525" s="30" t="inlineStr">
         <is>
-          <t>赋予共鸣时，自身获得其一个可获得的宠物被动</t>
+          <t>击败宠物+50%获技能，优先该宠物技能</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="42" t="n">
+        <v>5040001</v>
+      </c>
+      <c r="B526" s="3" t="inlineStr">
+        <is>
+          <t>共鸣·同化</t>
+        </is>
+      </c>
+      <c r="C526" s="30" t="inlineStr">
+        <is>
+          <t>共鸣宠物击败敌方时，自身获得其一个宠物被动技能。</t>
+        </is>
+      </c>
+      <c r="E526" s="30" t="inlineStr">
+        <is>
+          <t>共鸣宠物击败时，自身获得其一个可获得的宠物被动</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="42" t="n">
+        <v>5040002</v>
+      </c>
+      <c r="B527" s="3" t="inlineStr">
+        <is>
+          <t>共鸣·通感</t>
+        </is>
+      </c>
+      <c r="C527" s="30" t="inlineStr">
+        <is>
+          <t>建立共鸣时，自身获得共鸣宠物的一个技能。</t>
+        </is>
+      </c>
+      <c r="E527" s="30" t="inlineStr">
+        <is>
+          <t>赋予共鸣时，自身获得其一个可获得的宠物被动</t>
+        </is>
+      </c>
+    </row>
+    <row r="528" ht="40.5" customHeight="1" s="57">
+      <c r="A528" s="42" t="n">
         <v>5050001</v>
       </c>
-      <c r="B526" s="3" t="inlineStr">
+      <c r="B528" s="3" t="inlineStr">
         <is>
           <t>龙脉·精进</t>
         </is>
       </c>
-      <c r="C526" s="30" t="inlineStr">
+      <c r="C528" s="30" t="inlineStr">
         <is>
           <t>获得技能时更易获得已有技能，加速技能升级。</t>
         </is>
       </c>
-      <c r="E526" s="30" t="inlineStr">
+      <c r="E528" s="30" t="inlineStr">
         <is>
           <t>高概率获得已有的技能，获得已有的技能时，概率使其升级
 实现逻辑如下：
@@ -15534,1270 +15564,1270 @@
         </is>
       </c>
     </row>
-    <row r="527">
-      <c r="A527" s="42" t="n">
-        <v>5050002</v>
-      </c>
-      <c r="B527" s="3" t="inlineStr">
-        <is>
-          <t>龙脉·不灭</t>
-        </is>
-      </c>
-      <c r="C527" s="30" t="inlineStr">
-        <is>
-          <t>损失高级技能时有概率保留低级版本，降低损失。</t>
-        </is>
-      </c>
-      <c r="E527" s="30" t="inlineStr">
-        <is>
-          <t>高级技能损失时，50%概率返还获得1个低级技能</t>
-        </is>
-      </c>
-    </row>
-    <row r="528" ht="40.5" customHeight="1" s="57">
-      <c r="A528" s="42" t="n">
-        <v>5060001</v>
-      </c>
-      <c r="B528" s="3" t="inlineStr">
-        <is>
-          <t>舍身·舍命</t>
-        </is>
-      </c>
-      <c r="C528" s="30" t="inlineStr">
-        <is>
-          <t>舍身状态下首次致死时牺牲一个灵兽技能保住性命。</t>
-        </is>
-      </c>
-      <c r="E528" s="30" t="inlineStr">
-        <is>
-          <t>每次【舍身】状态下，首次致死消耗1技能保1血</t>
-        </is>
-      </c>
-    </row>
     <row r="529">
       <c r="A529" s="42" t="n">
-        <v>5060002</v>
+        <v>5050002</v>
       </c>
       <c r="B529" s="3" t="inlineStr">
         <is>
-          <t>舍身·续战</t>
+          <t>龙脉·不灭</t>
         </is>
       </c>
       <c r="C529" s="30" t="inlineStr">
         <is>
-          <t>舍身状态下每回合持续回复损失的气血。</t>
+          <t>损失高级技能时有概率保留低级版本，降低损失。</t>
         </is>
       </c>
       <c r="E529" s="30" t="inlineStr">
         <is>
-          <t>【舍身】状态下，每回合回复15%损失气血</t>
+          <t>高级技能损失时，50%概率返还获得1个低级技能</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="42" t="n">
+        <v>5060001</v>
+      </c>
+      <c r="B530" s="3" t="inlineStr">
+        <is>
+          <t>舍身·舍命</t>
+        </is>
+      </c>
+      <c r="C530" s="30" t="inlineStr">
+        <is>
+          <t>舍身状态下首次致死时牺牲一个灵兽技能保住性命。</t>
+        </is>
+      </c>
+      <c r="E530" s="30" t="inlineStr">
+        <is>
+          <t>每次【舍身】状态下，首次致死消耗1技能保1血</t>
+        </is>
+      </c>
+    </row>
+    <row r="531" ht="27" customHeight="1" s="57">
+      <c r="A531" s="42" t="n">
+        <v>5060002</v>
+      </c>
+      <c r="B531" s="3" t="inlineStr">
+        <is>
+          <t>舍身·续战</t>
+        </is>
+      </c>
+      <c r="C531" s="30" t="inlineStr">
+        <is>
+          <t>舍身状态下每回合持续回复损失的气血。</t>
+        </is>
+      </c>
+      <c r="E531" s="30" t="inlineStr">
+        <is>
+          <t>【舍身】状态下，每回合回复15%损失气血</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="42" t="n">
         <v>5070001</v>
       </c>
-      <c r="B530" s="3" t="inlineStr">
+      <c r="B532" s="3" t="inlineStr">
         <is>
           <t>骤雨·取舍</t>
         </is>
       </c>
-      <c r="C530" s="30" t="inlineStr">
+      <c r="C532" s="30" t="inlineStr">
         <is>
           <t>优先消耗非攻击类技能，保留核心战斗能力。</t>
         </is>
       </c>
-      <c r="E530" s="30" t="inlineStr">
+      <c r="E532" s="30" t="inlineStr">
         <is>
           <t>高概率消耗非攻击类
 基于【说明】中的技能页签，75%概率消耗非攻击类的技能</t>
         </is>
       </c>
     </row>
-    <row r="531" ht="27" customHeight="1" s="57">
-      <c r="A531" s="42" t="n">
-        <v>5070002</v>
-      </c>
-      <c r="B531" s="3" t="inlineStr">
-        <is>
-          <t>骤雨·回元</t>
-        </is>
-      </c>
-      <c r="C531" s="30" t="inlineStr">
-        <is>
-          <t>击败敌方时返还部分真元消耗。</t>
-        </is>
-      </c>
-      <c r="E531" s="30" t="inlineStr">
-        <is>
-          <t>该技能造成击败时，返还技能消耗的一半真元</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" s="42" t="n">
-        <v>5080001</v>
-      </c>
-      <c r="B532" s="3" t="inlineStr">
-        <is>
-          <t>天崩·精通</t>
-        </is>
-      </c>
-      <c r="C532" s="30" t="inlineStr">
-        <is>
-          <t>高级技能双倍计算，大幅提升伤害段数。</t>
-        </is>
-      </c>
-      <c r="E532" s="30" t="inlineStr">
-        <is>
-          <t>高级技能按照2个普通技能数结算</t>
-        </is>
-      </c>
-    </row>
     <row r="533">
       <c r="A533" s="42" t="n">
-        <v>5080002</v>
+        <v>5070002</v>
       </c>
       <c r="B533" s="3" t="inlineStr">
         <is>
-          <t>天崩·燃血</t>
+          <t>骤雨·回元</t>
         </is>
       </c>
       <c r="C533" s="30" t="inlineStr">
         <is>
-          <t>技能充足时额外消耗敌方真元，以力破巧。</t>
+          <t>击败敌方时返还部分真元消耗。</t>
         </is>
       </c>
       <c r="E533" s="30" t="inlineStr">
         <is>
-          <t>技能≥3时，真元扣除额外增加50%（算技能扣成100%）</t>
+          <t>该技能造成击败时，返还技能消耗的一半真元</t>
         </is>
       </c>
     </row>
     <row r="534" ht="40.5" customHeight="1" s="57">
       <c r="A534" s="42" t="n">
-        <v>5090001</v>
+        <v>5080001</v>
       </c>
       <c r="B534" s="3" t="inlineStr">
         <is>
-          <t>神龙摆尾·吞噬</t>
+          <t>天崩·精通</t>
         </is>
       </c>
       <c r="C534" s="30" t="inlineStr">
         <is>
-          <t>吸收时额外获得共鸣宠物的一个高级被动技能。</t>
+          <t>高级技能双倍计算，大幅提升伤害段数。</t>
         </is>
       </c>
       <c r="E534" s="30" t="inlineStr">
         <is>
-          <t>吸收时，获得共鸣宠物随机1个可获得的高级宠物技能</t>
+          <t>高级技能按照2个普通技能数结算</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="42" t="n">
-        <v>5090002</v>
+        <v>5080002</v>
       </c>
       <c r="B535" s="3" t="inlineStr">
         <is>
-          <t>神龙摆尾·治愈</t>
+          <t>天崩·燃血</t>
         </is>
       </c>
       <c r="C535" s="30" t="inlineStr">
         <is>
-          <t>吸收时回复宠物部分气血，减轻宠物损失。</t>
+          <t>技能充足时额外消耗敌方真元，以力破巧。</t>
         </is>
       </c>
       <c r="E535" s="30" t="inlineStr">
         <is>
-          <t>回复吸收宠物50%的当前气血</t>
+          <t>技能≥3时，真元扣除额外增加50%（算技能扣成100%）</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="42" t="n">
+        <v>5090001</v>
+      </c>
+      <c r="B536" s="3" t="inlineStr">
+        <is>
+          <t>神龙摆尾·吞噬</t>
+        </is>
+      </c>
+      <c r="C536" s="30" t="inlineStr">
+        <is>
+          <t>吸收时额外获得共鸣宠物的一个高级被动技能。</t>
+        </is>
+      </c>
+      <c r="E536" s="30" t="inlineStr">
+        <is>
+          <t>吸收时，获得共鸣宠物随机1个可获得的高级宠物技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="42" t="n">
+        <v>5090002</v>
+      </c>
+      <c r="B537" s="3" t="inlineStr">
+        <is>
+          <t>神龙摆尾·治愈</t>
+        </is>
+      </c>
+      <c r="C537" s="30" t="inlineStr">
+        <is>
+          <t>吸收时回复宠物部分气血，减轻宠物损失。</t>
+        </is>
+      </c>
+      <c r="E537" s="30" t="inlineStr">
+        <is>
+          <t>回复吸收宠物50%的当前气血</t>
+        </is>
+      </c>
+    </row>
+    <row r="538" ht="27" customHeight="1" s="57">
+      <c r="A538" s="42" t="n">
         <v>6010001</v>
       </c>
-      <c r="B536" s="3" t="inlineStr">
+      <c r="B538" s="3" t="inlineStr">
         <is>
           <t>三昧真火·穿甲</t>
         </is>
       </c>
-      <c r="C536" s="30" t="inlineStr">
+      <c r="C538" s="30" t="inlineStr">
         <is>
           <t>消耗火球积累法术穿透，持续增强后续输出。</t>
         </is>
       </c>
-      <c r="E536" s="30" t="inlineStr">
+      <c r="E538" s="30" t="inlineStr">
         <is>
           <t>每消耗3个火球，增加自身1%的法术穿透，至多增加10%
 (溢出火球不计算为消耗）</t>
         </is>
       </c>
     </row>
-    <row r="537">
-      <c r="A537" s="42" t="n">
-        <v>6010002</v>
-      </c>
-      <c r="B537" s="3" t="inlineStr">
-        <is>
-          <t>三昧真火·感应</t>
-        </is>
-      </c>
-      <c r="C537" s="30" t="inlineStr">
-        <is>
-          <t>使用法宝特技时有概率额外积蓄火球。</t>
-        </is>
-      </c>
-      <c r="E537" s="30" t="inlineStr">
-        <is>
-          <t>自身使用法宝特技时，30%概率额外积累一个火球</t>
-        </is>
-      </c>
-    </row>
-    <row r="538" ht="27" customHeight="1" s="57">
-      <c r="A538" s="42" t="n">
-        <v>6020001</v>
-      </c>
-      <c r="B538" s="3" t="inlineStr">
-        <is>
-          <t>红莲·灼身</t>
-        </is>
-      </c>
-      <c r="C538" s="30" t="inlineStr">
-        <is>
-          <t>攻击首目标时有概率附加灼烧持续伤害。</t>
-        </is>
-      </c>
-      <c r="E538" s="30" t="inlineStr">
-        <is>
-          <t>对首目标，20%概率附加【灼烧】</t>
-        </is>
-      </c>
-    </row>
     <row r="539">
       <c r="A539" s="42" t="n">
-        <v>6020002</v>
+        <v>6010002</v>
       </c>
       <c r="B539" s="3" t="inlineStr">
         <is>
-          <t>红莲·回火</t>
+          <t>三昧真火·感应</t>
         </is>
       </c>
       <c r="C539" s="30" t="inlineStr">
         <is>
-          <t>击败敌方时有概率回收火球。</t>
+          <t>使用法宝特技时有概率额外积蓄火球。</t>
         </is>
       </c>
       <c r="E539" s="30" t="inlineStr">
         <is>
-          <t>该技能造成击败时，50%概率回复1枚火球</t>
+          <t>自身使用法宝特技时，30%概率额外积累一个火球</t>
         </is>
       </c>
     </row>
     <row r="540" ht="27" customHeight="1" s="57">
       <c r="A540" s="42" t="n">
-        <v>6030001</v>
+        <v>6020001</v>
       </c>
       <c r="B540" s="3" t="inlineStr">
         <is>
-          <t>赤焰·蔓延</t>
+          <t>红莲·灼身</t>
         </is>
       </c>
       <c r="C540" s="30" t="inlineStr">
         <is>
-          <t>消耗火球时有概率对命中目标附加灼烧。</t>
+          <t>攻击首目标时有概率附加灼烧持续伤害。</t>
         </is>
       </c>
       <c r="E540" s="30" t="inlineStr">
         <is>
-          <t>消耗X个火球时，对每个目标10×X%概率附加【灼烧】</t>
+          <t>对首目标，20%概率附加【灼烧】</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="42" t="n">
-        <v>6030002</v>
+        <v>6020002</v>
       </c>
       <c r="B541" s="3" t="inlineStr">
         <is>
-          <t>赤焰·爆裂</t>
+          <t>红莲·回火</t>
         </is>
       </c>
       <c r="C541" s="30" t="inlineStr">
         <is>
-          <t>消耗多个火球时法术穿透大幅提升。</t>
+          <t>击败敌方时有概率回收火球。</t>
         </is>
       </c>
       <c r="E541" s="30" t="inlineStr">
         <is>
-          <t>消耗火球≥2时，增加15%的法术穿透</t>
+          <t>该技能造成击败时，50%概率回复1枚火球</t>
         </is>
       </c>
     </row>
     <row r="542" ht="27" customHeight="1" s="57">
       <c r="A542" s="42" t="n">
-        <v>6040001</v>
+        <v>6030001</v>
       </c>
       <c r="B542" s="3" t="inlineStr">
         <is>
-          <t>浴火·劫余</t>
+          <t>赤焰·蔓延</t>
         </is>
       </c>
       <c r="C542" s="30" t="inlineStr">
         <is>
-          <t>浴火期间击败敌方可回复气血与魔法，劫后余生。</t>
+          <t>消耗火球时有概率对命中目标附加灼烧。</t>
         </is>
       </c>
       <c r="E542" s="30" t="inlineStr">
         <is>
-          <t>【浴火】持续期间造成击败时，每个击败回复10%的最大魔法与10%的最大气血</t>
+          <t>消耗X个火球时，对每个目标10×X%概率附加【灼烧】</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="42" t="n">
-        <v>6040002</v>
+        <v>6030002</v>
       </c>
       <c r="B543" s="3" t="inlineStr">
         <is>
-          <t>浴火·怒焰</t>
+          <t>赤焰·爆裂</t>
         </is>
       </c>
       <c r="C543" s="30" t="inlineStr">
         <is>
-          <t>浴火状态下愤怒获取大幅提升。</t>
+          <t>消耗多个火球时法术穿透大幅提升。</t>
         </is>
       </c>
       <c r="E543" s="30" t="inlineStr">
         <is>
-          <t>焚身状态下，增加20%的愤怒获取</t>
+          <t>消耗火球≥2时，增加15%的法术穿透</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="42" t="n">
-        <v>6050001</v>
+        <v>6040001</v>
       </c>
       <c r="B544" s="3" t="inlineStr">
         <is>
-          <t>薪火·兽袭</t>
+          <t>浴火·劫余</t>
         </is>
       </c>
       <c r="C544" s="30" t="inlineStr">
         <is>
-          <t>薪火满层时宠物攻击后自动追击一次。</t>
+          <t>浴火期间击败敌方可回复气血与魔法，劫后余生。</t>
         </is>
       </c>
       <c r="E544" s="30" t="inlineStr">
         <is>
-          <t>【薪火】满层时，宠物攻击后以30%伤害使用相同技能追击1次</t>
+          <t>【浴火】持续期间造成击败时，每个击败回复10%的最大魔法与10%的最大气血</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="42" t="n">
-        <v>6050002</v>
+        <v>6040002</v>
       </c>
       <c r="B545" s="3" t="inlineStr">
         <is>
-          <t>薪火·反哺</t>
+          <t>浴火·怒焰</t>
         </is>
       </c>
       <c r="C545" s="30" t="inlineStr">
         <is>
-          <t>宠物击败敌方时有概率回收火球给主人。</t>
+          <t>浴火状态下愤怒获取大幅提升。</t>
         </is>
       </c>
       <c r="E545" s="30" t="inlineStr">
         <is>
-          <t>己方宠物造成击败时，40%概率回复自身1个火球</t>
+          <t>焚身状态下，增加20%的愤怒获取</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="42" t="n">
-        <v>6060001</v>
+        <v>6050001</v>
       </c>
       <c r="B546" s="3" t="inlineStr">
         <is>
-          <t>陨星坠·拾焰</t>
+          <t>薪火·兽袭</t>
         </is>
       </c>
       <c r="C546" s="30" t="inlineStr">
         <is>
-          <t>击败非人物单位时有概率回收火球。</t>
+          <t>薪火满层时宠物攻击后自动追击一次。</t>
         </is>
       </c>
       <c r="E546" s="30" t="inlineStr">
         <is>
-          <t>造成伤害时，25%概率附加1层【灼烧】</t>
+          <t>【薪火】满层时，宠物攻击后以30%伤害使用相同技能追击1次</t>
         </is>
       </c>
     </row>
     <row r="547" ht="27" customHeight="1" s="57">
       <c r="A547" s="42" t="n">
-        <v>6060002</v>
+        <v>6050002</v>
       </c>
       <c r="B547" s="3" t="inlineStr">
         <is>
-          <t>陨星坠·连破</t>
+          <t>薪火·反哺</t>
         </is>
       </c>
       <c r="C547" s="30" t="inlineStr">
         <is>
-          <t>每段命中均有概率附加灼烧。</t>
+          <t>宠物击败敌方时有概率回收火球给主人。</t>
         </is>
       </c>
       <c r="E547" s="30" t="inlineStr">
         <is>
-          <t>击败对方非人物单位时，50%概率回复1枚火球</t>
+          <t>己方宠物造成击败时，40%概率回复自身1个火球</t>
         </is>
       </c>
     </row>
     <row r="548" ht="27" customHeight="1" s="57">
       <c r="A548" s="42" t="n">
-        <v>6070001</v>
+        <v>6060001</v>
       </c>
       <c r="B548" s="3" t="inlineStr">
         <is>
-          <t>天赐·凝火</t>
+          <t>陨星坠·拾焰</t>
         </is>
       </c>
       <c r="C548" s="30" t="inlineStr">
         <is>
-          <t>附加时有概率直接凝出一个火球。</t>
+          <t>击败非人物单位时有概率回收火球。</t>
         </is>
       </c>
       <c r="E548" s="30" t="inlineStr">
         <is>
-          <t>附加该状态时，30%概率获得1个火球</t>
+          <t>造成伤害时，25%概率附加1层【灼烧】</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="42" t="n">
-        <v>6070002</v>
+        <v>6060002</v>
       </c>
       <c r="B549" s="3" t="inlineStr">
         <is>
-          <t>天赐·续焰</t>
+          <t>陨星坠·连破</t>
         </is>
       </c>
       <c r="C549" s="30" t="inlineStr">
         <is>
-          <t>天赐状态下每消耗火球有概率延长天赐持续时间。</t>
+          <t>每段命中均有概率附加灼烧。</t>
         </is>
       </c>
       <c r="E549" s="30" t="inlineStr">
         <is>
-          <t>天赐状态下每消耗1个火球，10%概率延长天赐状态1回合</t>
+          <t>击败对方非人物单位时，50%概率回复1枚火球</t>
         </is>
       </c>
     </row>
     <row r="550" ht="27" customHeight="1" s="57">
       <c r="A550" s="42" t="n">
+        <v>6070001</v>
+      </c>
+      <c r="B550" s="3" t="inlineStr">
+        <is>
+          <t>天赐·凝火</t>
+        </is>
+      </c>
+      <c r="C550" s="30" t="inlineStr">
+        <is>
+          <t>附加时有概率直接凝出一个火球。</t>
+        </is>
+      </c>
+      <c r="E550" s="30" t="inlineStr">
+        <is>
+          <t>附加该状态时，30%概率获得1个火球</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="42" t="n">
+        <v>6070002</v>
+      </c>
+      <c r="B551" s="3" t="inlineStr">
+        <is>
+          <t>天赐·续焰</t>
+        </is>
+      </c>
+      <c r="C551" s="30" t="inlineStr">
+        <is>
+          <t>天赐状态下每消耗火球有概率延长天赐持续时间。</t>
+        </is>
+      </c>
+      <c r="E551" s="30" t="inlineStr">
+        <is>
+          <t>天赐状态下每消耗1个火球，10%概率延长天赐状态1回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="42" t="n">
         <v>6080001</v>
       </c>
-      <c r="B550" s="3" t="inlineStr">
+      <c r="B552" s="3" t="inlineStr">
         <is>
           <t>炎盾·温养</t>
         </is>
       </c>
-      <c r="C550" s="30" t="inlineStr">
+      <c r="C552" s="30" t="inlineStr">
         <is>
           <t>炎盾存在时每有敌方处于灼烧状态可回复气血。</t>
         </is>
       </c>
-      <c r="E550" s="30" t="inlineStr">
+      <c r="E552" s="30" t="inlineStr">
         <is>
           <t>【炎盾】状态下，敌方回合每存在1个【灼烧】单位
 回合结束时，回复自身等级*境界倍率*3的气血</t>
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" s="42" t="n">
+    <row r="553" ht="27" customHeight="1" s="57">
+      <c r="A553" s="42" t="n">
         <v>6080002</v>
       </c>
-      <c r="B551" s="3" t="inlineStr">
+      <c r="B553" s="3" t="inlineStr">
         <is>
           <t>炎盾·余烬</t>
         </is>
       </c>
-      <c r="C551" s="30" t="inlineStr">
+      <c r="C553" s="30" t="inlineStr">
         <is>
           <t>被复活时有概率自动附加炎盾。</t>
         </is>
       </c>
-      <c r="E551" s="30" t="inlineStr">
+      <c r="E553" s="30" t="inlineStr">
         <is>
           <t>被复活时，50%概率附加【炎盾】状态</t>
         </is>
       </c>
     </row>
-    <row r="552">
-      <c r="A552" s="42" t="n">
+    <row r="554">
+      <c r="A554" s="42" t="n">
         <v>6090001</v>
       </c>
-      <c r="B552" s="3" t="inlineStr">
+      <c r="B554" s="3" t="inlineStr">
         <is>
           <t>焚天·燃尽</t>
         </is>
       </c>
-      <c r="C552" s="30" t="inlineStr">
+      <c r="C554" s="30" t="inlineStr">
         <is>
           <t>满火球释放时法术穿透大幅提升。</t>
         </is>
       </c>
-      <c r="E552" s="30" t="inlineStr">
+      <c r="E554" s="30" t="inlineStr">
         <is>
           <t>每次造成伤害时，结算1回合的灼烧增益
 扣除对方1回合的灼烧结算的气血</t>
         </is>
       </c>
     </row>
-    <row r="553" ht="27" customHeight="1" s="57">
-      <c r="A553" s="42" t="n">
-        <v>6090002</v>
-      </c>
-      <c r="B553" s="3" t="inlineStr">
-        <is>
-          <t>焚天·满溢</t>
-        </is>
-      </c>
-      <c r="C553" s="30" t="inlineStr">
-        <is>
-          <t>攻击时有概率附加灼烧。</t>
-        </is>
-      </c>
-      <c r="E553" s="30" t="inlineStr">
-        <is>
-          <t>满火球+20%的法术穿透</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" s="42" t="n">
-        <v>7010001</v>
-      </c>
-      <c r="B554" s="3" t="inlineStr">
-        <is>
-          <t>生生不息·护幼</t>
-        </is>
-      </c>
-      <c r="C554" s="30" t="inlineStr">
-        <is>
-          <t>召唤宠物时自动为其附加生息。</t>
-        </is>
-      </c>
-      <c r="E554" s="30" t="inlineStr">
-        <is>
-          <t>己方战斗中召唤宠物时，附加1层【生息】</t>
-        </is>
-      </c>
-    </row>
     <row r="555" ht="27" customHeight="1" s="57">
       <c r="A555" s="42" t="n">
-        <v>7010002</v>
+        <v>6090002</v>
       </c>
       <c r="B555" s="3" t="inlineStr">
         <is>
-          <t>生生不息·厚积</t>
+          <t>焚天·满溢</t>
         </is>
       </c>
       <c r="C555" s="30" t="inlineStr">
         <is>
-          <t>生息每回合额外回复一定比例最大气血。</t>
+          <t>攻击时有概率附加灼烧。</t>
         </is>
       </c>
       <c r="E555" s="30" t="inlineStr">
         <is>
-          <t>【生息】每回合额外目标回复2%的最大气血，不超过等级*境界倍率*2</t>
+          <t>满火球+20%的法术穿透</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="42" t="n">
-        <v>7020001</v>
+        <v>7010001</v>
       </c>
       <c r="B556" s="3" t="inlineStr">
         <is>
-          <t>回春术·妙手</t>
+          <t>生生不息·护幼</t>
         </is>
       </c>
       <c r="C556" s="30" t="inlineStr">
         <is>
-          <t>目标没有生息时有概率额外附加一层。</t>
+          <t>召唤宠物时自动为其附加生息。</t>
         </is>
       </c>
       <c r="E556" s="30" t="inlineStr">
         <is>
-          <t>目标未存在生息时，以30%概率额外附加1层生息</t>
+          <t>己方战斗中召唤宠物时，附加1层【生息】</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="42" t="n">
-        <v>7020002</v>
+        <v>7010002</v>
       </c>
       <c r="B557" s="3" t="inlineStr">
         <is>
-          <t>回春术·兽愈</t>
+          <t>生生不息·厚积</t>
         </is>
       </c>
       <c r="C557" s="30" t="inlineStr">
         <is>
-          <t>治疗时有概率同时治疗气血最低的宠物。</t>
+          <t>生息每回合额外回复一定比例最大气血。</t>
         </is>
       </c>
       <c r="E557" s="30" t="inlineStr">
         <is>
-          <t>30%概率同时对气血最低宠物单位释放1次，造成50%的治疗结果</t>
+          <t>【生息】每回合额外目标回复2%的最大气血，不超过等级*境界倍率*2</t>
         </is>
       </c>
     </row>
     <row r="558" ht="40.5" customHeight="1" s="57">
       <c r="A558" s="42" t="n">
-        <v>7030001</v>
+        <v>7020001</v>
       </c>
       <c r="B558" s="3" t="inlineStr">
         <is>
-          <t>飞花·斩获</t>
+          <t>回春术·妙手</t>
         </is>
       </c>
       <c r="C558" s="30" t="inlineStr">
         <is>
-          <t>击败敌方时附加生息的概率大幅提升。</t>
+          <t>目标没有生息时有概率额外附加一层。</t>
         </is>
       </c>
       <c r="E558" s="30" t="inlineStr">
         <is>
-          <t>击败敌方目标时，增加50%的附加概率（共计70%）</t>
+          <t>目标未存在生息时，以30%概率额外附加1层生息</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="42" t="n">
-        <v>7030002</v>
+        <v>7020002</v>
       </c>
       <c r="B559" s="3" t="inlineStr">
         <is>
-          <t>飞花·滋长</t>
+          <t>回春术·兽愈</t>
         </is>
       </c>
       <c r="C559" s="30" t="inlineStr">
         <is>
-          <t>友方身上的生息越多，飞花伤害越高。</t>
+          <t>治疗时有概率同时治疗气血最低的宠物。</t>
         </is>
       </c>
       <c r="E559" s="30" t="inlineStr">
         <is>
-          <t>己方每有1名存在【生息】的友方，该技能伤害+10%</t>
+          <t>30%概率同时对气血最低宠物单位释放1次，造成50%的治疗结果</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="42" t="n">
+        <v>7030001</v>
+      </c>
+      <c r="B560" s="3" t="inlineStr">
+        <is>
+          <t>飞花·斩获</t>
+        </is>
+      </c>
+      <c r="C560" s="30" t="inlineStr">
+        <is>
+          <t>击败敌方时附加生息的概率大幅提升。</t>
+        </is>
+      </c>
+      <c r="E560" s="30" t="inlineStr">
+        <is>
+          <t>击败敌方目标时，增加50%的附加概率（共计70%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="42" t="n">
+        <v>7030002</v>
+      </c>
+      <c r="B561" s="3" t="inlineStr">
+        <is>
+          <t>飞花·滋长</t>
+        </is>
+      </c>
+      <c r="C561" s="30" t="inlineStr">
+        <is>
+          <t>友方身上的生息越多，飞花伤害越高。</t>
+        </is>
+      </c>
+      <c r="E561" s="30" t="inlineStr">
+        <is>
+          <t>己方每有1名存在【生息】的友方，该技能伤害+10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="562" ht="27" customHeight="1" s="57">
+      <c r="A562" s="42" t="n">
         <v>7040001</v>
       </c>
-      <c r="B560" s="3" t="inlineStr">
+      <c r="B562" s="3" t="inlineStr">
         <is>
           <t>铁壁·金身</t>
         </is>
       </c>
-      <c r="C560" s="30" t="inlineStr">
+      <c r="C562" s="30" t="inlineStr">
         <is>
           <t>低血目标额外获得物理抗暴提升。</t>
         </is>
       </c>
-      <c r="E560" s="30" t="inlineStr">
+      <c r="E562" s="30" t="inlineStr">
         <is>
           <t>目标生命值低于30%时，额外附加【金身】
 【金身】：提升5%物理抗暴并降低20%的物理被爆伤结果</t>
         </is>
       </c>
     </row>
-    <row r="561">
-      <c r="A561" s="42" t="n">
-        <v>7040002</v>
-      </c>
-      <c r="B561" s="3" t="inlineStr">
-        <is>
-          <t>铁壁·护生</t>
-        </is>
-      </c>
-      <c r="C561" s="30" t="inlineStr">
-        <is>
-          <t>召唤宠物时自动附加铁壁。</t>
-        </is>
-      </c>
-      <c r="E561" s="30" t="inlineStr">
-        <is>
-          <t>己方召唤的宠物出场时，附加1层【铁壁】</t>
-        </is>
-      </c>
-    </row>
-    <row r="562" ht="27" customHeight="1" s="57">
-      <c r="A562" s="42" t="n">
-        <v>7050001</v>
-      </c>
-      <c r="B562" s="3" t="inlineStr">
-        <is>
-          <t>绽放·金铁</t>
-        </is>
-      </c>
-      <c r="C562" s="30" t="inlineStr">
-        <is>
-          <t>绽放时额外附加铁壁与金身双重防护。</t>
-        </is>
-      </c>
-      <c r="E562" s="30" t="inlineStr">
-        <is>
-          <t>【绽放】时，附加1层【铁壁】与【金身】</t>
-        </is>
-      </c>
-    </row>
     <row r="563" ht="27" customHeight="1" s="57">
       <c r="A563" s="42" t="n">
-        <v>7050002</v>
+        <v>7040002</v>
       </c>
       <c r="B563" s="3" t="inlineStr">
         <is>
-          <t>绽放·赐怒</t>
+          <t>铁壁·护生</t>
         </is>
       </c>
       <c r="C563" s="30" t="inlineStr">
         <is>
-          <t>绽放概率提升，且绽放后回复目标愤怒。</t>
+          <t>召唤宠物时自动附加铁壁。</t>
         </is>
       </c>
       <c r="E563" s="30" t="inlineStr">
         <is>
-          <t>【绽放】概率提高20%，绽放后回复目标6点愤怒</t>
+          <t>己方召唤的宠物出场时，附加1层【铁壁】</t>
         </is>
       </c>
     </row>
     <row r="564" ht="40.5" customHeight="1" s="57">
       <c r="A564" s="42" t="n">
-        <v>7060001</v>
+        <v>7050001</v>
       </c>
       <c r="B564" s="3" t="inlineStr">
         <is>
-          <t>醍醐·急救</t>
+          <t>绽放·金铁</t>
         </is>
       </c>
       <c r="C564" s="30" t="inlineStr">
         <is>
-          <t>低血目标的结算治疗量大幅增加，同时回复内伤。</t>
+          <t>绽放时额外附加铁壁与金身双重防护。</t>
         </is>
       </c>
       <c r="E564" s="30" t="inlineStr">
         <is>
-          <t>气血低于 50% 的目标，结算治疗倍率额外 +50%。同时回复治疗结果15%的内伤</t>
+          <t>【绽放】时，附加1层【铁壁】与【金身】</t>
         </is>
       </c>
     </row>
     <row r="565" ht="40.5" customHeight="1" s="57">
       <c r="A565" s="42" t="n">
-        <v>7060002</v>
+        <v>7050002</v>
       </c>
       <c r="B565" s="3" t="inlineStr">
         <is>
-          <t>醍醐·驱毒</t>
+          <t>绽放·赐怒</t>
         </is>
       </c>
       <c r="C565" s="30" t="inlineStr">
         <is>
-          <t>结算时每层生息有概率清除目标身上的减益。</t>
+          <t>绽放概率提升，且绽放后回复目标愤怒。</t>
         </is>
       </c>
       <c r="E565" s="30" t="inlineStr">
         <is>
-          <t>结算时，每层生息以30%概率清除结算单位1个非封印减益</t>
+          <t>【绽放】概率提高20%，绽放后回复目标6点愤怒</t>
         </is>
       </c>
     </row>
     <row r="566" ht="27" customHeight="1" s="57">
       <c r="A566" s="42" t="n">
+        <v>7060001</v>
+      </c>
+      <c r="B566" s="3" t="inlineStr">
+        <is>
+          <t>醍醐·急救</t>
+        </is>
+      </c>
+      <c r="C566" s="30" t="inlineStr">
+        <is>
+          <t>低血目标的结算治疗量大幅增加，同时回复内伤。</t>
+        </is>
+      </c>
+      <c r="E566" s="30" t="inlineStr">
+        <is>
+          <t>气血低于 50% 的目标，结算治疗倍率额外 +50%。同时回复治疗结果15%的内伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="27" customHeight="1" s="57">
+      <c r="A567" s="42" t="n">
+        <v>7060002</v>
+      </c>
+      <c r="B567" s="3" t="inlineStr">
+        <is>
+          <t>醍醐·驱毒</t>
+        </is>
+      </c>
+      <c r="C567" s="30" t="inlineStr">
+        <is>
+          <t>结算时每层生息有概率清除目标身上的减益。</t>
+        </is>
+      </c>
+      <c r="E567" s="30" t="inlineStr">
+        <is>
+          <t>结算时，每层生息以30%概率清除结算单位1个非封印减益</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="27" customHeight="1" s="57">
+      <c r="A568" s="42" t="n">
         <v>7070001</v>
       </c>
-      <c r="B566" s="3" t="inlineStr">
+      <c r="B568" s="3" t="inlineStr">
         <is>
           <t>逢春·免死</t>
         </is>
       </c>
-      <c r="C566" s="30" t="inlineStr">
+      <c r="C568" s="30" t="inlineStr">
         <is>
           <t>复活后附加免死效果，致命伤害下保住性命。</t>
         </is>
       </c>
-      <c r="E566" s="30" t="inlineStr">
+      <c r="E568" s="30" t="inlineStr">
         <is>
           <t>附加【免死】状态1回合
 使其本回合免死1次，受到致命伤害时免死并回复1血，同时清除免死状态</t>
         </is>
       </c>
     </row>
-    <row r="567" ht="27" customHeight="1" s="57">
-      <c r="A567" s="42" t="n">
+    <row r="569">
+      <c r="A569" s="42" t="n">
         <v>7070002</v>
       </c>
-      <c r="B567" s="3" t="inlineStr">
+      <c r="B569" s="3" t="inlineStr">
         <is>
           <t>逢春·药引</t>
         </is>
       </c>
-      <c r="C567" s="30" t="inlineStr">
+      <c r="C569" s="30" t="inlineStr">
         <is>
           <t>复活后附加药引效果，药品回复能力提升。</t>
         </is>
       </c>
-      <c r="E567" s="30" t="inlineStr">
+      <c r="E569" s="30" t="inlineStr">
         <is>
           <t>复活后，附加【药引】状态2回合，
 使其2回合内受到药品回复效果增加30%（包括回蓝回血）</t>
         </is>
       </c>
     </row>
-    <row r="568" ht="27" customHeight="1" s="57">
-      <c r="A568" s="42" t="n">
-        <v>7080001</v>
-      </c>
-      <c r="B568" s="3" t="inlineStr">
-        <is>
-          <t>枯荣·转虚</t>
-        </is>
-      </c>
-      <c r="C568" s="30" t="inlineStr">
-        <is>
-          <t>敌方宠物满层虚弱离场时传染给物伤最高的敌方。</t>
-        </is>
-      </c>
-      <c r="E568" s="30" t="inlineStr">
-        <is>
-          <t>对方宠物单位3层【虚弱】离场时，转移1层【虚弱】层数给对方物伤最高单位上</t>
-        </is>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" s="42" t="n">
-        <v>7080002</v>
-      </c>
-      <c r="B569" s="3" t="inlineStr">
-        <is>
-          <t>枯荣·趁虚</t>
-        </is>
-      </c>
-      <c r="C569" s="30" t="inlineStr">
-        <is>
-          <t>我方宠物攻击被虚弱的目标时物理伤害提升。</t>
-        </is>
-      </c>
-      <c r="E569" s="30" t="inlineStr">
-        <is>
-          <t>我方宠物物理攻击【虚弱】单位时，物理伤害结果+10%</t>
-        </is>
-      </c>
-    </row>
     <row r="570" ht="27" customHeight="1" s="57">
       <c r="A570" s="42" t="n">
-        <v>7090001</v>
+        <v>7080001</v>
       </c>
       <c r="B570" s="3" t="inlineStr">
         <is>
-          <t>万象复苏·大愈</t>
+          <t>枯荣·转虚</t>
         </is>
       </c>
       <c r="C570" s="30" t="inlineStr">
         <is>
-          <t>复活多人时额外回复大量内伤。</t>
+          <t>敌方宠物满层虚弱离场时传染给物伤最高的敌方。</t>
         </is>
       </c>
       <c r="E570" s="30" t="inlineStr">
         <is>
-          <t>若复活=2人，额外回复30%回复结果(总计50%）的内伤</t>
+          <t>对方宠物单位3层【虚弱】离场时，转移1层【虚弱】层数给对方物伤最高单位上</t>
         </is>
       </c>
     </row>
     <row r="571" ht="27" customHeight="1" s="57">
       <c r="A571" s="42" t="n">
-        <v>7090002</v>
+        <v>7080002</v>
       </c>
       <c r="B571" s="3" t="inlineStr">
         <is>
-          <t>万象复苏·遍洒</t>
+          <t>枯荣·趁虚</t>
         </is>
       </c>
       <c r="C571" s="30" t="inlineStr">
         <is>
-          <t>同时为所有非人物单位附加生息持续回血。</t>
+          <t>我方宠物攻击被虚弱的目标时物理伤害提升。</t>
         </is>
       </c>
       <c r="E571" s="30" t="inlineStr">
         <is>
-          <t>为全体非人物单位额外附加1层【生息】。</t>
+          <t>我方宠物物理攻击【虚弱】单位时，物理伤害结果+10%</t>
         </is>
       </c>
     </row>
     <row r="572" ht="27" customHeight="1" s="57">
       <c r="A572" s="42" t="n">
-        <v>8010001</v>
+        <v>7090001</v>
       </c>
       <c r="B572" s="3" t="inlineStr">
         <is>
-          <t>化形·执念</t>
+          <t>万象复苏·大愈</t>
         </is>
       </c>
       <c r="C572" s="30" t="inlineStr">
         <is>
-          <t>封印未触发化形时下次成功概率持续提升。</t>
+          <t>复活多人时额外回复大量内伤。</t>
         </is>
       </c>
       <c r="E572" s="30" t="inlineStr">
         <is>
-          <t>封印命中后未获得化形时，下一次成功施加封印时获得化形的概率增加20%，可叠加3次</t>
+          <t>若复活=2人，额外回复30%回复结果(总计50%）的内伤</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="42" t="n">
-        <v>8010002</v>
+        <v>7090002</v>
       </c>
       <c r="B573" s="3" t="inlineStr">
         <is>
-          <t>化形·突袭</t>
+          <t>万象复苏·遍洒</t>
         </is>
       </c>
       <c r="C573" s="30" t="inlineStr">
         <is>
-          <t>获得化形时有概率立刻对随机敌方发起攻击。</t>
+          <t>同时为所有非人物单位附加生息持续回血。</t>
         </is>
       </c>
       <c r="E573" s="30" t="inlineStr">
         <is>
-          <t>宠物获得化形时，50% 概率立刻对敌方随机目标释放 1 次法术攻击或普通攻击（优先释放法术）</t>
+          <t>为全体非人物单位额外附加1层【生息】。</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="42" t="n">
-        <v>8020001</v>
+        <v>8010001</v>
       </c>
       <c r="B574" s="3" t="inlineStr">
         <is>
-          <t>醉生梦死·破灵</t>
+          <t>化形·执念</t>
         </is>
       </c>
       <c r="C574" s="30" t="inlineStr">
         <is>
-          <t>封印成功时有概率附加脆弱或裂魂。</t>
+          <t>封印未触发化形时下次成功概率持续提升。</t>
         </is>
       </c>
       <c r="E574" s="30" t="inlineStr">
         <is>
-          <t>封印成功时，30%概率为对方附加【脆弱】或【裂魂】效果</t>
+          <t>封印命中后未获得化形时，下一次成功施加封印时获得化形的概率增加20%，可叠加3次</t>
         </is>
       </c>
     </row>
     <row r="575" ht="27" customHeight="1" s="57">
       <c r="A575" s="42" t="n">
-        <v>8020002</v>
+        <v>8010002</v>
       </c>
       <c r="B575" s="3" t="inlineStr">
         <is>
-          <t>醉生梦死·必化</t>
+          <t>化形·突袭</t>
         </is>
       </c>
       <c r="C575" s="30" t="inlineStr">
         <is>
-          <t>两个目标均封印成功时必定触发宠物化形。</t>
+          <t>获得化形时有概率立刻对随机敌方发起攻击。</t>
         </is>
       </c>
       <c r="E575" s="30" t="inlineStr">
         <is>
-          <t>两个目标均封印成功时，必定触发【化形】</t>
+          <t>宠物获得化形时，50% 概率立刻对敌方随机目标释放 1 次法术攻击或普通攻击（优先释放法术）</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="42" t="n">
-        <v>8030001</v>
+        <v>8020001</v>
       </c>
       <c r="B576" s="3" t="inlineStr">
         <is>
-          <t>霓裳·恃速</t>
+          <t>醉生梦死·破灵</t>
         </is>
       </c>
       <c r="C576" s="30" t="inlineStr">
         <is>
-          <t>攻击速度低于自身的目标时伤害大幅提升。</t>
+          <t>封印成功时有概率附加脆弱或裂魂。</t>
         </is>
       </c>
       <c r="E576" s="30" t="inlineStr">
         <is>
-          <t>攻击速度低于自身的目标时，增加50%的技能伤害</t>
+          <t>封印成功时，30%概率为对方附加【脆弱】或【裂魂】效果</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="42" t="n">
-        <v>8030002</v>
+        <v>8020002</v>
       </c>
       <c r="B577" s="3" t="inlineStr">
         <is>
-          <t>霓裳·克灵</t>
+          <t>醉生梦死·必化</t>
         </is>
       </c>
       <c r="C577" s="30" t="inlineStr">
         <is>
-          <t>攻击宠物时封禁概率大幅提升。</t>
+          <t>两个目标均封印成功时必定触发宠物化形。</t>
         </is>
       </c>
       <c r="E577" s="30" t="inlineStr">
         <is>
-          <t>攻击非人物单位时，【封技】概率额外增加 12%。(累计20%）</t>
+          <t>两个目标均封印成功时，必定触发【化形】</t>
         </is>
       </c>
     </row>
     <row r="578" ht="27" customHeight="1" s="57">
       <c r="A578" s="42" t="n">
-        <v>8040001</v>
+        <v>8030001</v>
       </c>
       <c r="B578" s="3" t="inlineStr">
         <is>
-          <t>幻惑·蛊毒</t>
+          <t>霓裳·恃速</t>
         </is>
       </c>
       <c r="C578" s="30" t="inlineStr">
         <is>
-          <t>每剥离一个增益就附加一层蛊毒持续伤害。</t>
+          <t>攻击速度低于自身的目标时伤害大幅提升。</t>
         </is>
       </c>
       <c r="E578" s="30" t="inlineStr">
         <is>
-          <t>目标每被移除一个增益效果，为目标附加1层【蛊毒】</t>
+          <t>攻击速度低于自身的目标时，增加50%的技能伤害</t>
         </is>
       </c>
     </row>
     <row r="579" ht="27" customHeight="1" s="57">
       <c r="A579" s="42" t="n">
-        <v>8040002</v>
+        <v>8030002</v>
       </c>
       <c r="B579" s="3" t="inlineStr">
         <is>
-          <t>幻惑·偷取</t>
+          <t>霓裳·克灵</t>
         </is>
       </c>
       <c r="C579" s="30" t="inlineStr">
         <is>
-          <t>剥离增益时有概率将其偷取到自身。</t>
+          <t>攻击宠物时封禁概率大幅提升。</t>
         </is>
       </c>
       <c r="E579" s="30" t="inlineStr">
         <is>
-          <t>目标被驱散增益效果时，30%概率将其偷窃到自身上</t>
+          <t>攻击非人物单位时，【封技】概率额外增加 12%。(累计20%）</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="42" t="n">
-        <v>8050001</v>
+        <v>8040001</v>
       </c>
       <c r="B580" s="3" t="inlineStr">
         <is>
-          <t>擅变·同气</t>
+          <t>幻惑·蛊毒</t>
         </is>
       </c>
       <c r="C580" s="30" t="inlineStr">
         <is>
-          <t>场上每存在一种化形类型，所有宠物伤害与减免均提升。</t>
+          <t>每剥离一个增益就附加一层蛊毒持续伤害。</t>
         </is>
       </c>
       <c r="E580" s="30" t="inlineStr">
         <is>
-          <t>己方宠物每存在1种类型化形时，增加己方所有在场宠物5%的伤害结果与5%的伤害减免</t>
+          <t>目标每被移除一个增益效果，为目标附加1层【蛊毒】</t>
         </is>
       </c>
     </row>
     <row r="581" ht="27" customHeight="1" s="57">
       <c r="A581" s="42" t="n">
-        <v>8050002</v>
+        <v>8040002</v>
       </c>
       <c r="B581" s="3" t="inlineStr">
         <is>
-          <t>擅变·传承</t>
+          <t>幻惑·偷取</t>
         </is>
       </c>
       <c r="C581" s="30" t="inlineStr">
         <is>
-          <t>化形宠物倒地时有概率将化形传承给其他宠物。</t>
+          <t>剥离增益时有概率将其偷取到自身。</t>
         </is>
       </c>
       <c r="E581" s="30" t="inlineStr">
         <is>
-          <t>化形宠物倒地时，50%概率减少1回合将其继承给未存在化形的宠物上</t>
+          <t>目标被驱散增益效果时，30%概率将其偷窃到自身上</t>
         </is>
       </c>
     </row>
     <row r="582" ht="27" customHeight="1" s="57">
       <c r="A582" s="42" t="n">
-        <v>8060001</v>
+        <v>8050001</v>
       </c>
       <c r="B582" s="3" t="inlineStr">
         <is>
-          <t>妖雾·反蛊</t>
+          <t>擅变·同气</t>
         </is>
       </c>
       <c r="C582" s="30" t="inlineStr">
         <is>
-          <t>成功闪避时为攻击者附加蛊毒。</t>
+          <t>场上每存在一种化形类型，所有宠物伤害与减免均提升。</t>
         </is>
       </c>
       <c r="E582" s="30" t="inlineStr">
         <is>
-          <t>成功躲避攻击时，为攻击来源单位附加1层【蛊毒】</t>
+          <t>己方宠物每存在1种类型化形时，增加己方所有在场宠物5%的伤害结果与5%的伤害减免</t>
         </is>
       </c>
     </row>
     <row r="583" ht="27" customHeight="1" s="57">
       <c r="A583" s="42" t="n">
+        <v>8050002</v>
+      </c>
+      <c r="B583" s="3" t="inlineStr">
+        <is>
+          <t>擅变·传承</t>
+        </is>
+      </c>
+      <c r="C583" s="30" t="inlineStr">
+        <is>
+          <t>化形宠物倒地时有概率将化形传承给其他宠物。</t>
+        </is>
+      </c>
+      <c r="E583" s="30" t="inlineStr">
+        <is>
+          <t>化形宠物倒地时，50%概率减少1回合将其继承给未存在化形的宠物上</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="42" t="n">
+        <v>8060001</v>
+      </c>
+      <c r="B584" s="3" t="inlineStr">
+        <is>
+          <t>妖雾·反蛊</t>
+        </is>
+      </c>
+      <c r="C584" s="30" t="inlineStr">
+        <is>
+          <t>成功闪避时为攻击者附加蛊毒。</t>
+        </is>
+      </c>
+      <c r="E584" s="30" t="inlineStr">
+        <is>
+          <t>成功躲避攻击时，为攻击来源单位附加1层【蛊毒】</t>
+        </is>
+      </c>
+    </row>
+    <row r="585" ht="27" customHeight="1" s="57">
+      <c r="A585" s="42" t="n">
         <v>8060002</v>
       </c>
-      <c r="B583" s="3" t="inlineStr">
+      <c r="B585" s="3" t="inlineStr">
         <is>
           <t>妖雾·窃怒</t>
         </is>
       </c>
-      <c r="C583" s="30" t="inlineStr">
+      <c r="C585" s="30" t="inlineStr">
         <is>
           <t>成功闪避时回复愤怒。</t>
         </is>
       </c>
-      <c r="E583" s="30" t="inlineStr">
+      <c r="E585" s="30" t="inlineStr">
         <is>
           <t>成功躲避攻击时，为自身回复3点愤怒
 每回合至多回复15点</t>
         </is>
       </c>
     </row>
-    <row r="584">
-      <c r="A584" s="42" t="n">
-        <v>8070001</v>
-      </c>
-      <c r="B584" s="3" t="inlineStr">
-        <is>
-          <t>绝息·削抗</t>
-        </is>
-      </c>
-      <c r="C584" s="30" t="inlineStr">
-        <is>
-          <t>释放后削弱目标的封印抵抗能力。</t>
-        </is>
-      </c>
-      <c r="E584" s="30" t="inlineStr">
-        <is>
-          <t>释放后，附加【削抗】DEBUFF，使其封印抵抗降低 10%，持续 4 回合</t>
-        </is>
-      </c>
-    </row>
-    <row r="585" ht="27" customHeight="1" s="57">
-      <c r="A585" s="42" t="n">
-        <v>8070002</v>
-      </c>
-      <c r="B585" s="3" t="inlineStr">
-        <is>
-          <t>绝息·追绝</t>
-        </is>
-      </c>
-      <c r="C585" s="30" t="inlineStr">
-        <is>
-          <t>绝息目标被击败时绝息效果延长传递。</t>
-        </is>
-      </c>
-      <c r="E585" s="30" t="inlineStr">
-        <is>
-          <t>【绝息】目标被击败时，其【绝息】持续时间延长1回合</t>
-        </is>
-      </c>
-    </row>
     <row r="586">
       <c r="A586" s="42" t="n">
-        <v>8080001</v>
+        <v>8070001</v>
       </c>
       <c r="B586" s="3" t="inlineStr">
         <is>
-          <t>裂魂爪·深创</t>
+          <t>绝息·削抗</t>
         </is>
       </c>
       <c r="C586" s="30" t="inlineStr">
         <is>
-          <t>目标重伤层数越多固定伤害越高。</t>
+          <t>释放后削弱目标的封印抵抗能力。</t>
         </is>
       </c>
       <c r="E586" s="30" t="inlineStr">
         <is>
-          <t>每层【重伤】增加该技能30%的固定伤害</t>
+          <t>释放后，附加【削抗】DEBUFF，使其封印抵抗降低 10%，持续 4 回合</t>
         </is>
       </c>
     </row>
     <row r="587" ht="27" customHeight="1" s="57">
       <c r="A587" s="42" t="n">
+        <v>8070002</v>
+      </c>
+      <c r="B587" s="3" t="inlineStr">
+        <is>
+          <t>绝息·追绝</t>
+        </is>
+      </c>
+      <c r="C587" s="30" t="inlineStr">
+        <is>
+          <t>绝息目标被击败时绝息效果延长传递。</t>
+        </is>
+      </c>
+      <c r="E587" s="30" t="inlineStr">
+        <is>
+          <t>【绝息】目标被击败时，其【绝息】持续时间延长1回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="42" t="n">
+        <v>8080001</v>
+      </c>
+      <c r="B588" s="3" t="inlineStr">
+        <is>
+          <t>裂魂爪·深创</t>
+        </is>
+      </c>
+      <c r="C588" s="30" t="inlineStr">
+        <is>
+          <t>目标重伤层数越多固定伤害越高。</t>
+        </is>
+      </c>
+      <c r="E588" s="30" t="inlineStr">
+        <is>
+          <t>每层【重伤】增加该技能30%的固定伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="42" t="n">
         <v>8080002</v>
       </c>
-      <c r="B587" s="3" t="inlineStr">
+      <c r="B589" s="3" t="inlineStr">
         <is>
           <t>裂魂爪·兽怒</t>
         </is>
       </c>
-      <c r="C587" s="30" t="inlineStr">
+      <c r="C589" s="30" t="inlineStr">
         <is>
           <t>化形宠物攻击重伤目标时暴击伤害大幅提升。</t>
         </is>
       </c>
-      <c r="E587" s="30" t="inlineStr">
+      <c r="E589" s="30" t="inlineStr">
         <is>
           <t>己方【化形】宠物对【重伤】目标攻击时
 增加30%的暴击伤害结果</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" s="42" t="n">
+    <row r="590">
+      <c r="A590" s="42" t="n">
         <v>8090001</v>
       </c>
-      <c r="B588" s="3" t="inlineStr">
+      <c r="B590" s="3" t="inlineStr">
         <is>
           <t>上古妖形·重置</t>
         </is>
       </c>
-      <c r="C588" s="30" t="inlineStr">
+      <c r="C590" s="30" t="inlineStr">
         <is>
           <t>进化后化形持续时间重置为满。</t>
         </is>
       </c>
-      <c r="E588" s="30" t="inlineStr">
+      <c r="E590" s="30" t="inlineStr">
         <is>
           <t>释放后，进化后的化形持续时间重置为4回合</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" s="42" t="n">
+    <row r="591">
+      <c r="A591" s="42" t="n">
         <v>8090002</v>
       </c>
-      <c r="B589" s="3" t="inlineStr">
+      <c r="B591" s="3" t="inlineStr">
         <is>
           <t>上古妖形·赐形</t>
         </is>
       </c>
-      <c r="C589" s="30" t="inlineStr">
+      <c r="C591" s="30" t="inlineStr">
         <is>
           <t>释放时额外为一个宠物赋予进化后的化形。</t>
         </is>
       </c>
-      <c r="E589" s="30" t="inlineStr">
+      <c r="E591" s="30" t="inlineStr">
         <is>
           <t>释放时，随机为我方1个宠物单位赋予1个进化后的化形</t>
         </is>
@@ -29475,78 +29505,207 @@
       </c>
     </row>
     <row r="153" ht="71.09999999999999" customHeight="1" s="57" thickBot="1">
-      <c r="A153" s="6" t="n">
+      <c r="A153" s="98" t="n">
+        <v>8600</v>
+      </c>
+      <c r="B153" s="98" t="inlineStr">
+        <is>
+          <t>焚天决·起手</t>
+        </is>
+      </c>
+      <c r="C153" s="98" t="n"/>
+      <c r="D153" s="98" t="n"/>
+      <c r="E153" s="98" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="F153" s="98" t="inlineStr">
+        <is>
+          <t>attack_damage</t>
+        </is>
+      </c>
+      <c r="G153" s="98" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="H153" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" s="98" t="n"/>
+      <c r="J153" s="99" t="n"/>
+      <c r="K153" s="99" t="n"/>
+      <c r="L153" s="98" t="n"/>
+      <c r="M153" s="98" t="n"/>
+      <c r="N153" s="98" t="n"/>
+      <c r="O153" s="98" t="n"/>
+      <c r="P153" s="98" t="n"/>
+      <c r="Q153" s="98" t="n"/>
+      <c r="R153" s="98" t="n"/>
+      <c r="S153" s="98" t="n"/>
+      <c r="T153" s="98" t="n"/>
+      <c r="U153" s="99" t="n"/>
+      <c r="V153" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="W153" s="98" t="n"/>
+      <c r="X153" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y153" s="98" t="n"/>
+      <c r="Z153" s="98" t="n"/>
+      <c r="AA153" s="98" t="n"/>
+      <c r="AB153" s="98" t="n"/>
+      <c r="AC153" s="98" t="n"/>
+      <c r="AD153" s="98" t="n"/>
+      <c r="AE153" s="98" t="n"/>
+      <c r="AF153" s="98" t="n"/>
+      <c r="AG153" s="98" t="n"/>
+      <c r="AH153" s="98" t="n"/>
+      <c r="AI153" s="98" t="n"/>
+      <c r="AJ153" s="98" t="n"/>
+      <c r="AK153" s="98" t="n"/>
+      <c r="AL153" s="98" t="n"/>
+    </row>
+    <row r="154" ht="63" customHeight="1" s="57" thickBot="1" thickTop="1">
+      <c r="A154" s="98" t="n">
+        <v>8601</v>
+      </c>
+      <c r="B154" s="98" t="inlineStr">
+        <is>
+          <t>焚天决·进阶</t>
+        </is>
+      </c>
+      <c r="C154" s="98" t="n"/>
+      <c r="D154" s="98" t="n"/>
+      <c r="E154" s="98" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="F154" s="98" t="inlineStr">
+        <is>
+          <t>attack_damage</t>
+        </is>
+      </c>
+      <c r="G154" s="98" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="H154" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" s="98" t="n"/>
+      <c r="J154" s="99" t="n"/>
+      <c r="K154" s="99" t="n"/>
+      <c r="L154" s="98" t="n"/>
+      <c r="M154" s="98" t="n"/>
+      <c r="N154" s="98" t="n"/>
+      <c r="O154" s="98" t="n"/>
+      <c r="P154" s="98" t="n"/>
+      <c r="Q154" s="98" t="n"/>
+      <c r="R154" s="98" t="n"/>
+      <c r="S154" s="98" t="n"/>
+      <c r="T154" s="98" t="n"/>
+      <c r="U154" s="99" t="n"/>
+      <c r="V154" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="W154" s="98" t="n"/>
+      <c r="X154" s="98" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y154" s="98" t="n"/>
+      <c r="Z154" s="98" t="n"/>
+      <c r="AA154" s="98" t="n"/>
+      <c r="AB154" s="98" t="n"/>
+      <c r="AC154" s="98" t="n"/>
+      <c r="AD154" s="98" t="n"/>
+      <c r="AE154" s="98" t="n"/>
+      <c r="AF154" s="98" t="n"/>
+      <c r="AG154" s="98" t="n"/>
+      <c r="AH154" s="98" t="n"/>
+      <c r="AI154" s="98" t="n"/>
+      <c r="AJ154" s="98" t="n"/>
+      <c r="AK154" s="98" t="n"/>
+      <c r="AL154" s="98" t="n"/>
+    </row>
+    <row r="155" ht="32.25" customFormat="1" customHeight="1" s="71" thickTop="1">
+      <c r="A155" s="6" t="n">
         <v>114514</v>
       </c>
-      <c r="B153" s="6" t="inlineStr">
+      <c r="B155" s="6" t="inlineStr">
         <is>
           <t>测试技能</t>
         </is>
       </c>
-      <c r="C153" s="6" t="n"/>
-      <c r="E153" s="0" t="inlineStr">
+      <c r="C155" s="6" t="n"/>
+      <c r="D155" s="3" t="n"/>
+      <c r="E155" s="0" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="F153" s="0" t="inlineStr">
+      <c r="F155" s="0" t="inlineStr">
         <is>
           <t>attack_damage</t>
         </is>
       </c>
-      <c r="G153" s="19" t="n"/>
-      <c r="H153" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I153" s="19" t="n"/>
-      <c r="J153" s="0" t="n">
+      <c r="G155" s="19" t="n"/>
+      <c r="H155" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" s="19" t="n"/>
+      <c r="J155" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K153" s="19" t="n"/>
-      <c r="L153" s="0" t="n">
+      <c r="K155" s="19" t="n"/>
+      <c r="L155" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M153" s="0" t="inlineStr">
+      <c r="M155" s="0" t="inlineStr">
         <is>
           <t>CurrHP,2,(HPMax, 0.1)</t>
         </is>
       </c>
-      <c r="O153" s="0" t="inlineStr">
+      <c r="O155" s="0" t="inlineStr">
         <is>
           <t>enemy</t>
         </is>
       </c>
-      <c r="Q153" s="0" t="inlineStr">
+      <c r="Q155" s="0" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="S153" s="0" t="inlineStr">
+      <c r="S155" s="0" t="inlineStr">
         <is>
           <t>alive</t>
         </is>
       </c>
-      <c r="T153" s="0" t="inlineStr">
+      <c r="T155" s="0" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="U153" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V153" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W153" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X153" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y153" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA153" s="0" t="inlineStr">
+      <c r="U155" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V155" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W155" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X155" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y155" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA155" s="0" t="inlineStr">
         <is>
           <t>释放消耗气血_最大气血百分比=0.1
 休息buff=107
@@ -29555,226 +29714,81 @@
 第三次攻击伤害倍率=1.2</t>
         </is>
       </c>
-      <c r="AB153" s="0" t="inlineStr">
+      <c r="AB155" s="0" t="inlineStr">
         <is>
           <t>code.Spell_102_1</t>
         </is>
       </c>
-      <c r="AC153" s="0" t="inlineStr">
+      <c r="AC155" s="0" t="inlineStr">
         <is>
           <t>code.Spell_102_2</t>
         </is>
       </c>
-      <c r="AD153" s="0" t="inlineStr">
+      <c r="AD155" s="0" t="inlineStr">
         <is>
           <t>code.Spell_102_3</t>
         </is>
       </c>
-      <c r="AE153" s="0" t="inlineStr">
+      <c r="AE155" s="0" t="inlineStr">
         <is>
           <t>AirAttack</t>
         </is>
       </c>
-      <c r="AF153" s="0" t="inlineStr">
+      <c r="AF155" s="0" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="AG153" s="0" t="inlineStr">
+      <c r="AG155" s="0" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="AH153" s="0" t="inlineStr">
+      <c r="AH155" s="0" t="inlineStr">
         <is>
           <t>SlowHuiDao</t>
         </is>
       </c>
-      <c r="AI153" s="0" t="inlineStr">
+      <c r="AI155" s="0" t="inlineStr">
         <is>
           <t>magic</t>
         </is>
       </c>
-      <c r="AJ153" s="0" t="inlineStr">
+      <c r="AJ155" s="0" t="inlineStr">
         <is>
           <t>SlowHuiDao</t>
         </is>
       </c>
-      <c r="AK153" s="0" t="inlineStr">
+      <c r="AK155" s="0" t="inlineStr">
         <is>
           <t>magic</t>
         </is>
       </c>
-      <c r="AL153" s="0" t="inlineStr">
+      <c r="AL155" s="0" t="inlineStr">
         <is>
           <t>SlowHuiDao</t>
         </is>
       </c>
-    </row>
-    <row r="154" ht="63" customHeight="1" s="57" thickBot="1" thickTop="1">
-      <c r="A154" s="21" t="n">
-        <v>200002</v>
-      </c>
-      <c r="B154" s="19" t="inlineStr">
-        <is>
-          <t>反击</t>
-        </is>
-      </c>
-      <c r="C154" s="21" t="n"/>
-      <c r="E154" s="19" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="F154" s="19" t="inlineStr">
-        <is>
-          <t>attack_damage</t>
-        </is>
-      </c>
-      <c r="G154" s="19" t="n"/>
-      <c r="H154" s="19" t="n"/>
-      <c r="I154" s="19" t="n"/>
-      <c r="J154" s="19" t="n"/>
-      <c r="K154" s="19" t="n"/>
-      <c r="M154" s="71" t="n"/>
-      <c r="O154" s="11" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="Q154" s="11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="S154" s="11" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
-      <c r="U154" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V154" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="W154" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X154" s="3" t="n"/>
-      <c r="AA154" s="95" t="n"/>
-      <c r="AB154" s="19" t="inlineStr">
-        <is>
-          <t>code.Spell_200002</t>
-        </is>
-      </c>
-      <c r="AE154" s="11" t="inlineStr">
-        <is>
-          <t>BaseAttack</t>
-        </is>
-      </c>
-      <c r="AG154" s="11" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="AH154" s="3" t="n"/>
-      <c r="AI154" s="21" t="n"/>
-      <c r="AK154" s="21" t="n"/>
-    </row>
-    <row r="155" ht="32.25" customFormat="1" customHeight="1" s="71" thickTop="1">
-      <c r="A155" s="21" t="n">
-        <v>200003</v>
-      </c>
-      <c r="B155" s="19" t="inlineStr">
-        <is>
-          <t>反震</t>
-        </is>
-      </c>
-      <c r="C155" s="21" t="n"/>
-      <c r="D155" s="3" t="n"/>
-      <c r="E155" s="19" t="inlineStr">
-        <is>
-          <t>magic</t>
-        </is>
-      </c>
-      <c r="F155" s="19" t="inlineStr">
-        <is>
-          <t>magic_damage</t>
-        </is>
-      </c>
-      <c r="G155" s="19" t="n"/>
-      <c r="H155" s="19" t="n"/>
-      <c r="I155" s="19" t="n"/>
-      <c r="J155" s="19" t="n"/>
-      <c r="K155" s="19" t="n"/>
-      <c r="M155" s="71" t="n"/>
-      <c r="O155" s="11" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="Q155" s="11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="S155" s="11" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
-      <c r="U155" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V155" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="W155" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB155" s="19" t="inlineStr">
-        <is>
-          <t>code.Spell_200003</t>
-        </is>
-      </c>
-      <c r="AE155" s="11" t="inlineStr">
-        <is>
-          <t>BaseMagic</t>
-        </is>
-      </c>
-      <c r="AG155" s="11" t="inlineStr">
-        <is>
-          <t>magic</t>
-        </is>
-      </c>
-      <c r="AH155" s="11" t="inlineStr">
-        <is>
-          <t>FaQiu</t>
-        </is>
-      </c>
-      <c r="AI155" s="21" t="n"/>
-      <c r="AK155" s="21" t="n"/>
     </row>
     <row r="156" ht="32.25" customHeight="1" s="57">
       <c r="A156" s="21" t="n">
-        <v>200004</v>
+        <v>200002</v>
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>法术反击</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="C156" s="21" t="n"/>
       <c r="D156" s="3" t="n"/>
       <c r="E156" s="19" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F156" s="19" t="inlineStr">
         <is>
-          <t>magic_damage</t>
+          <t>attack_damage</t>
         </is>
       </c>
       <c r="G156" s="19" t="n"/>
@@ -29782,7 +29796,7 @@
       <c r="I156" s="19" t="n"/>
       <c r="J156" s="19" t="n"/>
       <c r="K156" s="19" t="n"/>
-      <c r="M156" s="3" t="n"/>
+      <c r="M156" s="71" t="n"/>
       <c r="O156" s="11" t="inlineStr">
         <is>
           <t>enemy</t>
@@ -29807,48 +29821,46 @@
       <c r="W156" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="X156" s="3" t="n"/>
+      <c r="AA156" s="95" t="n"/>
       <c r="AB156" s="19" t="inlineStr">
         <is>
-          <t>code.Spell_200004</t>
+          <t>code.Spell_200002</t>
         </is>
       </c>
       <c r="AE156" s="11" t="inlineStr">
         <is>
-          <t>BaseMagic</t>
+          <t>BaseAttack</t>
         </is>
       </c>
       <c r="AG156" s="11" t="inlineStr">
         <is>
-          <t>magic</t>
-        </is>
-      </c>
-      <c r="AH156" s="11" t="inlineStr">
-        <is>
-          <t>FaQiu</t>
-        </is>
-      </c>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="AH156" s="3" t="n"/>
       <c r="AI156" s="21" t="n"/>
       <c r="AK156" s="21" t="n"/>
     </row>
     <row r="157" ht="32.25" customHeight="1" s="57">
       <c r="A157" s="21" t="n">
-        <v>200005</v>
+        <v>200003</v>
       </c>
       <c r="B157" s="19" t="inlineStr">
         <is>
-          <t>物理追击</t>
+          <t>反震</t>
         </is>
       </c>
       <c r="C157" s="21" t="n"/>
       <c r="D157" s="3" t="n"/>
       <c r="E157" s="19" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>magic</t>
         </is>
       </c>
       <c r="F157" s="19" t="inlineStr">
         <is>
-          <t>attack_damage</t>
+          <t>magic_damage</t>
         </is>
       </c>
       <c r="G157" s="19" t="n"/>
@@ -29856,7 +29868,7 @@
       <c r="I157" s="19" t="n"/>
       <c r="J157" s="19" t="n"/>
       <c r="K157" s="19" t="n"/>
-      <c r="M157" s="3" t="n"/>
+      <c r="M157" s="71" t="n"/>
       <c r="O157" s="11" t="inlineStr">
         <is>
           <t>enemy</t>
@@ -29883,30 +29895,34 @@
       </c>
       <c r="AB157" s="19" t="inlineStr">
         <is>
-          <t>code.Spell_200005</t>
+          <t>code.Spell_200003</t>
         </is>
       </c>
       <c r="AE157" s="11" t="inlineStr">
         <is>
-          <t>BaseAttack</t>
+          <t>BaseMagic</t>
         </is>
       </c>
       <c r="AG157" s="11" t="inlineStr">
         <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="AH157" s="11" t="n"/>
+          <t>magic</t>
+        </is>
+      </c>
+      <c r="AH157" s="11" t="inlineStr">
+        <is>
+          <t>FaQiu</t>
+        </is>
+      </c>
       <c r="AI157" s="21" t="n"/>
       <c r="AK157" s="21" t="n"/>
     </row>
     <row r="158" ht="32.25" customHeight="1" s="57">
       <c r="A158" s="21" t="n">
-        <v>200006</v>
+        <v>200004</v>
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>法术追击</t>
+          <t>法术反击</t>
         </is>
       </c>
       <c r="C158" s="21" t="n"/>
@@ -29953,7 +29969,7 @@
       </c>
       <c r="AB158" s="19" t="inlineStr">
         <is>
-          <t>code.Spell_200006</t>
+          <t>code.Spell_200004</t>
         </is>
       </c>
       <c r="AE158" s="11" t="inlineStr">
@@ -29976,23 +29992,23 @@
     </row>
     <row r="159" ht="32.25" customHeight="1" s="57">
       <c r="A159" s="21" t="n">
-        <v>200007</v>
+        <v>200005</v>
       </c>
       <c r="B159" s="19" t="inlineStr">
         <is>
-          <t>召唤宠物</t>
+          <t>物理追击</t>
         </is>
       </c>
       <c r="C159" s="21" t="n"/>
       <c r="D159" s="3" t="n"/>
       <c r="E159" s="19" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F159" s="19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>attack_damage</t>
         </is>
       </c>
       <c r="G159" s="19" t="n"/>
@@ -30003,7 +30019,7 @@
       <c r="M159" s="3" t="n"/>
       <c r="O159" s="11" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="Q159" s="11" t="inlineStr">
@@ -30027,284 +30043,326 @@
       </c>
       <c r="AB159" s="19" t="inlineStr">
         <is>
-          <t>code.Spell_summon_pet</t>
+          <t>code.Spell_200005</t>
         </is>
       </c>
       <c r="AE159" s="11" t="inlineStr">
         <is>
-          <t>BaseMagic</t>
+          <t>BaseAttack</t>
         </is>
       </c>
       <c r="AG159" s="11" t="inlineStr">
         <is>
-          <t>magic</t>
-        </is>
-      </c>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="AH159" s="11" t="n"/>
       <c r="AI159" s="21" t="n"/>
       <c r="AK159" s="21" t="n"/>
     </row>
     <row r="160" ht="32.25" customHeight="1" s="57">
-      <c r="A160" s="69" t="n">
-        <v>900001</v>
-      </c>
-      <c r="B160" s="70" t="inlineStr">
-        <is>
-          <t>单体攻击</t>
-        </is>
-      </c>
-      <c r="C160" s="65" t="n"/>
+      <c r="A160" s="21" t="n">
+        <v>200006</v>
+      </c>
+      <c r="B160" s="19" t="inlineStr">
+        <is>
+          <t>法术追击</t>
+        </is>
+      </c>
+      <c r="C160" s="21" t="n"/>
       <c r="D160" s="3" t="n"/>
-      <c r="E160" s="72" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="F160" s="72" t="n"/>
-      <c r="G160" s="72" t="n"/>
-      <c r="H160" s="72" t="n"/>
-      <c r="I160" s="72" t="n"/>
-      <c r="J160" s="70" t="n"/>
-      <c r="K160" s="70" t="n"/>
-      <c r="M160" s="71" t="inlineStr">
-        <is>
-          <t>CurrMP,1,10</t>
-        </is>
-      </c>
-      <c r="O160" s="71" t="inlineStr">
+      <c r="E160" s="19" t="inlineStr">
+        <is>
+          <t>magic</t>
+        </is>
+      </c>
+      <c r="F160" s="19" t="inlineStr">
+        <is>
+          <t>magic_damage</t>
+        </is>
+      </c>
+      <c r="G160" s="19" t="n"/>
+      <c r="H160" s="19" t="n"/>
+      <c r="I160" s="19" t="n"/>
+      <c r="J160" s="19" t="n"/>
+      <c r="K160" s="19" t="n"/>
+      <c r="M160" s="3" t="n"/>
+      <c r="O160" s="11" t="inlineStr">
         <is>
           <t>enemy</t>
         </is>
       </c>
-      <c r="Q160" s="71" t="inlineStr">
+      <c r="Q160" s="11" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="S160" s="71" t="inlineStr">
+      <c r="S160" s="11" t="inlineStr">
         <is>
           <t>alive</t>
         </is>
       </c>
-      <c r="U160" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="V160" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="W160" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB160" s="72" t="inlineStr">
-        <is>
-          <t>code.Spell_900001</t>
-        </is>
-      </c>
-      <c r="AE160" s="71" t="inlineStr">
-        <is>
-          <t>BaseAttack</t>
-        </is>
-      </c>
-      <c r="AG160" s="71" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
+      <c r="U160" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V160" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W160" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB160" s="19" t="inlineStr">
+        <is>
+          <t>code.Spell_200006</t>
+        </is>
+      </c>
+      <c r="AE160" s="11" t="inlineStr">
+        <is>
+          <t>BaseMagic</t>
+        </is>
+      </c>
+      <c r="AG160" s="11" t="inlineStr">
+        <is>
+          <t>magic</t>
+        </is>
+      </c>
+      <c r="AH160" s="11" t="inlineStr">
+        <is>
+          <t>FaQiu</t>
+        </is>
+      </c>
+      <c r="AI160" s="21" t="n"/>
+      <c r="AK160" s="21" t="n"/>
     </row>
     <row r="161" ht="32.25" customHeight="1" s="57">
-      <c r="A161" s="98" t="n">
-        <v>900015</v>
-      </c>
-      <c r="B161" s="98" t="n"/>
-      <c r="C161" s="98" t="n"/>
-      <c r="D161" s="98" t="n"/>
-      <c r="E161" s="98" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="F161" s="98" t="n"/>
-      <c r="G161" s="98" t="inlineStr">
-        <is>
-          <t>fire</t>
-        </is>
-      </c>
-      <c r="H161" s="98" t="n"/>
-      <c r="I161" s="98" t="n"/>
-      <c r="J161" s="99" t="n"/>
-      <c r="K161" s="99" t="n"/>
+      <c r="A161" s="21" t="n">
+        <v>200007</v>
+      </c>
+      <c r="B161" s="19" t="inlineStr">
+        <is>
+          <t>召唤宠物</t>
+        </is>
+      </c>
+      <c r="C161" s="21" t="n"/>
+      <c r="D161" s="3" t="n"/>
+      <c r="E161" s="19" t="inlineStr">
+        <is>
+          <t>magic</t>
+        </is>
+      </c>
+      <c r="F161" s="19" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G161" s="19" t="n"/>
+      <c r="H161" s="19" t="n"/>
+      <c r="I161" s="19" t="n"/>
+      <c r="J161" s="19" t="n"/>
+      <c r="K161" s="19" t="n"/>
       <c r="L161" s="98" t="n"/>
-      <c r="M161" s="98" t="n"/>
+      <c r="M161" s="3" t="n"/>
       <c r="N161" s="98" t="n"/>
-      <c r="O161" s="98" t="n"/>
+      <c r="O161" s="11" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
       <c r="P161" s="98" t="n"/>
-      <c r="Q161" s="98" t="n"/>
+      <c r="Q161" s="11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
       <c r="R161" s="98" t="n"/>
-      <c r="S161" s="98" t="n"/>
+      <c r="S161" s="11" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
       <c r="T161" s="98" t="n"/>
-      <c r="U161" s="99" t="n"/>
-      <c r="V161" s="98" t="n">
-        <v>3</v>
-      </c>
-      <c r="W161" s="98" t="n"/>
-      <c r="X161" s="98" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="U161" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V161" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W161" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X161" s="98" t="n"/>
       <c r="Y161" s="98" t="n"/>
       <c r="Z161" s="98" t="n"/>
       <c r="AA161" s="98" t="n"/>
-      <c r="AB161" s="98" t="n"/>
+      <c r="AB161" s="19" t="inlineStr">
+        <is>
+          <t>code.Spell_summon_pet</t>
+        </is>
+      </c>
       <c r="AC161" s="98" t="n"/>
       <c r="AD161" s="98" t="n"/>
-      <c r="AE161" s="98" t="n"/>
+      <c r="AE161" s="11" t="inlineStr">
+        <is>
+          <t>BaseMagic</t>
+        </is>
+      </c>
       <c r="AF161" s="98" t="n"/>
-      <c r="AG161" s="98" t="n"/>
+      <c r="AG161" s="11" t="inlineStr">
+        <is>
+          <t>magic</t>
+        </is>
+      </c>
       <c r="AH161" s="98" t="n"/>
-      <c r="AI161" s="98" t="n"/>
+      <c r="AI161" s="21" t="n"/>
       <c r="AJ161" s="98" t="n"/>
-      <c r="AK161" s="98" t="n"/>
+      <c r="AK161" s="21" t="n"/>
       <c r="AL161" s="98" t="n"/>
     </row>
     <row r="162" ht="32.25" customHeight="1" s="57">
-      <c r="A162" s="6" t="n">
-        <v>900023</v>
-      </c>
-      <c r="B162" s="43" t="inlineStr">
-        <is>
-          <t>水清决</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="n"/>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>damage,int</t>
-        </is>
-      </c>
-      <c r="E162" s="7" t="inlineStr">
+      <c r="A162" s="69" t="n">
+        <v>900001</v>
+      </c>
+      <c r="B162" s="70" t="inlineStr">
+        <is>
+          <t>单体攻击</t>
+        </is>
+      </c>
+      <c r="C162" s="65" t="n"/>
+      <c r="D162" s="3" t="n"/>
+      <c r="E162" s="72" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="J162" s="43" t="n"/>
-      <c r="K162" s="43" t="n"/>
-      <c r="M162" s="3" t="inlineStr">
+      <c r="F162" s="72" t="n"/>
+      <c r="G162" s="72" t="n"/>
+      <c r="H162" s="72" t="n"/>
+      <c r="I162" s="72" t="n"/>
+      <c r="J162" s="70" t="n"/>
+      <c r="K162" s="70" t="n"/>
+      <c r="L162" s="98" t="n"/>
+      <c r="M162" s="71" t="inlineStr">
         <is>
           <t>CurrMP,1,10</t>
         </is>
       </c>
-      <c r="O162" s="3" t="inlineStr">
+      <c r="N162" s="98" t="n"/>
+      <c r="O162" s="71" t="inlineStr">
         <is>
           <t>enemy</t>
         </is>
       </c>
-      <c r="Q162" s="3" t="inlineStr">
+      <c r="P162" s="98" t="n"/>
+      <c r="Q162" s="71" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="S162" s="3" t="inlineStr">
+      <c r="R162" s="98" t="n"/>
+      <c r="S162" s="71" t="inlineStr">
         <is>
           <t>alive</t>
         </is>
       </c>
-      <c r="U162" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V162" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W162" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB162" s="7" t="inlineStr">
-        <is>
-          <t>code.Spell_300001</t>
-        </is>
-      </c>
-      <c r="AE162" s="3" t="inlineStr">
+      <c r="T162" s="98" t="n"/>
+      <c r="U162" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V162" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W162" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="X162" s="98" t="n"/>
+      <c r="Y162" s="98" t="n"/>
+      <c r="Z162" s="98" t="n"/>
+      <c r="AA162" s="98" t="n"/>
+      <c r="AB162" s="72" t="inlineStr">
+        <is>
+          <t>code.Spell_900001</t>
+        </is>
+      </c>
+      <c r="AC162" s="98" t="n"/>
+      <c r="AD162" s="98" t="n"/>
+      <c r="AE162" s="71" t="inlineStr">
         <is>
           <t>BaseAttack</t>
         </is>
       </c>
-      <c r="AG162" s="3" t="inlineStr">
+      <c r="AF162" s="98" t="n"/>
+      <c r="AG162" s="71" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
+      <c r="AH162" s="98" t="n"/>
+      <c r="AI162" s="98" t="n"/>
+      <c r="AJ162" s="98" t="n"/>
+      <c r="AK162" s="98" t="n"/>
+      <c r="AL162" s="98" t="n"/>
     </row>
     <row r="163" ht="32.25" customHeight="1" s="57">
-      <c r="A163" s="6" t="n">
-        <v>900024</v>
-      </c>
-      <c r="B163" s="43" t="inlineStr">
-        <is>
-          <t>冰清决</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="n"/>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>damage,int</t>
-        </is>
-      </c>
-      <c r="E163" s="7" t="inlineStr">
+      <c r="A163" s="98" t="n">
+        <v>900015</v>
+      </c>
+      <c r="B163" s="98" t="n"/>
+      <c r="C163" s="98" t="n"/>
+      <c r="D163" s="98" t="n"/>
+      <c r="E163" s="98" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="J163" s="43" t="n"/>
-      <c r="K163" s="43" t="n"/>
-      <c r="M163" s="3" t="inlineStr">
-        <is>
-          <t>CurrMP,1,10</t>
-        </is>
-      </c>
-      <c r="O163" s="3" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="Q163" s="3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="S163" s="3" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
-      <c r="U163" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V163" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W163" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB163" s="7" t="inlineStr">
-        <is>
-          <t>code.Spell_300001</t>
-        </is>
-      </c>
-      <c r="AE163" s="3" t="inlineStr">
-        <is>
-          <t>BaseAttack</t>
-        </is>
-      </c>
-      <c r="AG163" s="3" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
+      <c r="F163" s="98" t="n"/>
+      <c r="G163" s="98" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="H163" s="98" t="n"/>
+      <c r="I163" s="98" t="n"/>
+      <c r="J163" s="99" t="n"/>
+      <c r="K163" s="99" t="n"/>
+      <c r="L163" s="98" t="n"/>
+      <c r="M163" s="98" t="n"/>
+      <c r="N163" s="98" t="n"/>
+      <c r="O163" s="98" t="n"/>
+      <c r="P163" s="98" t="n"/>
+      <c r="Q163" s="98" t="n"/>
+      <c r="R163" s="98" t="n"/>
+      <c r="S163" s="98" t="n"/>
+      <c r="T163" s="98" t="n"/>
+      <c r="U163" s="99" t="n"/>
+      <c r="V163" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="W163" s="98" t="n"/>
+      <c r="X163" s="98" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y163" s="98" t="n"/>
+      <c r="Z163" s="98" t="n"/>
+      <c r="AA163" s="98" t="n"/>
+      <c r="AB163" s="98" t="n"/>
+      <c r="AC163" s="98" t="n"/>
+      <c r="AD163" s="98" t="n"/>
+      <c r="AE163" s="98" t="n"/>
+      <c r="AF163" s="98" t="n"/>
+      <c r="AG163" s="98" t="n"/>
+      <c r="AH163" s="98" t="n"/>
+      <c r="AI163" s="98" t="n"/>
+      <c r="AJ163" s="98" t="n"/>
+      <c r="AK163" s="98" t="n"/>
+      <c r="AL163" s="98" t="n"/>
     </row>
     <row r="164" ht="32.25" customHeight="1" s="57">
       <c r="A164" s="6" t="n">
-        <v>900025</v>
+        <v>900023</v>
       </c>
       <c r="B164" s="43" t="inlineStr">
         <is>
-          <t>玉清诀</t>
+          <t>水清决</t>
         </is>
       </c>
       <c r="C164" s="6" t="n"/>
@@ -30367,11 +30425,11 @@
     </row>
     <row r="165" ht="32.25" customHeight="1" s="57">
       <c r="A165" s="6" t="n">
-        <v>900026</v>
+        <v>900024</v>
       </c>
       <c r="B165" s="43" t="inlineStr">
         <is>
-          <t>晶清决</t>
+          <t>冰清决</t>
         </is>
       </c>
       <c r="C165" s="6" t="n"/>
@@ -30434,11 +30492,11 @@
     </row>
     <row r="166" ht="32.25" customHeight="1" s="57">
       <c r="A166" s="6" t="n">
-        <v>900027</v>
+        <v>900025</v>
       </c>
       <c r="B166" s="43" t="inlineStr">
         <is>
-          <t>笑里藏刀</t>
+          <t>玉清诀</t>
         </is>
       </c>
       <c r="C166" s="6" t="n"/>
@@ -30501,11 +30559,11 @@
     </row>
     <row r="167" ht="32.25" customHeight="1" s="57">
       <c r="A167" s="6" t="n">
-        <v>900028</v>
+        <v>900026</v>
       </c>
       <c r="B167" s="43" t="inlineStr">
         <is>
-          <t>野兽之力</t>
+          <t>晶清决</t>
         </is>
       </c>
       <c r="C167" s="6" t="n"/>
@@ -30568,11 +30626,11 @@
     </row>
     <row r="168" ht="32.25" customHeight="1" s="57">
       <c r="A168" s="6" t="n">
-        <v>900029</v>
+        <v>900027</v>
       </c>
       <c r="B168" s="43" t="inlineStr">
         <is>
-          <t>魔兽之印</t>
+          <t>笑里藏刀</t>
         </is>
       </c>
       <c r="C168" s="6" t="n"/>
@@ -30635,11 +30693,11 @@
     </row>
     <row r="169" ht="32.25" customHeight="1" s="57">
       <c r="A169" s="6" t="n">
-        <v>900030</v>
+        <v>900028</v>
       </c>
       <c r="B169" s="43" t="inlineStr">
         <is>
-          <t>圣甲之灵</t>
+          <t>野兽之力</t>
         </is>
       </c>
       <c r="C169" s="6" t="n"/>
@@ -30702,11 +30760,11 @@
     </row>
     <row r="170" ht="32.25" customHeight="1" s="57">
       <c r="A170" s="6" t="n">
-        <v>900031</v>
+        <v>900029</v>
       </c>
       <c r="B170" s="43" t="inlineStr">
         <is>
-          <t>罗汉金钟</t>
+          <t>魔兽之印</t>
         </is>
       </c>
       <c r="C170" s="6" t="n"/>
@@ -30769,11 +30827,11 @@
     </row>
     <row r="171" ht="32.25" customHeight="1" s="57">
       <c r="A171" s="6" t="n">
-        <v>900032</v>
+        <v>900030</v>
       </c>
       <c r="B171" s="43" t="inlineStr">
         <is>
-          <t>放下屠刀</t>
+          <t>圣甲之灵</t>
         </is>
       </c>
       <c r="C171" s="6" t="n"/>
@@ -30836,11 +30894,11 @@
     </row>
     <row r="172" ht="32.25" customHeight="1" s="57">
       <c r="A172" s="6" t="n">
-        <v>900033</v>
+        <v>900031</v>
       </c>
       <c r="B172" s="43" t="inlineStr">
         <is>
-          <t>破血狂攻</t>
+          <t>罗汉金钟</t>
         </is>
       </c>
       <c r="C172" s="6" t="n"/>
@@ -30903,11 +30961,11 @@
     </row>
     <row r="173" ht="32.25" customHeight="1" s="57">
       <c r="A173" s="6" t="n">
-        <v>900034</v>
+        <v>900032</v>
       </c>
       <c r="B173" s="43" t="inlineStr">
         <is>
-          <t>弱点击破</t>
+          <t>放下屠刀</t>
         </is>
       </c>
       <c r="C173" s="6" t="n"/>
@@ -30970,11 +31028,11 @@
     </row>
     <row r="174" ht="32.25" customHeight="1" s="57">
       <c r="A174" s="6" t="n">
-        <v>900035</v>
+        <v>900033</v>
       </c>
       <c r="B174" s="43" t="inlineStr">
         <is>
-          <t>破碎无双</t>
+          <t>破血狂攻</t>
         </is>
       </c>
       <c r="C174" s="6" t="n"/>
@@ -31041,11 +31099,11 @@
     </row>
     <row r="175" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A175" s="6" t="n">
-        <v>900036</v>
+        <v>900034</v>
       </c>
       <c r="B175" s="43" t="inlineStr">
         <is>
-          <t>气疗术</t>
+          <t>弱点击破</t>
         </is>
       </c>
       <c r="C175" s="6" t="n"/>
@@ -31056,7 +31114,7 @@
       </c>
       <c r="E175" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F175" s="19" t="n"/>
@@ -31115,11 +31173,11 @@
     </row>
     <row r="176" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A176" s="6" t="n">
-        <v>900037</v>
+        <v>900035</v>
       </c>
       <c r="B176" s="43" t="inlineStr">
         <is>
-          <t>心疗术</t>
+          <t>破碎无双</t>
         </is>
       </c>
       <c r="C176" s="6" t="n"/>
@@ -31130,7 +31188,7 @@
       </c>
       <c r="E176" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F176" s="19" t="n"/>
@@ -31189,11 +31247,11 @@
     </row>
     <row r="177" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A177" s="6" t="n">
-        <v>900038</v>
+        <v>900036</v>
       </c>
       <c r="B177" s="43" t="inlineStr">
         <is>
-          <t>命疗术</t>
+          <t>气疗术</t>
         </is>
       </c>
       <c r="C177" s="6" t="n"/>
@@ -31263,11 +31321,11 @@
     </row>
     <row r="178" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A178" s="6" t="n">
-        <v>900039</v>
+        <v>900037</v>
       </c>
       <c r="B178" s="43" t="inlineStr">
         <is>
-          <t>起死回生</t>
+          <t>心疗术</t>
         </is>
       </c>
       <c r="C178" s="6" t="n"/>
@@ -31337,11 +31395,11 @@
     </row>
     <row r="179" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A179" s="6" t="n">
-        <v>900040</v>
+        <v>900038</v>
       </c>
       <c r="B179" s="43" t="inlineStr">
         <is>
-          <t>回魂咒</t>
+          <t>命疗术</t>
         </is>
       </c>
       <c r="C179" s="6" t="n"/>
@@ -31416,11 +31474,11 @@
     </row>
     <row r="180" ht="30" customFormat="1" customHeight="1" s="11">
       <c r="A180" s="6" t="n">
-        <v>900041</v>
+        <v>900039</v>
       </c>
       <c r="B180" s="43" t="inlineStr">
         <is>
-          <t>测试技能</t>
+          <t>起死回生</t>
         </is>
       </c>
       <c r="C180" s="6" t="n"/>
@@ -31431,7 +31489,7 @@
       </c>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F180" s="19" t="n"/>
@@ -31441,7 +31499,11 @@
       <c r="J180" s="43" t="n"/>
       <c r="K180" s="43" t="n"/>
       <c r="L180" s="0" t="n"/>
-      <c r="M180" s="98" t="n"/>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>CurrMP,1,10</t>
+        </is>
+      </c>
       <c r="N180" s="98" t="n"/>
       <c r="O180" s="3" t="inlineStr">
         <is>
@@ -31500,159 +31562,321 @@
     </row>
     <row r="181" ht="16.5" customHeight="1" s="57">
       <c r="A181" s="6" t="n">
-        <v>1145142</v>
-      </c>
-      <c r="B181" s="6" t="inlineStr">
-        <is>
-          <t>测试技能</t>
-        </is>
-      </c>
-      <c r="C181" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D181" s="98" t="n"/>
-      <c r="E181" s="0" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="F181" s="0" t="inlineStr">
-        <is>
-          <t>attack_damage</t>
-        </is>
-      </c>
-      <c r="G181" s="0" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H181" s="0" t="n">
-        <v>1</v>
-      </c>
+        <v>900040</v>
+      </c>
+      <c r="B181" s="43" t="inlineStr">
+        <is>
+          <t>回魂咒</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="n"/>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>damage,int</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F181" s="19" t="n"/>
+      <c r="G181" s="19" t="n"/>
+      <c r="H181" s="19" t="n"/>
       <c r="I181" s="19" t="n"/>
-      <c r="J181" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" s="19" t="n"/>
-      <c r="L181" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" s="98" t="n"/>
+      <c r="J181" s="43" t="n"/>
+      <c r="K181" s="43" t="n"/>
+      <c r="L181" s="0" t="n"/>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>CurrMP,1,10</t>
+        </is>
+      </c>
       <c r="N181" s="98" t="n"/>
-      <c r="O181" s="11" t="n"/>
+      <c r="O181" s="3" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
       <c r="P181" s="98" t="n"/>
-      <c r="Q181" s="11" t="n"/>
+      <c r="Q181" s="3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
       <c r="R181" s="98" t="n"/>
-      <c r="S181" s="11" t="n"/>
-      <c r="T181" s="0" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="U181" s="11" t="n"/>
-      <c r="V181" s="11" t="n"/>
-      <c r="W181" s="11" t="n"/>
-      <c r="X181" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y181" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="S181" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+      <c r="T181" s="0" t="n"/>
+      <c r="U181" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V181" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W181" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X181" s="0" t="n"/>
+      <c r="Y181" s="0" t="n"/>
       <c r="Z181" s="98" t="n"/>
       <c r="AA181" s="98" t="n"/>
-      <c r="AB181" s="19" t="n"/>
+      <c r="AB181" s="7" t="inlineStr">
+        <is>
+          <t>code.Spell_300001</t>
+        </is>
+      </c>
       <c r="AC181" s="98" t="n"/>
       <c r="AD181" s="98" t="n"/>
-      <c r="AE181" s="11" t="n"/>
-      <c r="AF181" s="0" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AG181" s="11" t="n"/>
-      <c r="AH181" s="98" t="n"/>
+      <c r="AE181" s="3" t="inlineStr">
+        <is>
+          <t>BaseAttack</t>
+        </is>
+      </c>
+      <c r="AF181" s="0" t="n"/>
+      <c r="AG181" s="3" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="AH181" s="11" t="n"/>
       <c r="AI181" s="21" t="n"/>
       <c r="AJ181" s="98" t="n"/>
       <c r="AK181" s="21" t="n"/>
       <c r="AL181" s="98" t="n"/>
     </row>
     <row r="182" ht="16.5" customHeight="1" s="57">
-      <c r="A182" s="98" t="n"/>
-      <c r="B182" s="98" t="n"/>
-      <c r="C182" s="98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D182" s="98" t="n"/>
-      <c r="E182" s="98" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="F182" s="98" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="G182" s="98" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H182" s="98" t="b">
-        <v>0</v>
-      </c>
-      <c r="I182" s="98" t="n"/>
-      <c r="J182" s="99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K182" s="99" t="n"/>
-      <c r="L182" s="98" t="b">
-        <v>0</v>
-      </c>
+      <c r="A182" s="6" t="n">
+        <v>900041</v>
+      </c>
+      <c r="B182" s="43" t="inlineStr">
+        <is>
+          <t>测试技能</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="n"/>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>damage,int</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="F182" s="19" t="n"/>
+      <c r="G182" s="19" t="n"/>
+      <c r="H182" s="19" t="n"/>
+      <c r="I182" s="19" t="n"/>
+      <c r="J182" s="43" t="n"/>
+      <c r="K182" s="43" t="n"/>
+      <c r="L182" s="0" t="n"/>
       <c r="M182" s="98" t="n"/>
       <c r="N182" s="98" t="n"/>
-      <c r="O182" s="98" t="n"/>
+      <c r="O182" s="3" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
       <c r="P182" s="98" t="n"/>
-      <c r="Q182" s="98" t="n"/>
+      <c r="Q182" s="3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
       <c r="R182" s="98" t="n"/>
-      <c r="S182" s="98" t="n"/>
-      <c r="T182" s="98" t="n"/>
-      <c r="U182" s="99" t="n"/>
-      <c r="V182" s="98" t="n"/>
-      <c r="W182" s="98" t="n"/>
-      <c r="X182" s="98" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y182" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="S182" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+      <c r="T182" s="0" t="n"/>
+      <c r="U182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X182" s="0" t="n"/>
+      <c r="Y182" s="0" t="n"/>
       <c r="Z182" s="98" t="n"/>
       <c r="AA182" s="98" t="n"/>
-      <c r="AB182" s="98" t="n"/>
+      <c r="AB182" s="7" t="inlineStr">
+        <is>
+          <t>code.Spell_300001</t>
+        </is>
+      </c>
       <c r="AC182" s="98" t="n"/>
       <c r="AD182" s="98" t="n"/>
-      <c r="AE182" s="98" t="n"/>
-      <c r="AF182" s="98" t="inlineStr">
+      <c r="AE182" s="3" t="inlineStr">
+        <is>
+          <t>BaseAttack</t>
+        </is>
+      </c>
+      <c r="AF182" s="0" t="n"/>
+      <c r="AG182" s="3" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="AH182" s="11" t="n"/>
+      <c r="AI182" s="21" t="n"/>
+      <c r="AJ182" s="98" t="n"/>
+      <c r="AK182" s="21" t="n"/>
+      <c r="AL182" s="98" t="n"/>
+    </row>
+    <row r="183" ht="16.5" customHeight="1" s="57">
+      <c r="A183" s="6" t="n">
+        <v>1145142</v>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>测试技能</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" s="98" t="n"/>
+      <c r="E183" s="0" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="F183" s="0" t="inlineStr">
+        <is>
+          <t>attack_damage</t>
+        </is>
+      </c>
+      <c r="G183" s="0" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I183" s="19" t="n"/>
+      <c r="J183" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" s="19" t="n"/>
+      <c r="L183" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" s="98" t="n"/>
+      <c r="N183" s="98" t="n"/>
+      <c r="O183" s="11" t="n"/>
+      <c r="P183" s="98" t="n"/>
+      <c r="Q183" s="11" t="n"/>
+      <c r="R183" s="98" t="n"/>
+      <c r="S183" s="11" t="n"/>
+      <c r="T183" s="0" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="U183" s="11" t="n"/>
+      <c r="V183" s="11" t="n"/>
+      <c r="W183" s="11" t="n"/>
+      <c r="X183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z183" s="98" t="n"/>
+      <c r="AA183" s="98" t="n"/>
+      <c r="AB183" s="19" t="n"/>
+      <c r="AC183" s="98" t="n"/>
+      <c r="AD183" s="98" t="n"/>
+      <c r="AE183" s="11" t="n"/>
+      <c r="AF183" s="0" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="AG182" s="98" t="n"/>
-      <c r="AH182" s="98" t="n"/>
-      <c r="AI182" s="98" t="n"/>
-      <c r="AJ182" s="98" t="n"/>
-      <c r="AK182" s="98" t="n"/>
-      <c r="AL182" s="98" t="n"/>
-    </row>
-    <row r="183" ht="16.5" customHeight="1" s="57">
-      <c r="A183" s="6" t="n"/>
-      <c r="B183" s="6" t="n"/>
-      <c r="C183" s="6" t="n"/>
+      <c r="AG183" s="11" t="n"/>
+      <c r="AH183" s="98" t="n"/>
+      <c r="AI183" s="21" t="n"/>
+      <c r="AJ183" s="98" t="n"/>
+      <c r="AK183" s="21" t="n"/>
+      <c r="AL183" s="98" t="n"/>
     </row>
     <row r="184" ht="16.5" customHeight="1" s="57">
-      <c r="A184" s="6" t="n"/>
-      <c r="B184" s="6" t="n"/>
-      <c r="C184" s="6" t="n"/>
+      <c r="A184" s="98" t="n"/>
+      <c r="B184" s="98" t="n"/>
+      <c r="C184" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" s="98" t="n"/>
+      <c r="E184" s="98" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F184" s="98" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G184" s="98" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H184" s="98" t="b">
+        <v>0</v>
+      </c>
+      <c r="I184" s="98" t="n"/>
+      <c r="J184" s="99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" s="99" t="n"/>
+      <c r="L184" s="98" t="b">
+        <v>0</v>
+      </c>
+      <c r="M184" s="98" t="n"/>
+      <c r="N184" s="98" t="n"/>
+      <c r="O184" s="98" t="n"/>
+      <c r="P184" s="98" t="n"/>
+      <c r="Q184" s="98" t="n"/>
+      <c r="R184" s="98" t="n"/>
+      <c r="S184" s="98" t="n"/>
+      <c r="T184" s="98" t="n"/>
+      <c r="U184" s="99" t="n"/>
+      <c r="V184" s="98" t="n"/>
+      <c r="W184" s="98" t="n"/>
+      <c r="X184" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y184" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z184" s="98" t="n"/>
+      <c r="AA184" s="98" t="n"/>
+      <c r="AB184" s="98" t="n"/>
+      <c r="AC184" s="98" t="n"/>
+      <c r="AD184" s="98" t="n"/>
+      <c r="AE184" s="98" t="n"/>
+      <c r="AF184" s="98" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AG184" s="98" t="n"/>
+      <c r="AH184" s="98" t="n"/>
+      <c r="AI184" s="98" t="n"/>
+      <c r="AJ184" s="98" t="n"/>
+      <c r="AK184" s="98" t="n"/>
+      <c r="AL184" s="98" t="n"/>
     </row>
     <row r="185" ht="16.5" customHeight="1" s="57">
       <c r="A185" s="6" t="n"/>
